--- a/tame_output/ON/bt/strategyON_20240720.xlsx
+++ b/tame_output/ON/bt/strategyON_20240720.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>30.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-72.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.8%</t>
+          <t>110.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-644.5%</t>
+          <t>-664.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-48.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.7%</t>
+          <t>-67.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.3%</t>
+          <t>453.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-498.7%</t>
+          <t>-505.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-258.2%</t>
+          <t>-266.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-36.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-129.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-144.0%</t>
+          <t>-146.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-132.1%</t>
+          <t>-136.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7213888716875563</v>
+        <v>-0.9216650444977963</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.832416789337956</v>
+        <v>2.75230632021386</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7099996350327549</v>
+        <v>-0.9102758078429949</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.834797280119117</v>
+        <v>2.754686810995021</v>
       </c>
       <c r="F1846" t="n">
         <v>1.405815606229521</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.127753658579592</v>
+        <v>-1.328029831389832</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.665622562205445</v>
+        <v>2.585512093081349</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9880615826826838</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.417885325185023</v>
+        <v>-1.618161497995263</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.549436112162195</v>
+        <v>2.469325643038099</v>
       </c>
       <c r="F1848" t="n">
         <v>1.012143377422864</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.625889383538101</v>
+        <v>-1.826165556348341</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.471126633374889</v>
+        <v>2.391016164250793</v>
       </c>
       <c r="F1849" t="n">
         <v>1.012143377422864</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.688067794699071</v>
+        <v>-1.888343967509311</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.441336725248489</v>
+        <v>2.361226256124393</v>
       </c>
       <c r="F1850" t="n">
         <v>0.9499649662618935</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.054136521843724</v>
+        <v>-2.254412694653963</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.287993533697077</v>
+        <v>2.207883064572981</v>
       </c>
       <c r="F1851" t="n">
         <v>0.5838962391172409</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.262627303295408</v>
+        <v>-2.462903476105648</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.224935510855171</v>
+        <v>2.144825041731075</v>
       </c>
       <c r="F1852" t="n">
         <v>0.3754054576655564</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.50982848806063</v>
+        <v>-2.710104660870869</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.134153787357651</v>
+        <v>2.054043318233555</v>
       </c>
       <c r="F1853" t="n">
         <v>0.3955588111643689</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.002213516084727</v>
+        <v>-3.202489688894966</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.938306168191745</v>
+        <v>1.858195699067649</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.09682621685972786</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.387393907014799</v>
+        <v>-3.587670079825038</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.782776550632579</v>
+        <v>1.702666081508483</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.09682621685972786</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.637264587029381</v>
+        <v>-3.83754075983962</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.684597402081363</v>
+        <v>1.604486932957267</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.06056349702926461</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.843776363916402</v>
+        <v>-4.044052536726641</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.598098749982812</v>
+        <v>1.517988280858716</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.2670752739162861</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.163120438996904</v>
+        <v>-4.363396611807143</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.472134046650871</v>
+        <v>1.392023577526775</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.2670752739162861</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.594926232146691</v>
+        <v>-4.79520240495693</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.28574461685836</v>
+        <v>1.205634147734264</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4034927703575531</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.829620226279244</v>
+        <v>-5.029896399089482</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.18015179420743</v>
+        <v>1.100041325083334</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.3971565031282979</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.165282873509696</v>
+        <v>-5.365559046319935</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.044467326971214</v>
+        <v>0.9643568578471182</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.4650874886172027</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.241727203712568</v>
+        <v>-5.442003376522806</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.020377155124307</v>
+        <v>0.9402666860002111</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.3846419795235408</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.606854586351314</v>
+        <v>-5.807130759161553</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8735807170746397</v>
+        <v>0.7934702479505438</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.6809527638225534</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.015443363531993</v>
+        <v>-6.215719536342232</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7089067502171269</v>
+        <v>0.628796281093031</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.089541541003232</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.129203775554858</v>
+        <v>-6.329479948365097</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6585880178794419</v>
+        <v>0.578477548755346</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.089541541003232</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.545595649841855</v>
+        <v>-6.745871822652094</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4900253187735202</v>
+        <v>0.4099148496494243</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.089541541003232</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.789867050568925</v>
+        <v>-6.990143223379164</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4025754491513713</v>
+        <v>0.3224649800272754</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.089541541003232</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.995118069805685</v>
+        <v>-7.195394242615924</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3165746066023623</v>
+        <v>0.2364641374782663</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.089541541003232</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.043320887048029</v>
+        <v>-7.243597059858268</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2956983997604259</v>
+        <v>0.21558793063633</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.089541541003232</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.339982228858227</v>
+        <v>-7.540258401668465</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1808128389655548</v>
+        <v>0.1007023698414593</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.15828467673711</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.526701937167529</v>
+        <v>-7.726978109977768</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1020986511074309</v>
+        <v>0.02198818198333496</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.15828467673711</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.909703325910161</v>
+        <v>-8.109979498720399</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.05120400571120598</v>
+        <v>-0.1313144748353015</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.15828467673711</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.914189771111549</v>
+        <v>-8.114465943921788</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05042706782033113</v>
+        <v>-0.1305375369444266</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.162771121938499</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.273720093615552</v>
+        <v>-8.47399626642579</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1888888935238819</v>
+        <v>-0.268999362647977</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.162771121938499</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.324069157069774</v>
+        <v>-8.524345329880012</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2011124989483934</v>
+        <v>-0.2812229680724885</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.213120185392721</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.42168843449117</v>
+        <v>-8.621964607301408</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2371184592951829</v>
+        <v>-0.317228928419278</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.310739462814118</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.475759933999528</v>
+        <v>-8.676036106809766</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.255853502776954</v>
+        <v>-0.3359639719010494</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.364810962322477</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.680018109329392</v>
+        <v>-8.88029428213963</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3320435757902573</v>
+        <v>-0.4121540449143524</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.492449906936466</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.713670947837866</v>
+        <v>-8.913947120648103</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3410221567092107</v>
+        <v>-0.4211326258333057</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.592863274853503</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.640201116170417</v>
+        <v>-8.840477288980654</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.29626252254881</v>
+        <v>-0.3763729916729051</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.519393443186055</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.81532553355696</v>
+        <v>-9.015601706367198</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3517570687559104</v>
+        <v>-0.4318675378800054</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.694517860572599</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.04977762757145</v>
+        <v>-9.250053800381687</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4527570712633024</v>
+        <v>-0.5328675403873975</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.694517860572599</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.154152358597896</v>
+        <v>-9.354428531408134</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5011791544478572</v>
+        <v>-0.5812896235719522</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.798892591599045</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.206938514198223</v>
+        <v>-9.407214687008461</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5211778268494314</v>
+        <v>-0.6012882959735264</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.894568078181442</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.332975307566512</v>
+        <v>-9.53325148037675</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5688988155676324</v>
+        <v>-0.6490092846917275</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.869316455371699</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.275903535670581</v>
+        <v>-9.476179708480819</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5420797711228591</v>
+        <v>-0.6221902402469546</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.869316455371699</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.417575377394702</v>
+        <v>-9.617851550204939</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6002237347112489</v>
+        <v>-0.6803342038353444</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.869316455371699</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.367984532969867</v>
+        <v>-9.568260705780105</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5653339867764431</v>
+        <v>-0.6454444559005381</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.819725610946866</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.219066198498011</v>
+        <v>-9.419342371308248</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5188177866343833</v>
+        <v>-0.5989282557584787</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.788476020211692</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.993221045778601</v>
+        <v>-9.193497218588838</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4189006525104109</v>
+        <v>-0.4990111216345059</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.746549344624529</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.868642389441009</v>
+        <v>-9.068918562251246</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3679300454193153</v>
+        <v>-0.4480405145434103</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.746549344624529</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.921537677485295</v>
+        <v>-9.121813850295533</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3864543864749219</v>
+        <v>-0.4665648555990174</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.741593998536083</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.849404502197414</v>
+        <v>-9.049680675007652</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3518674121211331</v>
+        <v>-0.4319778812452282</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.741593998536083</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.778038109587767</v>
+        <v>-8.978314282398005</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3330581174711393</v>
+        <v>-0.4131685865952344</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.670227605926435</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.684579075602542</v>
+        <v>-8.88485524841278</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.305557985189957</v>
+        <v>-0.3856684543140525</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.670227605926435</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.417337274734145</v>
+        <v>-8.617613447544382</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2004958253419717</v>
+        <v>-0.2806062944660668</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.670227605926435</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.319430236057654</v>
+        <v>-8.519706408867892</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1616333248448365</v>
+        <v>-0.2417437939689315</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.602241856065878</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.295476695081696</v>
+        <v>-8.495752867891934</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1513834023089595</v>
+        <v>-0.2314938714330546</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.578288315089921</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.031416756758899</v>
+        <v>-8.231692929569137</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05901974314159286</v>
+        <v>-0.1391302122656883</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.314228376767125</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.324337133254061</v>
+        <v>-7.524613306064299</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2210250726000416</v>
+        <v>0.1409146034759461</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.314228376767125</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.284152834887871</v>
+        <v>-7.484429007698108</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2374424158343591</v>
+        <v>0.1573319467102636</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.274044078400934</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.120752963948508</v>
+        <v>-7.321029136758746</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.302169185430861</v>
+        <v>0.2220587163067655</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.110644207461571</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.88727174171891</v>
+        <v>-7.087547914529147</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4034861031605526</v>
+        <v>0.3233756340364575</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8771629852319727</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.737605350711394</v>
+        <v>-6.937881523521632</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4604604492505997</v>
+        <v>0.3803499801265042</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7842594939894367</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.605329877080508</v>
+        <v>-6.805606049890746</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5087381254499812</v>
+        <v>0.4286276563258862</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.6519840203585501</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.449591544520766</v>
+        <v>-6.649867717331004</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5738485191615146</v>
+        <v>0.4937380500374196</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4962456877988085</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.200591745837185</v>
+        <v>-6.400867918647423</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6863547798586058</v>
+        <v>0.6062443107345108</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.4962456877988085</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.30618173561029</v>
+        <v>-6.506457908420527</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5161428543501452</v>
+        <v>0.4360323852260501</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.6018356775719129</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.324916637728887</v>
+        <v>-6.525192810539124</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5571932353797928</v>
+        <v>0.4770827662556978</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.6074316872320442</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.176976596321287</v>
+        <v>-6.377252769131525</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.496490329254665</v>
+        <v>0.4163798601305699</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.5871107713234867</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.124007074067299</v>
+        <v>-6.324283246877537</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5089641519027821</v>
+        <v>0.4288536827786871</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.5341412490694978</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.080458667296608</v>
+        <v>-6.280734840106846</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5194229025159651</v>
+        <v>0.4393124333918701</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.5341412490694978</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.04709546081784</v>
+        <v>-6.247371633628077</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5472305394886159</v>
+        <v>0.4671200703645209</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.5341412490694978</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.938836323695318</v>
+        <v>-6.139112496505556</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5850663147968196</v>
+        <v>0.5049558456727246</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.5341412490694978</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.815545188878187</v>
+        <v>-6.015821361688425</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6318808627342487</v>
+        <v>0.5517703936101537</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.4108501142523673</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.794395989974744</v>
+        <v>-5.994672162784981</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6480415205329515</v>
+        <v>0.567931051408856</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.3897009153489239</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.550630547991299</v>
+        <v>-5.750906720801537</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7413284056733795</v>
+        <v>0.6612179365492845</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.3897009153489239</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.448867727714005</v>
+        <v>-5.649143900524242</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7841578477043138</v>
+        <v>0.7040473785802184</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.3764818469564952</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.19901733376493</v>
+        <v>-5.399293506575168</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8768400802676455</v>
+        <v>0.7967296111435505</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.3764818469564952</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.023125241297498</v>
+        <v>-5.223401414107736</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9507960407752671</v>
+        <v>0.8706855716511721</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.3764818469564952</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.851678778275034</v>
+        <v>-5.051954951085272</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.032702132038806</v>
+        <v>0.9525916629147111</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.2050353839340321</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.777389212536695</v>
+        <v>-4.977665385346933</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.061438435950439</v>
+        <v>0.9813279668263437</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.1307458181956928</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.713753470302761</v>
+        <v>-4.914029643112999</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.09158753389833</v>
+        <v>1.011477064774235</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.06711007596175828</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.602326710976841</v>
+        <v>-4.802602883787078</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.117352496412494</v>
+        <v>1.037242027288399</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.06711007596175828</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.36189621417198</v>
+        <v>-4.562172386982218</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.215267771759315</v>
+        <v>1.13515730263522</v>
       </c>
       <c r="F1925" t="n">
         <v>0.173320420843102</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.289653646000786</v>
+        <v>-4.489929818811023</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.248094112862613</v>
+        <v>1.167983643738518</v>
       </c>
       <c r="F1926" t="n">
         <v>0.173320420843102</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.236655323719398</v>
+        <v>-4.436931496529636</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.269972025692508</v>
+        <v>1.189861556568413</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2286566798450408</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.127850438239671</v>
+        <v>-4.328126611049909</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.310492051104393</v>
+        <v>1.230381581980298</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2286566798450408</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.90782964020266</v>
+        <v>-4.108105813012898</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.400079407329811</v>
+        <v>1.319968938205716</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3698765249130211</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.774961951139382</v>
+        <v>-3.97523812394962</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.469120665756946</v>
+        <v>1.389010196632851</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3698765249130211</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.654788867774883</v>
+        <v>-3.855065040585121</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.518335743543047</v>
+        <v>1.438225274418952</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4900496082775201</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.510116722675146</v>
+        <v>-3.710392895485383</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.586292704144382</v>
+        <v>1.506182235020287</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6347217533772576</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.569991550032838</v>
+        <v>-3.770267722843076</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.548380264602731</v>
+        <v>1.468269795478636</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5748469260195654</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.450171319122</v>
+        <v>-3.650447491932238</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.611597526201274</v>
+        <v>1.531487057077179</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5748469260195654</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.452641025583806</v>
+        <v>-3.652917198394044</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.518253842938994</v>
+        <v>1.438143373814898</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5723772195577592</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.521011211907816</v>
+        <v>-3.721287384718054</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.410167629894691</v>
+        <v>1.330057160770596</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5816529185939742</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.534799264754863</v>
+        <v>-3.735075437565101</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.395089117387764</v>
+        <v>1.314978648263669</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5816529185939742</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.565792424083568</v>
+        <v>-3.766068596893806</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.207401418696668</v>
+        <v>1.127290949572573</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5816529185939742</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.390318164291099</v>
+        <v>-3.590594337101337</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.282158354605444</v>
+        <v>1.202047885481349</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5816529185939742</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.501254416932348</v>
+        <v>-3.701530589742585</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.213525882310151</v>
+        <v>1.133415413186056</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5816529185939742</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.467590871460066</v>
+        <v>-3.667867044270304</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.155529613900514</v>
+        <v>1.075419144776419</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6153164640662561</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.407738252256343</v>
+        <v>-3.60801442506658</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.189643048014136</v>
+        <v>1.109532578890041</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6153164640662561</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.321494789229965</v>
+        <v>-3.521770962040203</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.219086703798547</v>
+        <v>1.138976234674452</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6153164640662561</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.366801608628945</v>
+        <v>-3.567077781439183</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.19273975148348</v>
+        <v>1.112629282359385</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5745063010570253</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.395834713331247</v>
+        <v>-3.596110886141485</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.181678382635661</v>
+        <v>1.101567913511566</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5745063010570253</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.303024231880388</v>
+        <v>-3.503300404690625</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.148075267107371</v>
+        <v>1.067964797983276</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6673167825078846</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.347413701209815</v>
+        <v>-3.547689874020053</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.132192955300201</v>
+        <v>1.052082486176105</v>
       </c>
       <c r="F1947" t="n">
         <v>0.622927313178457</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.234742482973565</v>
+        <v>-3.435018655783803</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.172337151106424</v>
+        <v>1.092226681982329</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7355985314147071</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.122365481790892</v>
+        <v>-3.32264165460113</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.22277924741016</v>
+        <v>1.142668778286065</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7355985314147071</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.150145879692245</v>
+        <v>-3.350422052502483</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.223164290018158</v>
+        <v>1.143053820894063</v>
       </c>
       <c r="F1950" t="n">
         <v>0.707818133513354</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.233147160717524</v>
+        <v>-3.433423333527762</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.028319497608699</v>
+        <v>0.9482090284846043</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6892472489861803</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.341761239160856</v>
+        <v>-3.542037411971093</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.105023526950573</v>
+        <v>1.024913057826477</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6892472489861803</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.306352200912713</v>
+        <v>-3.50662837372295</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.133700168352153</v>
+        <v>1.053589699228058</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6892472489861803</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.267968538354562</v>
+        <v>-3.468244711164799</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.146473074717782</v>
+        <v>1.066362605593687</v>
       </c>
       <c r="F1954" t="n">
         <v>0.7276309115443315</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.090852208319395</v>
+        <v>-3.291128381129633</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.21404863557715</v>
+        <v>1.133938166453055</v>
       </c>
       <c r="F1955" t="n">
         <v>0.7276309115443315</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.135944453152941</v>
+        <v>-3.336220625963179</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.196695129405645</v>
+        <v>1.11658466028155</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6657348683749417</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.956569031914174</v>
+        <v>-3.156845204724411</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.262232273207566</v>
+        <v>1.182121804083471</v>
       </c>
       <c r="F1957" t="n">
         <v>0.8225116265456603</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.00158324543478</v>
+        <v>-3.201859418245018</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.225034043130914</v>
+        <v>1.144923574006818</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7921627312310557</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.268587755707215</v>
+        <v>-3.468863928517453</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.123923801360885</v>
+        <v>1.04381333223679</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5977996931881071</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.369785537144388</v>
+        <v>-3.570061709954626</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.082648610682517</v>
+        <v>1.002538141558422</v>
       </c>
       <c r="F1960" t="n">
         <v>0.529390879642788</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.363274570530075</v>
+        <v>-3.563550743340313</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.082852958882559</v>
+        <v>1.002742489758464</v>
       </c>
       <c r="F1961" t="n">
         <v>0.529390879642788</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.344236442822778</v>
+        <v>-3.544512615633016</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.086992929173723</v>
+        <v>1.006882460049628</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4712072683115934</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.375363073973396</v>
+        <v>-3.575639246783634</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.252124145652157</v>
+        <v>1.172013676528061</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4712072683115934</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.389229835307313</v>
+        <v>-3.589506008117551</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.247410770104723</v>
+        <v>1.167300300980628</v>
       </c>
       <c r="F1964" t="n">
         <v>0.4333493515777705</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.344425663767383</v>
+        <v>-3.544701836577621</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.271340969117621</v>
+        <v>1.191230499993526</v>
       </c>
       <c r="F1965" t="n">
         <v>0.4333493515777705</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.196682693532381</v>
+        <v>-3.396958866342619</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.228388378488821</v>
+        <v>1.148277909364726</v>
       </c>
       <c r="F1966" t="n">
         <v>0.6011567088126537</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.298697376063602</v>
+        <v>-3.49897354887384</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.190376127007814</v>
+        <v>1.110265657883719</v>
       </c>
       <c r="F1967" t="n">
         <v>0.6011567088126537</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.292544670010818</v>
+        <v>-3.492820842821056</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.193499557820586</v>
+        <v>1.113389088696491</v>
       </c>
       <c r="F1968" t="n">
         <v>0.607309414865438</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.309353968161319</v>
+        <v>-3.509630140971557</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.185856315300496</v>
+        <v>1.105745846176401</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5905001167149364</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.247055969385197</v>
+        <v>-3.447332142195435</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.277111068607765</v>
+        <v>1.19700059948367</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5905001167149364</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.04526577172004</v>
+        <v>-3.245541944530277</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.160119149387956</v>
+        <v>1.08000868026386</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7885183088840908</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.880452768641192</v>
+        <v>-3.08072894145143</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.29633458294167</v>
+        <v>1.216224113817574</v>
       </c>
       <c r="F1972" t="n">
         <v>0.9533313119629377</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.978193313266167</v>
+        <v>-3.178469486076405</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.271866101207723</v>
+        <v>1.191755632083628</v>
       </c>
       <c r="F1973" t="n">
         <v>0.9374420338299576</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.154531073389096</v>
+        <v>-3.354807246199334</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.199866977983223</v>
+        <v>1.119756508859128</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7611042737070282</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.078109026957169</v>
+        <v>-3.278385199767407</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.228927414595923</v>
+        <v>1.148816945471828</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7611042737070282</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.033735895318601</v>
+        <v>-3.234012068128838</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.246539534686786</v>
+        <v>1.166429065562691</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8054774053455968</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.910901674431433</v>
+        <v>-3.111177847241671</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.290067017180244</v>
+        <v>1.209956548056149</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8054774053455968</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.863245943870377</v>
+        <v>-3.063522116680615</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.315511066432471</v>
+        <v>1.235400597308376</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8531331359066524</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.762727785371623</v>
+        <v>-2.963003958181861</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.360610703206698</v>
+        <v>1.280500234082602</v>
       </c>
       <c r="F1979" t="n">
         <v>0.953651294405407</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.823394375774012</v>
+        <v>-3.02367054858425</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.323098739521614</v>
+        <v>1.242988270397519</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8719529776868733</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.778555974165614</v>
+        <v>-2.978832146975852</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.345131802775602</v>
+        <v>1.265021333651507</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8764964106317428</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.798054430407622</v>
+        <v>-2.99833060321786</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.341493359909877</v>
+        <v>1.261382890785782</v>
       </c>
       <c r="F1982" t="n">
         <v>0.8284117693518385</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.753851593321722</v>
+        <v>-2.954127766131959</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.365054097272074</v>
+        <v>1.284943628147979</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8726146064377389</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.790830620985165</v>
+        <v>-2.991106793795403</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.348672486675944</v>
+        <v>1.268562017551849</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9095885082290694</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.632539203445893</v>
+        <v>-2.83281537625613</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.463236818874693</v>
+        <v>1.383126349750598</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9095885082290694</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.424897199811416</v>
+        <v>-2.625173372621654</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.544734324922736</v>
+        <v>1.464623855798641</v>
       </c>
       <c r="F1986" t="n">
         <v>1.117230511863545</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.373865107088888</v>
+        <v>-2.574141279899126</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.560095390250018</v>
+        <v>1.479984921125923</v>
       </c>
       <c r="F1987" t="n">
         <v>1.168262604586074</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.308640925961683</v>
+        <v>-2.508917098771921</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.603372466793605</v>
+        <v>1.52326199766951</v>
       </c>
       <c r="F1988" t="n">
         <v>1.233486785713279</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.271213905890549</v>
+        <v>-2.471490078700787</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.614304247121339</v>
+        <v>1.534193777997244</v>
       </c>
       <c r="F1989" t="n">
         <v>1.238738323742461</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.291325561925257</v>
+        <v>-2.491601734735495</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.607516377038696</v>
+        <v>1.527405907914601</v>
       </c>
       <c r="F1990" t="n">
         <v>1.24976566873988</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.237580747498053</v>
+        <v>-2.43785692030829</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.789572073830788</v>
+        <v>1.709461604706693</v>
       </c>
       <c r="F1991" t="n">
         <v>1.259828978180342</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.16279848647304</v>
+        <v>-2.363074659283278</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.939597887458611</v>
+        <v>1.859487418334516</v>
       </c>
       <c r="F1992" t="n">
         <v>1.334611239205355</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.136714402209232</v>
+        <v>-2.33699057501947</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.941739497177993</v>
+        <v>1.861629028053898</v>
       </c>
       <c r="F1993" t="n">
         <v>1.334611239205355</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.058583221360285</v>
+        <v>-2.258859394170523</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.971185165101351</v>
+        <v>1.891074695977256</v>
       </c>
       <c r="F1994" t="n">
         <v>1.40878805008904</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.049690759967002</v>
+        <v>-2.24996693277724</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.992296555385455</v>
+        <v>1.91218608626136</v>
       </c>
       <c r="F1995" t="n">
         <v>1.40878805008904</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.21816687693688</v>
+        <v>-2.418443049747118</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.916761156002088</v>
+        <v>1.836650686877993</v>
       </c>
       <c r="F1996" t="n">
         <v>1.380840214372459</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782704</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.520367348075297</v>
+        <v>-1.720643520885535</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.177150664734584</v>
+        <v>2.097040195610488</v>
       </c>
       <c r="F1997" t="n">
         <v>1.310492155002048</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632632</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.497646244392144</v>
+        <v>-1.697922417202382</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.176903128704749</v>
+        <v>2.096792659580654</v>
       </c>
       <c r="F1998" t="n">
         <v>1.310492155002048</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.495921201102101</v>
+        <v>-1.696197373912338</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.336499271871936</v>
+        <v>2.25638880274784</v>
       </c>
       <c r="F1999" t="n">
         <v>1.312217198292092</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.650702207880356</v>
+        <v>-1.850978380690594</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.31166469165428</v>
+        <v>2.231554222530185</v>
       </c>
       <c r="F2000" t="n">
         <v>1.278849524237616</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.643647517665182</v>
+        <v>-1.84392369047542</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.311161923729895</v>
+        <v>2.2310514546058</v>
       </c>
       <c r="F2001" t="n">
         <v>1.285904214452789</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.616696293338694</v>
+        <v>-1.816972466148932</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.331948567105231</v>
+        <v>2.251838097981136</v>
       </c>
       <c r="F2002" t="n">
         <v>1.300784560480509</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784104</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.75264930139501</v>
+        <v>-1.952925474205248</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.461670496027665</v>
+        <v>2.381560026903569</v>
       </c>
       <c r="F2003" t="n">
         <v>1.300784560480509</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.775057419199882</v>
+        <v>-1.97533359201012</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.444823943808709</v>
+        <v>2.364713474684614</v>
       </c>
       <c r="F2004" t="n">
         <v>1.300784560480509</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.923063186679282</v>
+        <v>-2.12333935948952</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.387675636366587</v>
+        <v>2.307565167242491</v>
       </c>
       <c r="F2005" t="n">
         <v>1.214057551616967</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.932504112567811</v>
+        <v>-2.13278028537805</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.440152983733022</v>
+        <v>2.360042514608927</v>
       </c>
       <c r="F2006" t="n">
         <v>1.336484669160359</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.984777719903453</v>
+        <v>-2.185053892713691</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.422134635344066</v>
+        <v>2.342024166219971</v>
       </c>
       <c r="F2007" t="n">
         <v>1.284211061824717</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.061107697504359</v>
+        <v>-2.261383870314597</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.389714457197479</v>
+        <v>2.309603988073384</v>
       </c>
       <c r="F2008" t="n">
         <v>1.284211061824717</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887744</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.17286465011966</v>
+        <v>-2.373140822929898</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.339831905754221</v>
+        <v>2.259721436630126</v>
       </c>
       <c r="F2009" t="n">
         <v>1.172454109209416</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.171023631061408</v>
+        <v>-2.371299803871647</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.339002323587674</v>
+        <v>2.258891854463578</v>
       </c>
       <c r="F2010" t="n">
         <v>1.173722335880885</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647101</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.303324923158962</v>
+        <v>-2.5036010959692</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.299155213614571</v>
+        <v>2.219044744490476</v>
       </c>
       <c r="F2011" t="n">
         <v>1.173722335880885</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763528</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.304886565973821</v>
+        <v>-2.50516273878406</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.298530556488627</v>
+        <v>2.218420087364532</v>
       </c>
       <c r="F2012" t="n">
         <v>1.173722335880885</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392111</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.332787353083294</v>
+        <v>-2.533063525893533</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.28589428277184</v>
+        <v>2.205783813647745</v>
       </c>
       <c r="F2013" t="n">
         <v>1.13912541173795</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172522</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.455313455786188</v>
+        <v>-2.655589628596427</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.233648285667881</v>
+        <v>2.153537816543786</v>
       </c>
       <c r="F2014" t="n">
         <v>1.016599309035056</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971075</v>
+        <v>3.619362241971074</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.475374777062695</v>
+        <v>-2.675650949872934</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.292329716747783</v>
+        <v>2.212219247623687</v>
       </c>
       <c r="F2015" t="n">
         <v>0.996537987758549</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199803</v>
+        <v>3.640764248199801</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.732095595057519</v>
+        <v>-2.932371767867758</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.3299531085517</v>
+        <v>2.249842639427604</v>
       </c>
       <c r="F2016" t="n">
         <v>0.8881234136147341</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622234</v>
+        <v>3.668303164622232</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.88608201283366</v>
+        <v>-3.086358185643898</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.337338810586883</v>
+        <v>2.257228341462788</v>
       </c>
       <c r="F2017" t="n">
         <v>0.8881234136147341</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808525</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.835560109005994</v>
+        <v>-3.035836281816232</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.343598774238071</v>
+        <v>2.263488305113975</v>
       </c>
       <c r="F2018" t="n">
         <v>0.8881234136147341</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.65634689399489</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.088035263013718</v>
+        <v>-3.288311435823957</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.254479201690395</v>
+        <v>2.174368732566299</v>
       </c>
       <c r="F2019" t="n">
         <v>0.8881234136147341</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674042696358294</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.357508064935426</v>
+        <v>-3.557784237745665</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.147900615440655</v>
+        <v>2.06779014631656</v>
       </c>
       <c r="F2020" t="n">
         <v>0.8881234136147341</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637084</v>
+        <v>3.663523617637082</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.515052136664867</v>
+        <v>-3.715328309475106</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.0890047289762</v>
+        <v>2.008894259852105</v>
       </c>
       <c r="F2021" t="n">
         <v>0.8212216084744597</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.652163313301339</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.643902687366914</v>
+        <v>-3.844178860177152</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.032542361431571</v>
+        <v>1.952431892307476</v>
       </c>
       <c r="F2022" t="n">
         <v>0.7802281996237381</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215466</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.760870380005805</v>
+        <v>-3.961146552816043</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.147959341075059</v>
+        <v>2.067848871950964</v>
       </c>
       <c r="F2023" t="n">
         <v>0.7802281996237381</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69655362845669</v>
+        <v>3.696553628456688</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.845588322226758</v>
+        <v>-4.045864495036997</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.108918802150491</v>
+        <v>2.028808333026396</v>
       </c>
       <c r="F2024" t="n">
         <v>0.6951121706956918</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253286</v>
+        <v>3.750058176253284</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.927523140495642</v>
+        <v>-4.12779931330588</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.086374292411429</v>
+        <v>2.006263823287334</v>
       </c>
       <c r="F2025" t="n">
         <v>0.6851774251086116</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78364702771783</v>
+        <v>3.783647027717828</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.87378496709538</v>
+        <v>-4.074061139905618</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.116795200227436</v>
+        <v>2.036684731103341</v>
       </c>
       <c r="F2026" t="n">
         <v>0.7389155985088737</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616946</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.763778683618158</v>
+        <v>-3.964054856428397</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.152950600862501</v>
+        <v>2.072840131738405</v>
       </c>
       <c r="F2027" t="n">
         <v>0.7621201704261489</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78557808520366</v>
+        <v>3.785578085203658</v>
       </c>
       <c r="C2028" t="n">
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.620719107877232</v>
+        <v>-3.820995280687471</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.214424441880845</v>
+        <v>2.13431397275675</v>
       </c>
       <c r="F2028" t="n">
         <v>0.7701335970161282</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436926</v>
+        <v>3.777251572436924</v>
       </c>
       <c r="C2029" t="n">
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.319272382405395</v>
+        <v>-3.519548555215634</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.342264014952116</v>
+        <v>2.262153545828021</v>
       </c>
       <c r="F2029" t="n">
         <v>1.071580322487965</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.857236038816166</v>
+        <v>3.581431254392569</v>
       </c>
       <c r="C2030" t="n">
         <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.371063351883857</v>
+        <v>-3.438845098971391</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.322518804913442</v>
+        <v>2.295406106078428</v>
       </c>
       <c r="F2030" t="n">
         <v>1.071580322487965</v>

--- a/tame_output/ON/bt/strategyON_20240720.xlsx
+++ b/tame_output/ON/bt/strategyON_20240720.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.5%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.4%</t>
+          <t>110.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.7%</t>
+          <t>-68.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.0%</t>
+          <t>452.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-505.5%</t>
+          <t>-519.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-146.7%</t>
+          <t>-152.1%</t>
         </is>
       </c>
     </row>
@@ -48241,10 +48241,10 @@
         <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.438845098971391</v>
+        <v>-3.574503751658703</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.295406106078428</v>
+        <v>2.241142645003503</v>
       </c>
       <c r="F2030" t="n">
         <v>1.071580322487965</v>

--- a/tame_output/ON/bt/strategyON_20240720.xlsx
+++ b/tame_output/ON/bt/strategyON_20240720.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-664.6%</t>
+          <t>-644.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.7%</t>
+          <t>-67.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.7%</t>
+          <t>456.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-519.0%</t>
+          <t>-509.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.2%</t>
+          <t>-258.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-129.2%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.1%</t>
+          <t>-148.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-136.7%</t>
+          <t>-132.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-116.8%</t>
+          <t>-119.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-16.3%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.9216650444977963</v>
+        <v>-0.7213888716875563</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.75230632021386</v>
+        <v>2.832416789337956</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9102758078429949</v>
+        <v>-0.7099996350327549</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.754686810995021</v>
+        <v>2.834797280119117</v>
       </c>
       <c r="F1846" t="n">
         <v>1.405815606229521</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.328029831389832</v>
+        <v>-1.127753658579592</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.585512093081349</v>
+        <v>2.665622562205445</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9880615826826838</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.618161497995263</v>
+        <v>-1.417885325185023</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.469325643038099</v>
+        <v>2.549436112162195</v>
       </c>
       <c r="F1848" t="n">
         <v>1.012143377422864</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.826165556348341</v>
+        <v>-1.625889383538101</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.391016164250793</v>
+        <v>2.471126633374889</v>
       </c>
       <c r="F1849" t="n">
         <v>1.012143377422864</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.888343967509311</v>
+        <v>-1.688067794699071</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.361226256124393</v>
+        <v>2.441336725248489</v>
       </c>
       <c r="F1850" t="n">
         <v>0.9499649662618935</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.254412694653963</v>
+        <v>-2.054136521843724</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.207883064572981</v>
+        <v>2.287993533697077</v>
       </c>
       <c r="F1851" t="n">
         <v>0.5838962391172409</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.462903476105648</v>
+        <v>-2.262627303295408</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.144825041731075</v>
+        <v>2.224935510855171</v>
       </c>
       <c r="F1852" t="n">
         <v>0.3754054576655564</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.710104660870869</v>
+        <v>-2.50982848806063</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.054043318233555</v>
+        <v>2.134153787357651</v>
       </c>
       <c r="F1853" t="n">
         <v>0.3955588111643689</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.202489688894966</v>
+        <v>-3.002213516084727</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.858195699067649</v>
+        <v>1.938306168191745</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.09682621685972786</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.587670079825038</v>
+        <v>-3.387393907014799</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.702666081508483</v>
+        <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.09682621685972786</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.83754075983962</v>
+        <v>-3.637264587029381</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.604486932957267</v>
+        <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.06056349702926461</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.044052536726641</v>
+        <v>-3.843776363916402</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.517988280858716</v>
+        <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.2670752739162861</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.363396611807143</v>
+        <v>-4.163120438996904</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.392023577526775</v>
+        <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.2670752739162861</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.79520240495693</v>
+        <v>-4.594926232146691</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.205634147734264</v>
+        <v>1.28574461685836</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4034927703575531</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.029896399089482</v>
+        <v>-4.829620226279244</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.100041325083334</v>
+        <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.3971565031282979</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.365559046319935</v>
+        <v>-5.165282873509696</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9643568578471182</v>
+        <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.4650874886172027</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.442003376522806</v>
+        <v>-5.241727203712568</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9402666860002111</v>
+        <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.3846419795235408</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.807130759161553</v>
+        <v>-5.606854586351314</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7934702479505438</v>
+        <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.6809527638225534</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.215719536342232</v>
+        <v>-6.015443363531993</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.628796281093031</v>
+        <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.089541541003232</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.329479948365097</v>
+        <v>-6.129203775554858</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.578477548755346</v>
+        <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.089541541003232</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.745871822652094</v>
+        <v>-6.545595649841855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4099148496494243</v>
+        <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.089541541003232</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.990143223379164</v>
+        <v>-6.789867050568925</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.3224649800272754</v>
+        <v>0.4025754491513713</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.089541541003232</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.195394242615924</v>
+        <v>-6.995118069805685</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2364641374782663</v>
+        <v>0.3165746066023623</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.089541541003232</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.243597059858268</v>
+        <v>-7.043320887048029</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.21558793063633</v>
+        <v>0.2956983997604259</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.089541541003232</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.540258401668465</v>
+        <v>-7.339982228858227</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1007023698414593</v>
+        <v>0.1808128389655548</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.15828467673711</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.726978109977768</v>
+        <v>-7.526701937167529</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.02198818198333496</v>
+        <v>0.1020986511074309</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.15828467673711</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.109979498720399</v>
+        <v>-7.909703325910161</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.1313144748353015</v>
+        <v>-0.05120400571120598</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.15828467673711</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.114465943921788</v>
+        <v>-7.914189771111549</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1305375369444266</v>
+        <v>-0.05042706782033113</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.162771121938499</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.47399626642579</v>
+        <v>-8.273720093615552</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.268999362647977</v>
+        <v>-0.1888888935238819</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.162771121938499</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.524345329880012</v>
+        <v>-8.324069157069774</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2812229680724885</v>
+        <v>-0.2011124989483934</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.213120185392721</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.621964607301408</v>
+        <v>-8.42168843449117</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.317228928419278</v>
+        <v>-0.2371184592951829</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.310739462814118</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.676036106809766</v>
+        <v>-8.475759933999528</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3359639719010494</v>
+        <v>-0.255853502776954</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.364810962322477</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.88029428213963</v>
+        <v>-8.680018109329392</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.4121540449143524</v>
+        <v>-0.3320435757902573</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.492449906936466</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.913947120648103</v>
+        <v>-8.713670947837866</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4211326258333057</v>
+        <v>-0.3410221567092107</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.592863274853503</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.840477288980654</v>
+        <v>-8.640201116170417</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3763729916729051</v>
+        <v>-0.29626252254881</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.519393443186055</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.015601706367198</v>
+        <v>-8.81532553355696</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4318675378800054</v>
+        <v>-0.3517570687559104</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.694517860572599</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.250053800381687</v>
+        <v>-9.04977762757145</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5328675403873975</v>
+        <v>-0.4527570712633024</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.694517860572599</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.354428531408134</v>
+        <v>-9.154152358597896</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5812896235719522</v>
+        <v>-0.5011791544478572</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.798892591599045</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.407214687008461</v>
+        <v>-9.206938514198223</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6012882959735264</v>
+        <v>-0.5211778268494314</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.894568078181442</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.53325148037675</v>
+        <v>-9.332975307566512</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6490092846917275</v>
+        <v>-0.5688988155676324</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.869316455371699</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.476179708480819</v>
+        <v>-9.275903535670581</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6221902402469546</v>
+        <v>-0.5420797711228591</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.869316455371699</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.617851550204939</v>
+        <v>-9.417575377394702</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6803342038353444</v>
+        <v>-0.6002237347112489</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.869316455371699</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.568260705780105</v>
+        <v>-9.367984532969867</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6454444559005381</v>
+        <v>-0.5653339867764431</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.819725610946866</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.419342371308248</v>
+        <v>-9.219066198498011</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5989282557584787</v>
+        <v>-0.5188177866343833</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.788476020211692</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.193497218588838</v>
+        <v>-8.993221045778601</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4990111216345059</v>
+        <v>-0.4189006525104109</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.746549344624529</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.068918562251246</v>
+        <v>-8.868642389441009</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4480405145434103</v>
+        <v>-0.3679300454193153</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.746549344624529</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.121813850295533</v>
+        <v>-8.921537677485295</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4665648555990174</v>
+        <v>-0.3864543864749219</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.741593998536083</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.049680675007652</v>
+        <v>-8.849404502197414</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4319778812452282</v>
+        <v>-0.3518674121211331</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.741593998536083</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.978314282398005</v>
+        <v>-8.778038109587767</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4131685865952344</v>
+        <v>-0.3330581174711393</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.670227605926435</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.88485524841278</v>
+        <v>-8.684579075602542</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3856684543140525</v>
+        <v>-0.305557985189957</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.670227605926435</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.617613447544382</v>
+        <v>-8.417337274734145</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2806062944660668</v>
+        <v>-0.2004958253419717</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.670227605926435</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.519706408867892</v>
+        <v>-8.319430236057654</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2417437939689315</v>
+        <v>-0.1616333248448365</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.602241856065878</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.495752867891934</v>
+        <v>-8.295476695081696</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2314938714330546</v>
+        <v>-0.1513834023089595</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.578288315089921</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.231692929569137</v>
+        <v>-8.031416756758899</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1391302122656883</v>
+        <v>-0.05901974314159286</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.314228376767125</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.524613306064299</v>
+        <v>-7.324337133254061</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1409146034759461</v>
+        <v>0.2210250726000416</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.314228376767125</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.484429007698108</v>
+        <v>-7.284152834887871</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1573319467102636</v>
+        <v>0.2374424158343591</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.274044078400934</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.321029136758746</v>
+        <v>-7.120752963948508</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2220587163067655</v>
+        <v>0.302169185430861</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.110644207461571</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.087547914529147</v>
+        <v>-6.88727174171891</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3233756340364575</v>
+        <v>0.4034861031605526</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8771629852319727</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.937881523521632</v>
+        <v>-6.737605350711394</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3803499801265042</v>
+        <v>0.4604604492505997</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7842594939894367</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.805606049890746</v>
+        <v>-6.605329877080508</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4286276563258862</v>
+        <v>0.5087381254499812</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.6519840203585501</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.649867717331004</v>
+        <v>-6.449591544520766</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4937380500374196</v>
+        <v>0.5738485191615146</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4962456877988085</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.400867918647423</v>
+        <v>-6.200591745837185</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6062443107345108</v>
+        <v>0.6863547798586058</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.4962456877988085</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.506457908420527</v>
+        <v>-6.30618173561029</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4360323852260501</v>
+        <v>0.5161428543501452</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.6018356775719129</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.525192810539124</v>
+        <v>-6.324916637728887</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4770827662556978</v>
+        <v>0.5571932353797928</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.6074316872320442</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.377252769131525</v>
+        <v>-6.176976596321287</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4163798601305699</v>
+        <v>0.496490329254665</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.5871107713234867</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.324283246877537</v>
+        <v>-6.124007074067299</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4288536827786871</v>
+        <v>0.5089641519027821</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.5341412490694978</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.280734840106846</v>
+        <v>-6.080458667296608</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4393124333918701</v>
+        <v>0.5194229025159651</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.5341412490694978</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.247371633628077</v>
+        <v>-6.04709546081784</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4671200703645209</v>
+        <v>0.5472305394886159</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.5341412490694978</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.139112496505556</v>
+        <v>-5.938836323695318</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5049558456727246</v>
+        <v>0.5850663147968196</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.5341412490694978</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.015821361688425</v>
+        <v>-5.815545188878187</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5517703936101537</v>
+        <v>0.6318808627342487</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.4108501142523673</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.994672162784981</v>
+        <v>-5.794395989974744</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.567931051408856</v>
+        <v>0.6480415205329515</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.3897009153489239</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.750906720801537</v>
+        <v>-5.550630547991299</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6612179365492845</v>
+        <v>0.7413284056733795</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.3897009153489239</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.649143900524242</v>
+        <v>-5.448867727714005</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7040473785802184</v>
+        <v>0.7841578477043138</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.3764818469564952</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.399293506575168</v>
+        <v>-5.19901733376493</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7967296111435505</v>
+        <v>0.8768400802676455</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.3764818469564952</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.223401414107736</v>
+        <v>-5.023125241297498</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8706855716511721</v>
+        <v>0.9507960407752671</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.3764818469564952</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.051954951085272</v>
+        <v>-4.851678778275034</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9525916629147111</v>
+        <v>1.032702132038806</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.2050353839340321</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.977665385346933</v>
+        <v>-4.777389212536695</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9813279668263437</v>
+        <v>1.061438435950439</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.1307458181956928</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.914029643112999</v>
+        <v>-4.713753470302761</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.011477064774235</v>
+        <v>1.09158753389833</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.06711007596175828</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.802602883787078</v>
+        <v>-4.602326710976841</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.037242027288399</v>
+        <v>1.117352496412494</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.06711007596175828</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.562172386982218</v>
+        <v>-4.36189621417198</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.13515730263522</v>
+        <v>1.215267771759315</v>
       </c>
       <c r="F1925" t="n">
         <v>0.173320420843102</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.489929818811023</v>
+        <v>-4.289653646000786</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.167983643738518</v>
+        <v>1.248094112862613</v>
       </c>
       <c r="F1926" t="n">
         <v>0.173320420843102</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.436931496529636</v>
+        <v>-4.236655323719398</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.189861556568413</v>
+        <v>1.269972025692508</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2286566798450408</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.328126611049909</v>
+        <v>-4.127850438239671</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.230381581980298</v>
+        <v>1.310492051104393</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2286566798450408</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.108105813012898</v>
+        <v>-3.90782964020266</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.319968938205716</v>
+        <v>1.400079407329811</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3698765249130211</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.97523812394962</v>
+        <v>-3.774961951139382</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.389010196632851</v>
+        <v>1.469120665756946</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3698765249130211</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.855065040585121</v>
+        <v>-3.654788867774883</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.438225274418952</v>
+        <v>1.518335743543047</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4900496082775201</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.710392895485383</v>
+        <v>-3.510116722675146</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.506182235020287</v>
+        <v>1.586292704144382</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6347217533772576</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.770267722843076</v>
+        <v>-3.569991550032838</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.468269795478636</v>
+        <v>1.548380264602731</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5748469260195654</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.650447491932238</v>
+        <v>-3.450171319122</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.531487057077179</v>
+        <v>1.611597526201274</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5748469260195654</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.652917198394044</v>
+        <v>-3.452641025583806</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.438143373814898</v>
+        <v>1.518253842938994</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5723772195577592</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.721287384718054</v>
+        <v>-3.521011211907816</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.330057160770596</v>
+        <v>1.410167629894691</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5816529185939742</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.735075437565101</v>
+        <v>-3.534799264754863</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.314978648263669</v>
+        <v>1.395089117387764</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5816529185939742</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.766068596893806</v>
+        <v>-3.565792424083568</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.127290949572573</v>
+        <v>1.207401418696668</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5816529185939742</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.590594337101337</v>
+        <v>-3.390318164291099</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.202047885481349</v>
+        <v>1.282158354605444</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5816529185939742</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.701530589742585</v>
+        <v>-3.501254416932348</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.133415413186056</v>
+        <v>1.213525882310151</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5816529185939742</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.667867044270304</v>
+        <v>-3.467590871460066</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.075419144776419</v>
+        <v>1.155529613900514</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6153164640662561</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.60801442506658</v>
+        <v>-3.407738252256343</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.109532578890041</v>
+        <v>1.189643048014136</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6153164640662561</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.521770962040203</v>
+        <v>-3.321494789229965</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.138976234674452</v>
+        <v>1.219086703798547</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6153164640662561</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.567077781439183</v>
+        <v>-3.366801608628945</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.112629282359385</v>
+        <v>1.19273975148348</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5745063010570253</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.596110886141485</v>
+        <v>-3.395834713331247</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.101567913511566</v>
+        <v>1.181678382635661</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5745063010570253</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.503300404690625</v>
+        <v>-3.303024231880388</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.067964797983276</v>
+        <v>1.148075267107371</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6673167825078846</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.547689874020053</v>
+        <v>-3.347413701209815</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.052082486176105</v>
+        <v>1.132192955300201</v>
       </c>
       <c r="F1947" t="n">
         <v>0.622927313178457</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.435018655783803</v>
+        <v>-3.234742482973565</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.092226681982329</v>
+        <v>1.172337151106424</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7355985314147071</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.32264165460113</v>
+        <v>-3.122365481790892</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.142668778286065</v>
+        <v>1.22277924741016</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7355985314147071</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.350422052502483</v>
+        <v>-3.150145879692245</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.143053820894063</v>
+        <v>1.223164290018158</v>
       </c>
       <c r="F1950" t="n">
         <v>0.707818133513354</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.433423333527762</v>
+        <v>-3.233147160717524</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9482090284846043</v>
+        <v>1.028319497608699</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6892472489861803</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.542037411971093</v>
+        <v>-3.341761239160856</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.024913057826477</v>
+        <v>1.105023526950573</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6892472489861803</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.50662837372295</v>
+        <v>-3.306352200912713</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.053589699228058</v>
+        <v>1.133700168352153</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6892472489861803</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.468244711164799</v>
+        <v>-3.267968538354562</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.066362605593687</v>
+        <v>1.146473074717782</v>
       </c>
       <c r="F1954" t="n">
         <v>0.7276309115443315</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.291128381129633</v>
+        <v>-3.090852208319395</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.133938166453055</v>
+        <v>1.21404863557715</v>
       </c>
       <c r="F1955" t="n">
         <v>0.7276309115443315</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.336220625963179</v>
+        <v>-3.135944453152941</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.11658466028155</v>
+        <v>1.196695129405645</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6657348683749417</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.156845204724411</v>
+        <v>-2.956569031914174</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.182121804083471</v>
+        <v>1.262232273207566</v>
       </c>
       <c r="F1957" t="n">
         <v>0.8225116265456603</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.201859418245018</v>
+        <v>-3.00158324543478</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.144923574006818</v>
+        <v>1.225034043130914</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7921627312310557</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.468863928517453</v>
+        <v>-3.268587755707215</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.04381333223679</v>
+        <v>1.123923801360885</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5977996931881071</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.570061709954626</v>
+        <v>-3.369785537144388</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.002538141558422</v>
+        <v>1.082648610682517</v>
       </c>
       <c r="F1960" t="n">
         <v>0.529390879642788</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.563550743340313</v>
+        <v>-3.363274570530075</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.002742489758464</v>
+        <v>1.082852958882559</v>
       </c>
       <c r="F1961" t="n">
         <v>0.529390879642788</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.544512615633016</v>
+        <v>-3.344236442822778</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.006882460049628</v>
+        <v>1.086992929173723</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4712072683115934</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.575639246783634</v>
+        <v>-3.375363073973396</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.172013676528061</v>
+        <v>1.252124145652157</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4712072683115934</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.589506008117551</v>
+        <v>-3.389229835307313</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.167300300980628</v>
+        <v>1.247410770104723</v>
       </c>
       <c r="F1964" t="n">
         <v>0.4333493515777705</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.544701836577621</v>
+        <v>-3.344425663767383</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.191230499993526</v>
+        <v>1.271340969117621</v>
       </c>
       <c r="F1965" t="n">
         <v>0.4333493515777705</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.396958866342619</v>
+        <v>-3.196682693532381</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.148277909364726</v>
+        <v>1.228388378488821</v>
       </c>
       <c r="F1966" t="n">
         <v>0.6011567088126537</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.49897354887384</v>
+        <v>-3.298697376063602</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.110265657883719</v>
+        <v>1.190376127007814</v>
       </c>
       <c r="F1967" t="n">
         <v>0.6011567088126537</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.492820842821056</v>
+        <v>-3.292544670010818</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.113389088696491</v>
+        <v>1.193499557820586</v>
       </c>
       <c r="F1968" t="n">
         <v>0.607309414865438</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.509630140971557</v>
+        <v>-3.309353968161319</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.105745846176401</v>
+        <v>1.185856315300496</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5905001167149364</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.447332142195435</v>
+        <v>-3.247055969385197</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.19700059948367</v>
+        <v>1.277111068607765</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5905001167149364</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.245541944530277</v>
+        <v>-3.04526577172004</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.08000868026386</v>
+        <v>1.160119149387956</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7885183088840908</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.08072894145143</v>
+        <v>-2.880452768641192</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.216224113817574</v>
+        <v>1.29633458294167</v>
       </c>
       <c r="F1972" t="n">
         <v>0.9533313119629377</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.178469486076405</v>
+        <v>-2.978193313266167</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.191755632083628</v>
+        <v>1.271866101207723</v>
       </c>
       <c r="F1973" t="n">
         <v>0.9374420338299576</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.354807246199334</v>
+        <v>-3.154531073389096</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.119756508859128</v>
+        <v>1.199866977983223</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7611042737070282</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.278385199767407</v>
+        <v>-3.078109026957169</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.148816945471828</v>
+        <v>1.228927414595923</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7611042737070282</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.234012068128838</v>
+        <v>-3.033735895318601</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.166429065562691</v>
+        <v>1.246539534686786</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8054774053455968</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.111177847241671</v>
+        <v>-2.910901674431433</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.209956548056149</v>
+        <v>1.290067017180244</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8054774053455968</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.063522116680615</v>
+        <v>-2.863245943870377</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.235400597308376</v>
+        <v>1.315511066432471</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8531331359066524</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.963003958181861</v>
+        <v>-2.762727785371623</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.280500234082602</v>
+        <v>1.360610703206698</v>
       </c>
       <c r="F1979" t="n">
         <v>0.953651294405407</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.02367054858425</v>
+        <v>-2.823394375774012</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.242988270397519</v>
+        <v>1.323098739521614</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8719529776868733</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.978832146975852</v>
+        <v>-2.778555974165614</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.265021333651507</v>
+        <v>1.345131802775602</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8764964106317428</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.99833060321786</v>
+        <v>-2.798054430407622</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.261382890785782</v>
+        <v>1.341493359909877</v>
       </c>
       <c r="F1982" t="n">
         <v>0.8284117693518385</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.954127766131959</v>
+        <v>-2.753851593321722</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.284943628147979</v>
+        <v>1.365054097272074</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8726146064377389</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.991106793795403</v>
+        <v>-2.790830620985165</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.268562017551849</v>
+        <v>1.348672486675944</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9095885082290694</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.83281537625613</v>
+        <v>-2.632539203445893</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.383126349750598</v>
+        <v>1.463236818874693</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9095885082290694</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.625173372621654</v>
+        <v>-2.424897199811416</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.464623855798641</v>
+        <v>1.544734324922736</v>
       </c>
       <c r="F1986" t="n">
         <v>1.117230511863545</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.574141279899126</v>
+        <v>-2.373865107088888</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.479984921125923</v>
+        <v>1.560095390250018</v>
       </c>
       <c r="F1987" t="n">
         <v>1.168262604586074</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.508917098771921</v>
+        <v>-2.308640925961683</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.52326199766951</v>
+        <v>1.603372466793605</v>
       </c>
       <c r="F1988" t="n">
         <v>1.233486785713279</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.471490078700787</v>
+        <v>-2.271213905890549</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.534193777997244</v>
+        <v>1.614304247121339</v>
       </c>
       <c r="F1989" t="n">
         <v>1.238738323742461</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.491601734735495</v>
+        <v>-2.291325561925257</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.527405907914601</v>
+        <v>1.607516377038696</v>
       </c>
       <c r="F1990" t="n">
         <v>1.24976566873988</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.43785692030829</v>
+        <v>-2.237580747498053</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.709461604706693</v>
+        <v>1.789572073830788</v>
       </c>
       <c r="F1991" t="n">
         <v>1.259828978180342</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.363074659283278</v>
+        <v>-2.16279848647304</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.859487418334516</v>
+        <v>1.939597887458611</v>
       </c>
       <c r="F1992" t="n">
         <v>1.334611239205355</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.33699057501947</v>
+        <v>-2.136714402209232</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.861629028053898</v>
+        <v>1.941739497177993</v>
       </c>
       <c r="F1993" t="n">
         <v>1.334611239205355</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.258859394170523</v>
+        <v>-2.058583221360285</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.891074695977256</v>
+        <v>1.971185165101351</v>
       </c>
       <c r="F1994" t="n">
         <v>1.40878805008904</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959853</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.24996693277724</v>
+        <v>-2.049690759967002</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.91218608626136</v>
+        <v>1.992296555385455</v>
       </c>
       <c r="F1995" t="n">
         <v>1.40878805008904</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.418443049747118</v>
+        <v>-2.21816687693688</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.836650686877993</v>
+        <v>1.916761156002088</v>
       </c>
       <c r="F1996" t="n">
         <v>1.380840214372459</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782704</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.720643520885535</v>
+        <v>-1.520367348075297</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.097040195610488</v>
+        <v>2.177150664734584</v>
       </c>
       <c r="F1997" t="n">
         <v>1.310492155002048</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632632</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.697922417202382</v>
+        <v>-1.497646244392144</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.096792659580654</v>
+        <v>2.176903128704749</v>
       </c>
       <c r="F1998" t="n">
         <v>1.310492155002048</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.696197373912338</v>
+        <v>-1.495921201102101</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.25638880274784</v>
+        <v>2.336499271871936</v>
       </c>
       <c r="F1999" t="n">
         <v>1.312217198292092</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.850978380690594</v>
+        <v>-1.650702207880356</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.231554222530185</v>
+        <v>2.31166469165428</v>
       </c>
       <c r="F2000" t="n">
         <v>1.278849524237616</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.84392369047542</v>
+        <v>-1.643647517665182</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.2310514546058</v>
+        <v>2.311161923729895</v>
       </c>
       <c r="F2001" t="n">
         <v>1.285904214452789</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.816972466148932</v>
+        <v>-1.616696293338694</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.251838097981136</v>
+        <v>2.331948567105231</v>
       </c>
       <c r="F2002" t="n">
         <v>1.300784560480509</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784104</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.952925474205248</v>
+        <v>-1.75264930139501</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.381560026903569</v>
+        <v>2.461670496027665</v>
       </c>
       <c r="F2003" t="n">
         <v>1.300784560480509</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.97533359201012</v>
+        <v>-1.775057419199882</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.364713474684614</v>
+        <v>2.444823943808709</v>
       </c>
       <c r="F2004" t="n">
         <v>1.300784560480509</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.12333935948952</v>
+        <v>-1.923063186679282</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.307565167242491</v>
+        <v>2.387675636366587</v>
       </c>
       <c r="F2005" t="n">
         <v>1.214057551616967</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.13278028537805</v>
+        <v>-1.932504112567811</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.360042514608927</v>
+        <v>2.440152983733022</v>
       </c>
       <c r="F2006" t="n">
         <v>1.336484669160359</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.185053892713691</v>
+        <v>-1.984777719903453</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.342024166219971</v>
+        <v>2.422134635344066</v>
       </c>
       <c r="F2007" t="n">
         <v>1.284211061824717</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.261383870314597</v>
+        <v>-2.061107697504359</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.309603988073384</v>
+        <v>2.389714457197479</v>
       </c>
       <c r="F2008" t="n">
         <v>1.284211061824717</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887744</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.373140822929898</v>
+        <v>-2.17286465011966</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.259721436630126</v>
+        <v>2.339831905754221</v>
       </c>
       <c r="F2009" t="n">
         <v>1.172454109209416</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.371299803871647</v>
+        <v>-2.171023631061408</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.258891854463578</v>
+        <v>2.339002323587674</v>
       </c>
       <c r="F2010" t="n">
         <v>1.173722335880885</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647101</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.5036010959692</v>
+        <v>-2.303324923158962</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.219044744490476</v>
+        <v>2.299155213614571</v>
       </c>
       <c r="F2011" t="n">
         <v>1.173722335880885</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763528</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.50516273878406</v>
+        <v>-2.304886565973821</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.218420087364532</v>
+        <v>2.298530556488627</v>
       </c>
       <c r="F2012" t="n">
         <v>1.173722335880885</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392111</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.533063525893533</v>
+        <v>-2.332787353083294</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.205783813647745</v>
+        <v>2.28589428277184</v>
       </c>
       <c r="F2013" t="n">
         <v>1.13912541173795</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172522</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.655589628596427</v>
+        <v>-2.455313455786188</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.153537816543786</v>
+        <v>2.233648285667881</v>
       </c>
       <c r="F2014" t="n">
         <v>1.016599309035056</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971074</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.675650949872934</v>
+        <v>-2.475374777062695</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.212219247623687</v>
+        <v>2.292329716747783</v>
       </c>
       <c r="F2015" t="n">
         <v>0.996537987758549</v>
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199801</v>
+        <v>3.640764248199803</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.932371767867758</v>
+        <v>-2.838655399166138</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.249842639427604</v>
+        <v>2.287329186908252</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8881234136147341</v>
+        <v>0.8605332425646113</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.956021819057296</v>
+        <v>3.939467716427222</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622232</v>
+        <v>3.668303164622234</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.086358185643898</v>
+        <v>-2.992641816942279</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.257228341462788</v>
+        <v>2.294714888943436</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8881234136147341</v>
+        <v>0.8605332425646113</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.025002088202935</v>
+        <v>4.008447985572861</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808525</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.035836281816232</v>
+        <v>-2.942119913114613</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.263488305113975</v>
+        <v>2.300974852594623</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8881234136147341</v>
+        <v>0.8605332425646113</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.011053290323056</v>
+        <v>3.994499187692982</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.65634689399489</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.288311435823957</v>
+        <v>-3.194595067122338</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.174368732566299</v>
+        <v>2.211855280046947</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8881234136147341</v>
+        <v>0.8605332425646113</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.02292377937847</v>
+        <v>4.006369676748396</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358294</v>
+        <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.557784237745665</v>
+        <v>-3.464067869044046</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.06779014631656</v>
+        <v>2.105276693797207</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8881234136147341</v>
+        <v>0.8605332425646113</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.024134313897414</v>
+        <v>4.00758021126734</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637082</v>
+        <v>3.663523617637084</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.715328309475106</v>
+        <v>-3.621611940773487</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.008894259852105</v>
+        <v>2.046380807332752</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.8212216084744597</v>
+        <v>0.7936314374243367</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.98811497304057</v>
+        <v>3.971560870410497</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301339</v>
+        <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.844178860177152</v>
+        <v>-3.750462491475533</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.952431892307476</v>
+        <v>1.989918439788123</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7802281996237381</v>
+        <v>0.7526380285736152</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.958596780466327</v>
+        <v>3.942042677836254</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215466</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.961146552816043</v>
+        <v>-3.867430184114424</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.067848871950964</v>
+        <v>2.105335419431611</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7802281996237381</v>
+        <v>0.7526380285736152</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.120800837165371</v>
+        <v>4.104246734535297</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456688</v>
+        <v>3.69655362845669</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.045864495036997</v>
+        <v>-3.952148126335378</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.028808333026396</v>
+        <v>2.066294880507043</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6951121706956918</v>
+        <v>0.6675219996455688</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.064577857772357</v>
+        <v>4.048023755142284</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253284</v>
+        <v>3.750058176253286</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.12779931330588</v>
+        <v>-4.034082944604261</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.006263823287334</v>
+        <v>2.043750370767981</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.6851774251086116</v>
+        <v>0.6575872540584886</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.068846427988601</v>
+        <v>4.052292325358526</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717828</v>
+        <v>3.78364702771783</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.074061139905618</v>
+        <v>-3.980344771203999</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.036684731103341</v>
+        <v>2.074171278583989</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.7389155985088737</v>
+        <v>0.7113254274587507</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.11001497048466</v>
+        <v>4.093460867854587</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.798310944616946</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.964054856428397</v>
+        <v>-3.870338487726777</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.072840131738405</v>
+        <v>2.110326679219053</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.7621201704261489</v>
+        <v>0.7345299993760259</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.1160906008792</v>
+        <v>4.099536498249127</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203658</v>
+        <v>3.78557808520366</v>
       </c>
       <c r="C2028" t="n">
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.820995280687471</v>
+        <v>-3.727278911985852</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.13431397275675</v>
+        <v>2.171800520237397</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.7701335970161282</v>
+        <v>0.7425434259660052</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.125148667555163</v>
+        <v>4.108594564925089</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436924</v>
+        <v>3.777251572436926</v>
       </c>
       <c r="C2029" t="n">
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.519548555215634</v>
+        <v>-3.425832186514015</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.262153545828021</v>
+        <v>2.299640093308668</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.071580322487965</v>
+        <v>1.043990151437842</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.313277585720801</v>
+        <v>4.296723483090727</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.581431254392569</v>
+        <v>3.758409284237583</v>
       </c>
       <c r="C2030" t="n">
         <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.574503751658703</v>
+        <v>-3.480787382957084</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.241142645003503</v>
+        <v>2.278629192484151</v>
       </c>
       <c r="F2030" t="n">
-        <v>1.071580322487965</v>
+        <v>1.043990151437842</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.314248763473511</v>
+        <v>4.297694660843438</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240720.xlsx
+++ b/tame_output/ON/bt/strategyON_20240720.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>41.1%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-73.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-644.5%</t>
+          <t>-664.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.8%</t>
+          <t>-68.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.8%</t>
+          <t>452.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-509.7%</t>
+          <t>-519.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-258.2%</t>
+          <t>-266.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-36.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-129.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-148.4%</t>
+          <t>-152.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-132.3%</t>
+          <t>-136.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-119.6%</t>
+          <t>-116.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-94.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2030"/>
+  <dimension ref="A1:G2031"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7213888716875563</v>
+        <v>-0.9216650444977963</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.832416789337956</v>
+        <v>2.75230632021386</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7099996350327549</v>
+        <v>-0.9102758078429949</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.834797280119117</v>
+        <v>2.754686810995021</v>
       </c>
       <c r="F1846" t="n">
         <v>1.405815606229521</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.127753658579592</v>
+        <v>-1.328029831389832</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.665622562205445</v>
+        <v>2.585512093081349</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9880615826826838</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.417885325185023</v>
+        <v>-1.618161497995263</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.549436112162195</v>
+        <v>2.469325643038099</v>
       </c>
       <c r="F1848" t="n">
         <v>1.012143377422864</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.625889383538101</v>
+        <v>-1.826165556348341</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.471126633374889</v>
+        <v>2.391016164250793</v>
       </c>
       <c r="F1849" t="n">
         <v>1.012143377422864</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.688067794699071</v>
+        <v>-1.888343967509311</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.441336725248489</v>
+        <v>2.361226256124393</v>
       </c>
       <c r="F1850" t="n">
         <v>0.9499649662618935</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.054136521843724</v>
+        <v>-2.254412694653963</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.287993533697077</v>
+        <v>2.207883064572981</v>
       </c>
       <c r="F1851" t="n">
         <v>0.5838962391172409</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.262627303295408</v>
+        <v>-2.462903476105648</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.224935510855171</v>
+        <v>2.144825041731075</v>
       </c>
       <c r="F1852" t="n">
         <v>0.3754054576655564</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.50982848806063</v>
+        <v>-2.710104660870869</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.134153787357651</v>
+        <v>2.054043318233555</v>
       </c>
       <c r="F1853" t="n">
         <v>0.3955588111643689</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.002213516084727</v>
+        <v>-3.202489688894966</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.938306168191745</v>
+        <v>1.858195699067649</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.09682621685972786</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.387393907014799</v>
+        <v>-3.587670079825038</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.782776550632579</v>
+        <v>1.702666081508483</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.09682621685972786</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.637264587029381</v>
+        <v>-3.83754075983962</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.684597402081363</v>
+        <v>1.604486932957267</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.06056349702926461</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.843776363916402</v>
+        <v>-4.044052536726641</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.598098749982812</v>
+        <v>1.517988280858716</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.2670752739162861</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.163120438996904</v>
+        <v>-4.363396611807143</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.472134046650871</v>
+        <v>1.392023577526775</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.2670752739162861</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.594926232146691</v>
+        <v>-4.79520240495693</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.28574461685836</v>
+        <v>1.205634147734264</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4034927703575531</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.829620226279244</v>
+        <v>-5.029896399089482</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.18015179420743</v>
+        <v>1.100041325083334</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.3971565031282979</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.165282873509696</v>
+        <v>-5.365559046319935</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.044467326971214</v>
+        <v>0.9643568578471182</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.4650874886172027</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.241727203712568</v>
+        <v>-5.442003376522806</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.020377155124307</v>
+        <v>0.9402666860002111</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.3846419795235408</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.606854586351314</v>
+        <v>-5.807130759161553</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8735807170746397</v>
+        <v>0.7934702479505438</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.6809527638225534</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.015443363531993</v>
+        <v>-6.215719536342232</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7089067502171269</v>
+        <v>0.628796281093031</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.089541541003232</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.129203775554858</v>
+        <v>-6.329479948365097</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6585880178794419</v>
+        <v>0.578477548755346</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.089541541003232</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.545595649841855</v>
+        <v>-6.745871822652094</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4900253187735202</v>
+        <v>0.4099148496494243</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.089541541003232</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.789867050568925</v>
+        <v>-6.990143223379164</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4025754491513713</v>
+        <v>0.3224649800272754</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.089541541003232</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.995118069805685</v>
+        <v>-7.195394242615924</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3165746066023623</v>
+        <v>0.2364641374782663</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.089541541003232</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.043320887048029</v>
+        <v>-7.243597059858268</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2956983997604259</v>
+        <v>0.21558793063633</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.089541541003232</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.339982228858227</v>
+        <v>-7.540258401668465</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1808128389655548</v>
+        <v>0.1007023698414593</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.15828467673711</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.526701937167529</v>
+        <v>-7.726978109977768</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1020986511074309</v>
+        <v>0.02198818198333496</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.15828467673711</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.909703325910161</v>
+        <v>-8.109979498720399</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.05120400571120598</v>
+        <v>-0.1313144748353015</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.15828467673711</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.914189771111549</v>
+        <v>-8.114465943921788</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05042706782033113</v>
+        <v>-0.1305375369444266</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.162771121938499</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.273720093615552</v>
+        <v>-8.47399626642579</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1888888935238819</v>
+        <v>-0.268999362647977</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.162771121938499</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.324069157069774</v>
+        <v>-8.524345329880012</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2011124989483934</v>
+        <v>-0.2812229680724885</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.213120185392721</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.42168843449117</v>
+        <v>-8.621964607301408</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2371184592951829</v>
+        <v>-0.317228928419278</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.310739462814118</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.475759933999528</v>
+        <v>-8.676036106809766</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.255853502776954</v>
+        <v>-0.3359639719010494</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.364810962322477</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.680018109329392</v>
+        <v>-8.88029428213963</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3320435757902573</v>
+        <v>-0.4121540449143524</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.492449906936466</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.713670947837866</v>
+        <v>-8.913947120648103</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3410221567092107</v>
+        <v>-0.4211326258333057</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.592863274853503</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.640201116170417</v>
+        <v>-8.840477288980654</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.29626252254881</v>
+        <v>-0.3763729916729051</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.519393443186055</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.81532553355696</v>
+        <v>-9.015601706367198</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3517570687559104</v>
+        <v>-0.4318675378800054</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.694517860572599</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.04977762757145</v>
+        <v>-9.250053800381687</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4527570712633024</v>
+        <v>-0.5328675403873975</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.694517860572599</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.154152358597896</v>
+        <v>-9.354428531408134</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5011791544478572</v>
+        <v>-0.5812896235719522</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.798892591599045</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.206938514198223</v>
+        <v>-9.407214687008461</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5211778268494314</v>
+        <v>-0.6012882959735264</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.894568078181442</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.332975307566512</v>
+        <v>-9.53325148037675</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5688988155676324</v>
+        <v>-0.6490092846917275</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.869316455371699</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.275903535670581</v>
+        <v>-9.476179708480819</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5420797711228591</v>
+        <v>-0.6221902402469546</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.869316455371699</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.417575377394702</v>
+        <v>-9.617851550204939</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6002237347112489</v>
+        <v>-0.6803342038353444</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.869316455371699</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.367984532969867</v>
+        <v>-9.568260705780105</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5653339867764431</v>
+        <v>-0.6454444559005381</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.819725610946866</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.219066198498011</v>
+        <v>-9.419342371308248</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5188177866343833</v>
+        <v>-0.5989282557584787</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.788476020211692</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.993221045778601</v>
+        <v>-9.193497218588838</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4189006525104109</v>
+        <v>-0.4990111216345059</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.746549344624529</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.868642389441009</v>
+        <v>-9.068918562251246</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3679300454193153</v>
+        <v>-0.4480405145434103</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.746549344624529</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.921537677485295</v>
+        <v>-9.121813850295533</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3864543864749219</v>
+        <v>-0.4665648555990174</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.741593998536083</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.849404502197414</v>
+        <v>-9.049680675007652</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3518674121211331</v>
+        <v>-0.4319778812452282</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.741593998536083</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.778038109587767</v>
+        <v>-8.978314282398005</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3330581174711393</v>
+        <v>-0.4131685865952344</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.670227605926435</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.684579075602542</v>
+        <v>-8.88485524841278</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.305557985189957</v>
+        <v>-0.3856684543140525</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.670227605926435</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.417337274734145</v>
+        <v>-8.617613447544382</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2004958253419717</v>
+        <v>-0.2806062944660668</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.670227605926435</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.319430236057654</v>
+        <v>-8.519706408867892</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1616333248448365</v>
+        <v>-0.2417437939689315</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.602241856065878</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.295476695081696</v>
+        <v>-8.495752867891934</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1513834023089595</v>
+        <v>-0.2314938714330546</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.578288315089921</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.031416756758899</v>
+        <v>-8.231692929569137</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05901974314159286</v>
+        <v>-0.1391302122656883</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.314228376767125</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.324337133254061</v>
+        <v>-7.524613306064299</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2210250726000416</v>
+        <v>0.1409146034759461</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.314228376767125</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.284152834887871</v>
+        <v>-7.484429007698108</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2374424158343591</v>
+        <v>0.1573319467102636</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.274044078400934</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.120752963948508</v>
+        <v>-7.321029136758746</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.302169185430861</v>
+        <v>0.2220587163067655</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.110644207461571</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.88727174171891</v>
+        <v>-7.087547914529147</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4034861031605526</v>
+        <v>0.3233756340364575</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8771629852319727</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.737605350711394</v>
+        <v>-6.937881523521632</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4604604492505997</v>
+        <v>0.3803499801265042</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7842594939894367</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.605329877080508</v>
+        <v>-6.805606049890746</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5087381254499812</v>
+        <v>0.4286276563258862</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.6519840203585501</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.449591544520766</v>
+        <v>-6.649867717331004</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5738485191615146</v>
+        <v>0.4937380500374196</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4962456877988085</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.200591745837185</v>
+        <v>-6.400867918647423</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6863547798586058</v>
+        <v>0.6062443107345108</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.4962456877988085</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.30618173561029</v>
+        <v>-6.506457908420527</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5161428543501452</v>
+        <v>0.4360323852260501</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.6018356775719129</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.324916637728887</v>
+        <v>-6.525192810539124</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5571932353797928</v>
+        <v>0.4770827662556978</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.6074316872320442</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.176976596321287</v>
+        <v>-6.377252769131525</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.496490329254665</v>
+        <v>0.4163798601305699</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.5871107713234867</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.124007074067299</v>
+        <v>-6.324283246877537</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5089641519027821</v>
+        <v>0.4288536827786871</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.5341412490694978</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.080458667296608</v>
+        <v>-6.280734840106846</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5194229025159651</v>
+        <v>0.4393124333918701</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.5341412490694978</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.04709546081784</v>
+        <v>-6.247371633628077</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5472305394886159</v>
+        <v>0.4671200703645209</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.5341412490694978</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.938836323695318</v>
+        <v>-6.139112496505556</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5850663147968196</v>
+        <v>0.5049558456727246</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.5341412490694978</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.815545188878187</v>
+        <v>-6.015821361688425</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6318808627342487</v>
+        <v>0.5517703936101537</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.4108501142523673</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.794395989974744</v>
+        <v>-5.994672162784981</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6480415205329515</v>
+        <v>0.567931051408856</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.3897009153489239</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.550630547991299</v>
+        <v>-5.750906720801537</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7413284056733795</v>
+        <v>0.6612179365492845</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.3897009153489239</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.448867727714005</v>
+        <v>-5.649143900524242</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7841578477043138</v>
+        <v>0.7040473785802184</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.3764818469564952</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.19901733376493</v>
+        <v>-5.399293506575168</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8768400802676455</v>
+        <v>0.7967296111435505</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.3764818469564952</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.023125241297498</v>
+        <v>-5.223401414107736</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9507960407752671</v>
+        <v>0.8706855716511721</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.3764818469564952</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.851678778275034</v>
+        <v>-5.051954951085272</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.032702132038806</v>
+        <v>0.9525916629147111</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.2050353839340321</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.777389212536695</v>
+        <v>-4.977665385346933</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.061438435950439</v>
+        <v>0.9813279668263437</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.1307458181956928</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.713753470302761</v>
+        <v>-4.914029643112999</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.09158753389833</v>
+        <v>1.011477064774235</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.06711007596175828</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.602326710976841</v>
+        <v>-4.802602883787078</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.117352496412494</v>
+        <v>1.037242027288399</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.06711007596175828</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.36189621417198</v>
+        <v>-4.562172386982218</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.215267771759315</v>
+        <v>1.13515730263522</v>
       </c>
       <c r="F1925" t="n">
         <v>0.173320420843102</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.289653646000786</v>
+        <v>-4.489929818811023</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.248094112862613</v>
+        <v>1.167983643738518</v>
       </c>
       <c r="F1926" t="n">
         <v>0.173320420843102</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.236655323719398</v>
+        <v>-4.436931496529636</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.269972025692508</v>
+        <v>1.189861556568413</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2286566798450408</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.127850438239671</v>
+        <v>-4.328126611049909</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.310492051104393</v>
+        <v>1.230381581980298</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2286566798450408</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.90782964020266</v>
+        <v>-4.108105813012898</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.400079407329811</v>
+        <v>1.319968938205716</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3698765249130211</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.774961951139382</v>
+        <v>-3.97523812394962</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.469120665756946</v>
+        <v>1.389010196632851</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3698765249130211</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.654788867774883</v>
+        <v>-3.855065040585121</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.518335743543047</v>
+        <v>1.438225274418952</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4900496082775201</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.510116722675146</v>
+        <v>-3.710392895485383</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.586292704144382</v>
+        <v>1.506182235020287</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6347217533772576</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.569991550032838</v>
+        <v>-3.770267722843076</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.548380264602731</v>
+        <v>1.468269795478636</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5748469260195654</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.450171319122</v>
+        <v>-3.650447491932238</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.611597526201274</v>
+        <v>1.531487057077179</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5748469260195654</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.452641025583806</v>
+        <v>-3.652917198394044</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.518253842938994</v>
+        <v>1.438143373814898</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5723772195577592</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.521011211907816</v>
+        <v>-3.721287384718054</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.410167629894691</v>
+        <v>1.330057160770596</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5816529185939742</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.534799264754863</v>
+        <v>-3.735075437565101</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.395089117387764</v>
+        <v>1.314978648263669</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5816529185939742</v>
@@ -46125,10 +46125,10 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.565792424083568</v>
+        <v>-3.766068596893806</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.207401418696668</v>
+        <v>1.127290949572573</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5816529185939742</v>
@@ -46148,10 +46148,10 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.390318164291099</v>
+        <v>-3.590594337101337</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.282158354605444</v>
+        <v>1.202047885481349</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5816529185939742</v>
@@ -46171,10 +46171,10 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.501254416932348</v>
+        <v>-3.701530589742585</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.213525882310151</v>
+        <v>1.133415413186056</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5816529185939742</v>
@@ -46194,10 +46194,10 @@
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.467590871460066</v>
+        <v>-3.667867044270304</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.155529613900514</v>
+        <v>1.075419144776419</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6153164640662561</v>
@@ -46217,10 +46217,10 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.407738252256343</v>
+        <v>-3.60801442506658</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.189643048014136</v>
+        <v>1.109532578890041</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6153164640662561</v>
@@ -46240,10 +46240,10 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.321494789229965</v>
+        <v>-3.521770962040203</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.219086703798547</v>
+        <v>1.138976234674452</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6153164640662561</v>
@@ -46263,10 +46263,10 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.366801608628945</v>
+        <v>-3.567077781439183</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.19273975148348</v>
+        <v>1.112629282359385</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5745063010570253</v>
@@ -46286,10 +46286,10 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.395834713331247</v>
+        <v>-3.596110886141485</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.181678382635661</v>
+        <v>1.101567913511566</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5745063010570253</v>
@@ -46309,10 +46309,10 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.303024231880388</v>
+        <v>-3.503300404690625</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.148075267107371</v>
+        <v>1.067964797983276</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6673167825078846</v>
@@ -46332,10 +46332,10 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.347413701209815</v>
+        <v>-3.547689874020053</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.132192955300201</v>
+        <v>1.052082486176105</v>
       </c>
       <c r="F1947" t="n">
         <v>0.622927313178457</v>
@@ -46355,10 +46355,10 @@
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.234742482973565</v>
+        <v>-3.435018655783803</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.172337151106424</v>
+        <v>1.092226681982329</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7355985314147071</v>
@@ -46378,10 +46378,10 @@
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.122365481790892</v>
+        <v>-3.32264165460113</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.22277924741016</v>
+        <v>1.142668778286065</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7355985314147071</v>
@@ -46401,10 +46401,10 @@
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.150145879692245</v>
+        <v>-3.350422052502483</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.223164290018158</v>
+        <v>1.143053820894063</v>
       </c>
       <c r="F1950" t="n">
         <v>0.707818133513354</v>
@@ -46424,10 +46424,10 @@
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.233147160717524</v>
+        <v>-3.433423333527762</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.028319497608699</v>
+        <v>0.9482090284846043</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6892472489861803</v>
@@ -46447,10 +46447,10 @@
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.341761239160856</v>
+        <v>-3.542037411971093</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.105023526950573</v>
+        <v>1.024913057826477</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6892472489861803</v>
@@ -46470,10 +46470,10 @@
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.306352200912713</v>
+        <v>-3.50662837372295</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.133700168352153</v>
+        <v>1.053589699228058</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6892472489861803</v>
@@ -46493,10 +46493,10 @@
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.267968538354562</v>
+        <v>-3.468244711164799</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.146473074717782</v>
+        <v>1.066362605593687</v>
       </c>
       <c r="F1954" t="n">
         <v>0.7276309115443315</v>
@@ -46516,10 +46516,10 @@
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.090852208319395</v>
+        <v>-3.291128381129633</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.21404863557715</v>
+        <v>1.133938166453055</v>
       </c>
       <c r="F1955" t="n">
         <v>0.7276309115443315</v>
@@ -46539,10 +46539,10 @@
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.135944453152941</v>
+        <v>-3.336220625963179</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.196695129405645</v>
+        <v>1.11658466028155</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6657348683749417</v>
@@ -46562,10 +46562,10 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.956569031914174</v>
+        <v>-3.156845204724411</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.262232273207566</v>
+        <v>1.182121804083471</v>
       </c>
       <c r="F1957" t="n">
         <v>0.8225116265456603</v>
@@ -46585,10 +46585,10 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.00158324543478</v>
+        <v>-3.201859418245018</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.225034043130914</v>
+        <v>1.144923574006818</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7921627312310557</v>
@@ -46608,10 +46608,10 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.268587755707215</v>
+        <v>-3.468863928517453</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.123923801360885</v>
+        <v>1.04381333223679</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5977996931881071</v>
@@ -46631,10 +46631,10 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.369785537144388</v>
+        <v>-3.570061709954626</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.082648610682517</v>
+        <v>1.002538141558422</v>
       </c>
       <c r="F1960" t="n">
         <v>0.529390879642788</v>
@@ -46654,10 +46654,10 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.363274570530075</v>
+        <v>-3.563550743340313</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.082852958882559</v>
+        <v>1.002742489758464</v>
       </c>
       <c r="F1961" t="n">
         <v>0.529390879642788</v>
@@ -46677,10 +46677,10 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.344236442822778</v>
+        <v>-3.544512615633016</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.086992929173723</v>
+        <v>1.006882460049628</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4712072683115934</v>
@@ -46700,10 +46700,10 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.375363073973396</v>
+        <v>-3.575639246783634</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.252124145652157</v>
+        <v>1.172013676528061</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4712072683115934</v>
@@ -46723,10 +46723,10 @@
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.389229835307313</v>
+        <v>-3.589506008117551</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.247410770104723</v>
+        <v>1.167300300980628</v>
       </c>
       <c r="F1964" t="n">
         <v>0.4333493515777705</v>
@@ -46746,10 +46746,10 @@
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.344425663767383</v>
+        <v>-3.544701836577621</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.271340969117621</v>
+        <v>1.191230499993526</v>
       </c>
       <c r="F1965" t="n">
         <v>0.4333493515777705</v>
@@ -46769,10 +46769,10 @@
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.196682693532381</v>
+        <v>-3.396958866342619</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.228388378488821</v>
+        <v>1.148277909364726</v>
       </c>
       <c r="F1966" t="n">
         <v>0.6011567088126537</v>
@@ -46792,10 +46792,10 @@
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.298697376063602</v>
+        <v>-3.49897354887384</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.190376127007814</v>
+        <v>1.110265657883719</v>
       </c>
       <c r="F1967" t="n">
         <v>0.6011567088126537</v>
@@ -46815,10 +46815,10 @@
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.292544670010818</v>
+        <v>-3.492820842821056</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.193499557820586</v>
+        <v>1.113389088696491</v>
       </c>
       <c r="F1968" t="n">
         <v>0.607309414865438</v>
@@ -46838,10 +46838,10 @@
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.309353968161319</v>
+        <v>-3.509630140971557</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.185856315300496</v>
+        <v>1.105745846176401</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5905001167149364</v>
@@ -46861,10 +46861,10 @@
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.247055969385197</v>
+        <v>-3.447332142195435</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.277111068607765</v>
+        <v>1.19700059948367</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5905001167149364</v>
@@ -46884,10 +46884,10 @@
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.04526577172004</v>
+        <v>-3.245541944530277</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.160119149387956</v>
+        <v>1.08000868026386</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7885183088840908</v>
@@ -46907,10 +46907,10 @@
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.880452768641192</v>
+        <v>-3.08072894145143</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.29633458294167</v>
+        <v>1.216224113817574</v>
       </c>
       <c r="F1972" t="n">
         <v>0.9533313119629377</v>
@@ -46930,10 +46930,10 @@
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.978193313266167</v>
+        <v>-3.178469486076405</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.271866101207723</v>
+        <v>1.191755632083628</v>
       </c>
       <c r="F1973" t="n">
         <v>0.9374420338299576</v>
@@ -46953,10 +46953,10 @@
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.154531073389096</v>
+        <v>-3.354807246199334</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.199866977983223</v>
+        <v>1.119756508859128</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7611042737070282</v>
@@ -46976,10 +46976,10 @@
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.078109026957169</v>
+        <v>-3.278385199767407</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.228927414595923</v>
+        <v>1.148816945471828</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7611042737070282</v>
@@ -46999,10 +46999,10 @@
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.033735895318601</v>
+        <v>-3.234012068128838</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.246539534686786</v>
+        <v>1.166429065562691</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8054774053455968</v>
@@ -47022,10 +47022,10 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.910901674431433</v>
+        <v>-3.111177847241671</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.290067017180244</v>
+        <v>1.209956548056149</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8054774053455968</v>
@@ -47045,10 +47045,10 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.863245943870377</v>
+        <v>-3.063522116680615</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.315511066432471</v>
+        <v>1.235400597308376</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8531331359066524</v>
@@ -47068,10 +47068,10 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.762727785371623</v>
+        <v>-2.963003958181861</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.360610703206698</v>
+        <v>1.280500234082602</v>
       </c>
       <c r="F1979" t="n">
         <v>0.953651294405407</v>
@@ -47091,10 +47091,10 @@
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.823394375774012</v>
+        <v>-3.02367054858425</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.323098739521614</v>
+        <v>1.242988270397519</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8719529776868733</v>
@@ -47114,10 +47114,10 @@
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.778555974165614</v>
+        <v>-2.978832146975852</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.345131802775602</v>
+        <v>1.265021333651507</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8764964106317428</v>
@@ -47137,10 +47137,10 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.798054430407622</v>
+        <v>-2.99833060321786</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.341493359909877</v>
+        <v>1.261382890785782</v>
       </c>
       <c r="F1982" t="n">
         <v>0.8284117693518385</v>
@@ -47160,10 +47160,10 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.753851593321722</v>
+        <v>-2.954127766131959</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.365054097272074</v>
+        <v>1.284943628147979</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8726146064377389</v>
@@ -47183,10 +47183,10 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.790830620985165</v>
+        <v>-2.991106793795403</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.348672486675944</v>
+        <v>1.268562017551849</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9095885082290694</v>
@@ -47206,10 +47206,10 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.632539203445893</v>
+        <v>-2.83281537625613</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.463236818874693</v>
+        <v>1.383126349750598</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9095885082290694</v>
@@ -47229,10 +47229,10 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.424897199811416</v>
+        <v>-2.625173372621654</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.544734324922736</v>
+        <v>1.464623855798641</v>
       </c>
       <c r="F1986" t="n">
         <v>1.117230511863545</v>
@@ -47252,10 +47252,10 @@
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.373865107088888</v>
+        <v>-2.574141279899126</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.560095390250018</v>
+        <v>1.479984921125923</v>
       </c>
       <c r="F1987" t="n">
         <v>1.168262604586074</v>
@@ -47275,10 +47275,10 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.308640925961683</v>
+        <v>-2.508917098771921</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.603372466793605</v>
+        <v>1.52326199766951</v>
       </c>
       <c r="F1988" t="n">
         <v>1.233486785713279</v>
@@ -47298,10 +47298,10 @@
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.271213905890549</v>
+        <v>-2.471490078700787</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.614304247121339</v>
+        <v>1.534193777997244</v>
       </c>
       <c r="F1989" t="n">
         <v>1.238738323742461</v>
@@ -47321,10 +47321,10 @@
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.291325561925257</v>
+        <v>-2.491601734735495</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.607516377038696</v>
+        <v>1.527405907914601</v>
       </c>
       <c r="F1990" t="n">
         <v>1.24976566873988</v>
@@ -47344,10 +47344,10 @@
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.237580747498053</v>
+        <v>-2.43785692030829</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.789572073830788</v>
+        <v>1.709461604706693</v>
       </c>
       <c r="F1991" t="n">
         <v>1.259828978180342</v>
@@ -47367,10 +47367,10 @@
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.16279848647304</v>
+        <v>-2.363074659283278</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.939597887458611</v>
+        <v>1.859487418334516</v>
       </c>
       <c r="F1992" t="n">
         <v>1.334611239205355</v>
@@ -47390,10 +47390,10 @@
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.136714402209232</v>
+        <v>-2.33699057501947</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.941739497177993</v>
+        <v>1.861629028053898</v>
       </c>
       <c r="F1993" t="n">
         <v>1.334611239205355</v>
@@ -47413,10 +47413,10 @@
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.058583221360285</v>
+        <v>-2.258859394170523</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.971185165101351</v>
+        <v>1.891074695977256</v>
       </c>
       <c r="F1994" t="n">
         <v>1.40878805008904</v>
@@ -47436,10 +47436,10 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.049690759967002</v>
+        <v>-2.24996693277724</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.992296555385455</v>
+        <v>1.91218608626136</v>
       </c>
       <c r="F1995" t="n">
         <v>1.40878805008904</v>
@@ -47459,10 +47459,10 @@
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.21816687693688</v>
+        <v>-2.418443049747118</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.916761156002088</v>
+        <v>1.836650686877993</v>
       </c>
       <c r="F1996" t="n">
         <v>1.380840214372459</v>
@@ -47482,10 +47482,10 @@
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.520367348075297</v>
+        <v>-1.720643520885535</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.177150664734584</v>
+        <v>2.097040195610488</v>
       </c>
       <c r="F1997" t="n">
         <v>1.310492155002048</v>
@@ -47505,10 +47505,10 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.497646244392144</v>
+        <v>-1.697922417202382</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.176903128704749</v>
+        <v>2.096792659580654</v>
       </c>
       <c r="F1998" t="n">
         <v>1.310492155002048</v>
@@ -47528,10 +47528,10 @@
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.495921201102101</v>
+        <v>-1.696197373912338</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.336499271871936</v>
+        <v>2.25638880274784</v>
       </c>
       <c r="F1999" t="n">
         <v>1.312217198292092</v>
@@ -47551,10 +47551,10 @@
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.650702207880356</v>
+        <v>-1.850978380690594</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.31166469165428</v>
+        <v>2.231554222530185</v>
       </c>
       <c r="F2000" t="n">
         <v>1.278849524237616</v>
@@ -47574,10 +47574,10 @@
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.643647517665182</v>
+        <v>-1.84392369047542</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.311161923729895</v>
+        <v>2.2310514546058</v>
       </c>
       <c r="F2001" t="n">
         <v>1.285904214452789</v>
@@ -47597,10 +47597,10 @@
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.616696293338694</v>
+        <v>-1.816972466148932</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.331948567105231</v>
+        <v>2.251838097981136</v>
       </c>
       <c r="F2002" t="n">
         <v>1.300784560480509</v>
@@ -47620,10 +47620,10 @@
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.75264930139501</v>
+        <v>-1.952925474205248</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.461670496027665</v>
+        <v>2.381560026903569</v>
       </c>
       <c r="F2003" t="n">
         <v>1.300784560480509</v>
@@ -47643,10 +47643,10 @@
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.775057419199882</v>
+        <v>-1.97533359201012</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.444823943808709</v>
+        <v>2.364713474684614</v>
       </c>
       <c r="F2004" t="n">
         <v>1.300784560480509</v>
@@ -47666,10 +47666,10 @@
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.923063186679282</v>
+        <v>-2.12333935948952</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.387675636366587</v>
+        <v>2.307565167242491</v>
       </c>
       <c r="F2005" t="n">
         <v>1.214057551616967</v>
@@ -47689,10 +47689,10 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.932504112567811</v>
+        <v>-2.13278028537805</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.440152983733022</v>
+        <v>2.360042514608927</v>
       </c>
       <c r="F2006" t="n">
         <v>1.336484669160359</v>
@@ -47712,10 +47712,10 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.984777719903453</v>
+        <v>-2.185053892713691</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.422134635344066</v>
+        <v>2.342024166219971</v>
       </c>
       <c r="F2007" t="n">
         <v>1.284211061824717</v>
@@ -47735,10 +47735,10 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.061107697504359</v>
+        <v>-2.261383870314597</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.389714457197479</v>
+        <v>2.309603988073384</v>
       </c>
       <c r="F2008" t="n">
         <v>1.284211061824717</v>
@@ -47758,10 +47758,10 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.17286465011966</v>
+        <v>-2.373140822929898</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.339831905754221</v>
+        <v>2.259721436630126</v>
       </c>
       <c r="F2009" t="n">
         <v>1.172454109209416</v>
@@ -47781,10 +47781,10 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.171023631061408</v>
+        <v>-2.371299803871647</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.339002323587674</v>
+        <v>2.258891854463578</v>
       </c>
       <c r="F2010" t="n">
         <v>1.173722335880885</v>
@@ -47804,10 +47804,10 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.303324923158962</v>
+        <v>-2.5036010959692</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.299155213614571</v>
+        <v>2.219044744490476</v>
       </c>
       <c r="F2011" t="n">
         <v>1.173722335880885</v>
@@ -47827,10 +47827,10 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.304886565973821</v>
+        <v>-2.50516273878406</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.298530556488627</v>
+        <v>2.218420087364532</v>
       </c>
       <c r="F2012" t="n">
         <v>1.173722335880885</v>
@@ -47850,10 +47850,10 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.332787353083294</v>
+        <v>-2.533063525893533</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.28589428277184</v>
+        <v>2.205783813647745</v>
       </c>
       <c r="F2013" t="n">
         <v>1.13912541173795</v>
@@ -47873,10 +47873,10 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.455313455786188</v>
+        <v>-2.655589628596427</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.233648285667881</v>
+        <v>2.153537816543786</v>
       </c>
       <c r="F2014" t="n">
         <v>1.016599309035056</v>
@@ -47896,10 +47896,10 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.475374777062695</v>
+        <v>-2.675650949872934</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.292329716747783</v>
+        <v>2.212219247623687</v>
       </c>
       <c r="F2015" t="n">
         <v>0.996537987758549</v>
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.838655399166138</v>
+        <v>-2.932371767867758</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.287329186908252</v>
+        <v>2.249842639427604</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8605332425646113</v>
+        <v>0.8881234136147341</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.939467716427222</v>
+        <v>3.956021819057296</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.992641816942279</v>
+        <v>-3.086358185643898</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.294714888943436</v>
+        <v>2.257228341462788</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8605332425646113</v>
+        <v>0.8881234136147341</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.008447985572861</v>
+        <v>4.025002088202935</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.942119913114613</v>
+        <v>-3.035836281816232</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.300974852594623</v>
+        <v>2.263488305113975</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8605332425646113</v>
+        <v>0.8881234136147341</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.994499187692982</v>
+        <v>4.011053290323056</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.194595067122338</v>
+        <v>-3.288311435823957</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.211855280046947</v>
+        <v>2.174368732566299</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8605332425646113</v>
+        <v>0.8881234136147341</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.006369676748396</v>
+        <v>4.02292377937847</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.464067869044046</v>
+        <v>-3.557784237745665</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.105276693797207</v>
+        <v>2.06779014631656</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8605332425646113</v>
+        <v>0.8881234136147341</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.00758021126734</v>
+        <v>4.024134313897414</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.621611940773487</v>
+        <v>-3.715328309475106</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.046380807332752</v>
+        <v>2.008894259852105</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7936314374243367</v>
+        <v>0.8212216084744597</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.971560870410497</v>
+        <v>3.98811497304057</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.750462491475533</v>
+        <v>-3.844178860177152</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.989918439788123</v>
+        <v>1.952431892307476</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7526380285736152</v>
+        <v>0.7802281996237381</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.942042677836254</v>
+        <v>3.958596780466327</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.867430184114424</v>
+        <v>-3.961146552816043</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.105335419431611</v>
+        <v>2.067848871950964</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7526380285736152</v>
+        <v>0.7802281996237381</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.104246734535297</v>
+        <v>4.120800837165371</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.952148126335378</v>
+        <v>-4.045864495036997</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.066294880507043</v>
+        <v>2.028808333026396</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6675219996455688</v>
+        <v>0.6951121706956918</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.048023755142284</v>
+        <v>4.064577857772357</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.034082944604261</v>
+        <v>-4.12779931330588</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.043750370767981</v>
+        <v>2.006263823287334</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.6575872540584886</v>
+        <v>0.6851774251086116</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.052292325358526</v>
+        <v>4.068846427988601</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.980344771203999</v>
+        <v>-4.074061139905618</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.074171278583989</v>
+        <v>2.036684731103341</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.7113254274587507</v>
+        <v>0.7389155985088737</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.093460867854587</v>
+        <v>4.11001497048466</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.870338487726777</v>
+        <v>-3.964054856428397</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.110326679219053</v>
+        <v>2.072840131738405</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.7345299993760259</v>
+        <v>0.7621201704261489</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.099536498249127</v>
+        <v>4.1160906008792</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.727278911985852</v>
+        <v>-3.820995280687471</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.171800520237397</v>
+        <v>2.13431397275675</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.7425434259660052</v>
+        <v>0.7701335970161282</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.108594564925089</v>
+        <v>4.125148667555163</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.425832186514015</v>
+        <v>-3.519548555215634</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.299640093308668</v>
+        <v>2.262153545828021</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.043990151437842</v>
+        <v>1.071580322487965</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.296723483090727</v>
+        <v>4.313277585720801</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,45 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.758409284237583</v>
+        <v>3.812650101064758</v>
       </c>
       <c r="C2030" t="n">
         <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.480787382957084</v>
+        <v>-3.574503751658703</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.278629192484151</v>
+        <v>2.241142645003503</v>
       </c>
       <c r="F2030" t="n">
-        <v>1.043990151437842</v>
+        <v>1.071580322487965</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.297694660843438</v>
+        <v>4.314248763473511</v>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" s="2" t="n">
+        <v>45493</v>
+      </c>
+      <c r="B2031" t="n">
+        <v>3.589336236616242</v>
+      </c>
+      <c r="C2031" t="n">
+        <v>3.527558354233377</v>
+      </c>
+      <c r="D2031" t="n">
+        <v>-3.574503751658703</v>
+      </c>
+      <c r="E2031" t="n">
+        <v>2.241142645003503</v>
+      </c>
+      <c r="F2031" t="n">
+        <v>1.071580322487965</v>
+      </c>
+      <c r="G2031" t="n">
+        <v>3.520622151219745</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240720.xlsx
+++ b/tame_output/ON/bt/strategyON_20240720.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>17.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>32.7%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.1%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-664.6%</t>
+          <t>-644.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.6%</t>
+          <t>-69.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.8%</t>
+          <t>454.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-519.0%</t>
+          <t>-530.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.2%</t>
+          <t>-258.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.5%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-129.2%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-152.1%</t>
+          <t>-156.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-136.7%</t>
+          <t>-136.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-116.8%</t>
+          <t>-119.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>83.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1471,37 +1471,37 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-94.0%</t>
+          <t>-102.4%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.9216650444977963</v>
+        <v>-0.7213888716875563</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.75230632021386</v>
+        <v>2.832416789337956</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201484</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9102758078429949</v>
+        <v>-0.7099996350327549</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.754686810995021</v>
+        <v>2.834797280119117</v>
       </c>
       <c r="F1846" t="n">
         <v>1.405815606229521</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153003</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.328029831389832</v>
+        <v>-1.127753658579592</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.585512093081349</v>
+        <v>2.665622562205445</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9880615826826838</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537423</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.618161497995263</v>
+        <v>-1.417885325185023</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.469325643038099</v>
+        <v>2.549436112162195</v>
       </c>
       <c r="F1848" t="n">
         <v>1.012143377422864</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382188</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.826165556348341</v>
+        <v>-1.625889383538101</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.391016164250793</v>
+        <v>2.471126633374889</v>
       </c>
       <c r="F1849" t="n">
         <v>1.012143377422864</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074618</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.888343967509311</v>
+        <v>-1.688067794699071</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.361226256124393</v>
+        <v>2.441336725248489</v>
       </c>
       <c r="F1850" t="n">
         <v>0.9499649662618935</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911636</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.254412694653963</v>
+        <v>-2.054136521843724</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.207883064572981</v>
+        <v>2.287993533697077</v>
       </c>
       <c r="F1851" t="n">
         <v>0.5838962391172409</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.462903476105648</v>
+        <v>-2.262627303295408</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.144825041731075</v>
+        <v>2.224935510855171</v>
       </c>
       <c r="F1852" t="n">
         <v>0.3754054576655564</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416042</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.710104660870869</v>
+        <v>-2.50982848806063</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.054043318233555</v>
+        <v>2.134153787357651</v>
       </c>
       <c r="F1853" t="n">
         <v>0.3955588111643689</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382325</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.202489688894966</v>
+        <v>-3.002213516084727</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.858195699067649</v>
+        <v>1.938306168191745</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.09682621685972786</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495495</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.587670079825038</v>
+        <v>-3.387393907014799</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.702666081508483</v>
+        <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.09682621685972786</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347051</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.83754075983962</v>
+        <v>-3.637264587029381</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.604486932957267</v>
+        <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.06056349702926461</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130013</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.044052536726641</v>
+        <v>-3.843776363916402</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.517988280858716</v>
+        <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.2670752739162861</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.363396611807143</v>
+        <v>-4.163120438996904</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.392023577526775</v>
+        <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.2670752739162861</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.79520240495693</v>
+        <v>-4.594926232146691</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.205634147734264</v>
+        <v>1.28574461685836</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4034927703575531</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.029896399089482</v>
+        <v>-4.829620226279244</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.100041325083334</v>
+        <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.3971565031282979</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.365559046319935</v>
+        <v>-5.165282873509696</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9643568578471182</v>
+        <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.4650874886172027</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.442003376522806</v>
+        <v>-5.241727203712568</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9402666860002111</v>
+        <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.3846419795235408</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.807130759161553</v>
+        <v>-5.606854586351314</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7934702479505438</v>
+        <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.6809527638225534</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.215719536342232</v>
+        <v>-6.015443363531993</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.628796281093031</v>
+        <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.089541541003232</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.329479948365097</v>
+        <v>-6.129203775554858</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.578477548755346</v>
+        <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.089541541003232</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.745871822652094</v>
+        <v>-6.545595649841855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4099148496494243</v>
+        <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.089541541003232</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.990143223379164</v>
+        <v>-6.789867050568925</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.3224649800272754</v>
+        <v>0.4025754491513713</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.089541541003232</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.195394242615924</v>
+        <v>-6.995118069805685</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2364641374782663</v>
+        <v>0.3165746066023623</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.089541541003232</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.243597059858268</v>
+        <v>-7.043320887048029</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.21558793063633</v>
+        <v>0.2956983997604259</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.089541541003232</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.540258401668465</v>
+        <v>-7.339982228858227</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1007023698414593</v>
+        <v>0.1808128389655548</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.15828467673711</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.726978109977768</v>
+        <v>-7.526701937167529</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.02198818198333496</v>
+        <v>0.1020986511074309</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.15828467673711</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.109979498720399</v>
+        <v>-7.909703325910161</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.1313144748353015</v>
+        <v>-0.05120400571120598</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.15828467673711</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.114465943921788</v>
+        <v>-7.914189771111549</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1305375369444266</v>
+        <v>-0.05042706782033113</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.162771121938499</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.47399626642579</v>
+        <v>-8.273720093615552</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.268999362647977</v>
+        <v>-0.1888888935238819</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.162771121938499</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.524345329880012</v>
+        <v>-8.324069157069774</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2812229680724885</v>
+        <v>-0.2011124989483934</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.213120185392721</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.621964607301408</v>
+        <v>-8.42168843449117</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.317228928419278</v>
+        <v>-0.2371184592951829</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.310739462814118</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.676036106809766</v>
+        <v>-8.475759933999528</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3359639719010494</v>
+        <v>-0.255853502776954</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.364810962322477</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.88029428213963</v>
+        <v>-8.680018109329392</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.4121540449143524</v>
+        <v>-0.3320435757902573</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.492449906936466</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.913947120648103</v>
+        <v>-8.713670947837866</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4211326258333057</v>
+        <v>-0.3410221567092107</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.592863274853503</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.840477288980654</v>
+        <v>-8.640201116170417</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3763729916729051</v>
+        <v>-0.29626252254881</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.519393443186055</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.015601706367198</v>
+        <v>-8.81532553355696</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4318675378800054</v>
+        <v>-0.3517570687559104</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.694517860572599</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.250053800381687</v>
+        <v>-9.04977762757145</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5328675403873975</v>
+        <v>-0.4527570712633024</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.694517860572599</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.354428531408134</v>
+        <v>-9.154152358597896</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5812896235719522</v>
+        <v>-0.5011791544478572</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.798892591599045</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.407214687008461</v>
+        <v>-9.206938514198223</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6012882959735264</v>
+        <v>-0.5211778268494314</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.894568078181442</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.53325148037675</v>
+        <v>-9.332975307566512</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6490092846917275</v>
+        <v>-0.5688988155676324</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.869316455371699</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.476179708480819</v>
+        <v>-9.275903535670581</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6221902402469546</v>
+        <v>-0.5420797711228591</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.869316455371699</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.617851550204939</v>
+        <v>-9.417575377394702</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6803342038353444</v>
+        <v>-0.6002237347112489</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.869316455371699</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.568260705780105</v>
+        <v>-9.367984532969867</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6454444559005381</v>
+        <v>-0.5653339867764431</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.819725610946866</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.419342371308248</v>
+        <v>-9.219066198498011</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5989282557584787</v>
+        <v>-0.5188177866343833</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.788476020211692</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.193497218588838</v>
+        <v>-8.993221045778601</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4990111216345059</v>
+        <v>-0.4189006525104109</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.746549344624529</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.068918562251246</v>
+        <v>-8.868642389441009</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4480405145434103</v>
+        <v>-0.3679300454193153</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.746549344624529</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.121813850295533</v>
+        <v>-8.921537677485295</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4665648555990174</v>
+        <v>-0.3864543864749219</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.741593998536083</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.049680675007652</v>
+        <v>-8.849404502197414</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4319778812452282</v>
+        <v>-0.3518674121211331</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.741593998536083</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.978314282398005</v>
+        <v>-8.778038109587767</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4131685865952344</v>
+        <v>-0.3330581174711393</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.670227605926435</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.88485524841278</v>
+        <v>-8.684579075602542</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3856684543140525</v>
+        <v>-0.305557985189957</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.670227605926435</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.617613447544382</v>
+        <v>-8.417337274734145</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2806062944660668</v>
+        <v>-0.2004958253419717</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.670227605926435</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.519706408867892</v>
+        <v>-8.319430236057654</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2417437939689315</v>
+        <v>-0.1616333248448365</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.602241856065878</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.495752867891934</v>
+        <v>-8.295476695081696</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2314938714330546</v>
+        <v>-0.1513834023089595</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.578288315089921</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.231692929569137</v>
+        <v>-8.031416756758899</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1391302122656883</v>
+        <v>-0.05901974314159286</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.314228376767125</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.524613306064299</v>
+        <v>-7.324337133254061</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1409146034759461</v>
+        <v>0.2210250726000416</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.314228376767125</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.484429007698108</v>
+        <v>-7.284152834887871</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1573319467102636</v>
+        <v>0.2374424158343591</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.274044078400934</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.321029136758746</v>
+        <v>-7.120752963948508</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2220587163067655</v>
+        <v>0.302169185430861</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.110644207461571</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.087547914529147</v>
+        <v>-6.88727174171891</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3233756340364575</v>
+        <v>0.4034861031605526</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8771629852319727</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.937881523521632</v>
+        <v>-6.737605350711394</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3803499801265042</v>
+        <v>0.4604604492505997</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7842594939894367</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.805606049890746</v>
+        <v>-6.605329877080508</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4286276563258862</v>
+        <v>0.5087381254499812</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.6519840203585501</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.649867717331004</v>
+        <v>-6.449591544520766</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4937380500374196</v>
+        <v>0.5738485191615146</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4962456877988085</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.400867918647423</v>
+        <v>-6.200591745837185</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6062443107345108</v>
+        <v>0.6863547798586058</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.4962456877988085</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.506457908420527</v>
+        <v>-6.30618173561029</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4360323852260501</v>
+        <v>0.5161428543501452</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.6018356775719129</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.525192810539124</v>
+        <v>-6.324916637728887</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4770827662556978</v>
+        <v>0.5571932353797928</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.6074316872320442</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.377252769131525</v>
+        <v>-6.176976596321287</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4163798601305699</v>
+        <v>0.496490329254665</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.5871107713234867</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.324283246877537</v>
+        <v>-6.124007074067299</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4288536827786871</v>
+        <v>0.5089641519027821</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.5341412490694978</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.280734840106846</v>
+        <v>-6.080458667296608</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4393124333918701</v>
+        <v>0.5194229025159651</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.5341412490694978</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.247371633628077</v>
+        <v>-6.04709546081784</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4671200703645209</v>
+        <v>0.5472305394886159</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.5341412490694978</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.139112496505556</v>
+        <v>-5.938836323695318</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5049558456727246</v>
+        <v>0.5850663147968196</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.5341412490694978</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.015821361688425</v>
+        <v>-5.815545188878187</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5517703936101537</v>
+        <v>0.6318808627342487</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.4108501142523673</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.994672162784981</v>
+        <v>-5.794395989974744</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.567931051408856</v>
+        <v>0.6480415205329515</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.3897009153489239</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.750906720801537</v>
+        <v>-5.550630547991299</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6612179365492845</v>
+        <v>0.7413284056733795</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.3897009153489239</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.649143900524242</v>
+        <v>-5.448867727714005</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7040473785802184</v>
+        <v>0.7841578477043138</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.3764818469564952</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.399293506575168</v>
+        <v>-5.19901733376493</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7967296111435505</v>
+        <v>0.8768400802676455</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.3764818469564952</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.223401414107736</v>
+        <v>-5.023125241297498</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8706855716511721</v>
+        <v>0.9507960407752671</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.3764818469564952</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.051954951085272</v>
+        <v>-4.851678778275034</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9525916629147111</v>
+        <v>1.032702132038806</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.2050353839340321</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.977665385346933</v>
+        <v>-4.777389212536695</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9813279668263437</v>
+        <v>1.061438435950439</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.1307458181956928</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.914029643112999</v>
+        <v>-4.713753470302761</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.011477064774235</v>
+        <v>1.09158753389833</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.06711007596175828</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.802602883787078</v>
+        <v>-4.602326710976841</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.037242027288399</v>
+        <v>1.117352496412494</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.06711007596175828</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.562172386982218</v>
+        <v>-4.36189621417198</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.13515730263522</v>
+        <v>1.215267771759315</v>
       </c>
       <c r="F1925" t="n">
         <v>0.173320420843102</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.489929818811023</v>
+        <v>-4.289653646000786</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.167983643738518</v>
+        <v>1.248094112862613</v>
       </c>
       <c r="F1926" t="n">
         <v>0.173320420843102</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.436931496529636</v>
+        <v>-4.236655323719398</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.189861556568413</v>
+        <v>1.269972025692508</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2286566798450408</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.328126611049909</v>
+        <v>-4.127850438239671</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.230381581980298</v>
+        <v>1.310492051104393</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2286566798450408</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.108105813012898</v>
+        <v>-3.90782964020266</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.319968938205716</v>
+        <v>1.400079407329811</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3698765249130211</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.97523812394962</v>
+        <v>-3.774961951139382</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.389010196632851</v>
+        <v>1.469120665756946</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3698765249130211</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.855065040585121</v>
+        <v>-3.654788867774883</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.438225274418952</v>
+        <v>1.518335743543047</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4900496082775201</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.710392895485383</v>
+        <v>-3.510116722675146</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.506182235020287</v>
+        <v>1.586292704144382</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6347217533772576</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.770267722843076</v>
+        <v>-3.569991550032838</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.468269795478636</v>
+        <v>1.548380264602731</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5748469260195654</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.650447491932238</v>
+        <v>-3.450171319122</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.531487057077179</v>
+        <v>1.611597526201274</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5748469260195654</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.652917198394044</v>
+        <v>-3.452641025583806</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.438143373814898</v>
+        <v>1.518253842938994</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5723772195577592</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.721287384718054</v>
+        <v>-3.521011211907816</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.330057160770596</v>
+        <v>1.410167629894691</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5816529185939742</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.735075437565101</v>
+        <v>-3.534799264754863</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.314978648263669</v>
+        <v>1.395089117387764</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5816529185939742</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.766068596893806</v>
+        <v>-3.565792424083568</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.127290949572573</v>
+        <v>1.207401418696668</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5816529185939742</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.590594337101337</v>
+        <v>-3.390318164291099</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.202047885481349</v>
+        <v>1.282158354605444</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5816529185939742</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.701530589742585</v>
+        <v>-3.501254416932348</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.133415413186056</v>
+        <v>1.213525882310151</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5816529185939742</v>
@@ -46194,10 +46194,10 @@
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.667867044270304</v>
+        <v>-3.467590871460066</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.075419144776419</v>
+        <v>1.155529613900514</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6153164640662561</v>
@@ -46217,10 +46217,10 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.60801442506658</v>
+        <v>-3.407738252256343</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.109532578890041</v>
+        <v>1.189643048014136</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6153164640662561</v>
@@ -46240,10 +46240,10 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.521770962040203</v>
+        <v>-3.321494789229965</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.138976234674452</v>
+        <v>1.219086703798547</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6153164640662561</v>
@@ -46263,10 +46263,10 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.567077781439183</v>
+        <v>-3.366801608628945</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.112629282359385</v>
+        <v>1.19273975148348</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5745063010570253</v>
@@ -46286,10 +46286,10 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.596110886141485</v>
+        <v>-3.395834713331247</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.101567913511566</v>
+        <v>1.181678382635661</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5745063010570253</v>
@@ -46309,10 +46309,10 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.503300404690625</v>
+        <v>-3.303024231880388</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.067964797983276</v>
+        <v>1.148075267107371</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6673167825078846</v>
@@ -46332,10 +46332,10 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.547689874020053</v>
+        <v>-3.347413701209815</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.052082486176105</v>
+        <v>1.132192955300201</v>
       </c>
       <c r="F1947" t="n">
         <v>0.622927313178457</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.435018655783803</v>
+        <v>-3.234742482973565</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.092226681982329</v>
+        <v>1.172337151106424</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7355985314147071</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.32264165460113</v>
+        <v>-3.327594300339412</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.142668778286065</v>
+        <v>1.140687719990752</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7355985314147071</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.350422052502483</v>
+        <v>-3.355374698240765</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.143053820894063</v>
+        <v>1.14107276259875</v>
       </c>
       <c r="F1950" t="n">
         <v>0.707818133513354</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.433423333527762</v>
+        <v>-3.438375979266044</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9482090284846043</v>
+        <v>0.9462279701892917</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6892472489861803</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.542037411971093</v>
+        <v>-3.546990057709375</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.024913057826477</v>
+        <v>1.022931999531165</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6892472489861803</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.50662837372295</v>
+        <v>-3.511581019461232</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.053589699228058</v>
+        <v>1.051608640932745</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6892472489861803</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.468244711164799</v>
+        <v>-3.473197356903081</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.066362605593687</v>
+        <v>1.064381547298374</v>
       </c>
       <c r="F1954" t="n">
         <v>0.7276309115443315</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.291128381129633</v>
+        <v>-3.296081026867915</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.133938166453055</v>
+        <v>1.131957108157742</v>
       </c>
       <c r="F1955" t="n">
         <v>0.7276309115443315</v>
@@ -46539,10 +46539,10 @@
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.336220625963179</v>
+        <v>-3.34117327170146</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.11658466028155</v>
+        <v>1.114603601986238</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6657348683749417</v>
@@ -46562,10 +46562,10 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.156845204724411</v>
+        <v>-3.161797850462692</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.182121804083471</v>
+        <v>1.180140745788159</v>
       </c>
       <c r="F1957" t="n">
         <v>0.8225116265456603</v>
@@ -46585,10 +46585,10 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.201859418245018</v>
+        <v>-3.206812063983298</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.144923574006818</v>
+        <v>1.142942515711506</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7921627312310557</v>
@@ -46608,10 +46608,10 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.468863928517453</v>
+        <v>-3.473816574255734</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.04381333223679</v>
+        <v>1.041832273941478</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5977996931881071</v>
@@ -46631,10 +46631,10 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.570061709954626</v>
+        <v>-3.575014355692907</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.002538141558422</v>
+        <v>1.00055708326311</v>
       </c>
       <c r="F1960" t="n">
         <v>0.529390879642788</v>
@@ -46654,10 +46654,10 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.563550743340313</v>
+        <v>-3.568503389078594</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.002742489758464</v>
+        <v>1.000761431463152</v>
       </c>
       <c r="F1961" t="n">
         <v>0.529390879642788</v>
@@ -46677,10 +46677,10 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.544512615633016</v>
+        <v>-3.549465261371297</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.006882460049628</v>
+        <v>1.004901401754316</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4712072683115934</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.575639246783634</v>
+        <v>-3.580591892521915</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.172013676528061</v>
+        <v>1.170032618232749</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4712072683115934</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.589506008117551</v>
+        <v>-3.594458653855832</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.167300300980628</v>
+        <v>1.165319242685316</v>
       </c>
       <c r="F1964" t="n">
         <v>0.4333493515777705</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.544701836577621</v>
+        <v>-3.549654482315902</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.191230499993526</v>
+        <v>1.189249441698214</v>
       </c>
       <c r="F1965" t="n">
         <v>0.4333493515777705</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.396958866342619</v>
+        <v>-3.4019115120809</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.148277909364726</v>
+        <v>1.146296851069414</v>
       </c>
       <c r="F1966" t="n">
         <v>0.6011567088126537</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.49897354887384</v>
+        <v>-3.503926194612121</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.110265657883719</v>
+        <v>1.108284599588407</v>
       </c>
       <c r="F1967" t="n">
         <v>0.6011567088126537</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.492820842821056</v>
+        <v>-3.497773488559337</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.113389088696491</v>
+        <v>1.111408030401179</v>
       </c>
       <c r="F1968" t="n">
         <v>0.607309414865438</v>
@@ -46838,10 +46838,10 @@
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.509630140971557</v>
+        <v>-3.514582786709838</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.105745846176401</v>
+        <v>1.103764787881088</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5905001167149364</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.447332142195435</v>
+        <v>-3.452284787933716</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.19700059948367</v>
+        <v>1.195019541188358</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5905001167149364</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.245541944530277</v>
+        <v>-3.250494590268558</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.08000868026386</v>
+        <v>1.078027621968548</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7885183088840908</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.08072894145143</v>
+        <v>-3.085681587189711</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.216224113817574</v>
+        <v>1.214243055522262</v>
       </c>
       <c r="F1972" t="n">
         <v>0.9533313119629377</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.178469486076405</v>
+        <v>-3.183422131814686</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.191755632083628</v>
+        <v>1.189774573788316</v>
       </c>
       <c r="F1973" t="n">
         <v>0.9374420338299576</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.354807246199334</v>
+        <v>-3.359759891937615</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.119756508859128</v>
+        <v>1.117775450563816</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7611042737070282</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.278385199767407</v>
+        <v>-3.283337845505688</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.148816945471828</v>
+        <v>1.146835887176515</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7611042737070282</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.234012068128838</v>
+        <v>-3.238964713867119</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.166429065562691</v>
+        <v>1.164448007267379</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8054774053455968</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.111177847241671</v>
+        <v>-3.116130492979952</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.209956548056149</v>
+        <v>1.207975489760836</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8054774053455968</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.063522116680615</v>
+        <v>-3.068474762418896</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.235400597308376</v>
+        <v>1.233419539013063</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8531331359066524</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.963003958181861</v>
+        <v>-2.967956603920141</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.280500234082602</v>
+        <v>1.27851917578729</v>
       </c>
       <c r="F1979" t="n">
         <v>0.953651294405407</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.02367054858425</v>
+        <v>-3.028623194322531</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.242988270397519</v>
+        <v>1.241007212102207</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8719529776868733</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.978832146975852</v>
+        <v>-2.983784792714133</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.265021333651507</v>
+        <v>1.263040275356194</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8764964106317428</v>
@@ -47137,10 +47137,10 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.99833060321786</v>
+        <v>-3.003283248956141</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.261382890785782</v>
+        <v>1.259401832490469</v>
       </c>
       <c r="F1982" t="n">
         <v>0.8284117693518385</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.954127766131959</v>
+        <v>-2.95908041187024</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.284943628147979</v>
+        <v>1.282962569852667</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8726146064377389</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.991106793795403</v>
+        <v>-2.996059439533683</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.268562017551849</v>
+        <v>1.266580959256537</v>
       </c>
       <c r="F1984" t="n">
         <v>0.9095885082290694</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.83281537625613</v>
+        <v>-2.837768021994411</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.383126349750598</v>
+        <v>1.381145291455285</v>
       </c>
       <c r="F1985" t="n">
         <v>0.9095885082290694</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.625173372621654</v>
+        <v>-2.630126018359935</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.464623855798641</v>
+        <v>1.462642797503329</v>
       </c>
       <c r="F1986" t="n">
         <v>1.117230511863545</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.574141279899126</v>
+        <v>-2.579093925637407</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.479984921125923</v>
+        <v>1.47800386283061</v>
       </c>
       <c r="F1987" t="n">
         <v>1.168262604586074</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.508917098771921</v>
+        <v>-2.513869744510202</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.52326199766951</v>
+        <v>1.521280939374197</v>
       </c>
       <c r="F1988" t="n">
         <v>1.233486785713279</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.471490078700787</v>
+        <v>-2.476442724439068</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.534193777997244</v>
+        <v>1.532212719701931</v>
       </c>
       <c r="F1989" t="n">
         <v>1.238738323742461</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.491601734735495</v>
+        <v>-2.496554380473776</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.527405907914601</v>
+        <v>1.525424849619288</v>
       </c>
       <c r="F1990" t="n">
         <v>1.24976566873988</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.43785692030829</v>
+        <v>-2.442809566046571</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.709461604706693</v>
+        <v>1.707480546411381</v>
       </c>
       <c r="F1991" t="n">
         <v>1.259828978180342</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.363074659283278</v>
+        <v>-2.368027305021559</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.859487418334516</v>
+        <v>1.857506360039203</v>
       </c>
       <c r="F1992" t="n">
         <v>1.334611239205355</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.33699057501947</v>
+        <v>-2.341943220757751</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.861629028053898</v>
+        <v>1.859647969758585</v>
       </c>
       <c r="F1993" t="n">
         <v>1.334611239205355</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.258859394170523</v>
+        <v>-2.263812039908804</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.891074695977256</v>
+        <v>1.889093637681944</v>
       </c>
       <c r="F1994" t="n">
         <v>1.40878805008904</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.24996693277724</v>
+        <v>-2.254919578515521</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.91218608626136</v>
+        <v>1.910205027966048</v>
       </c>
       <c r="F1995" t="n">
         <v>1.40878805008904</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.418443049747118</v>
+        <v>-2.423395695485399</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.836650686877993</v>
+        <v>1.834669628582681</v>
       </c>
       <c r="F1996" t="n">
         <v>1.380840214372459</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782704</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.720643520885535</v>
+        <v>-1.725596166623816</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.097040195610488</v>
+        <v>2.095059137315176</v>
       </c>
       <c r="F1997" t="n">
         <v>1.310492155002048</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632632</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.697922417202382</v>
+        <v>-1.702875062940663</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.096792659580654</v>
+        <v>2.094811601285341</v>
       </c>
       <c r="F1998" t="n">
         <v>1.310492155002048</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.696197373912338</v>
+        <v>-1.701150019650619</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.25638880274784</v>
+        <v>2.254407744452528</v>
       </c>
       <c r="F1999" t="n">
         <v>1.312217198292092</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.850978380690594</v>
+        <v>-1.855931026428875</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.231554222530185</v>
+        <v>2.229573164234873</v>
       </c>
       <c r="F2000" t="n">
         <v>1.278849524237616</v>
@@ -47574,10 +47574,10 @@
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.84392369047542</v>
+        <v>-1.848876336213701</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.2310514546058</v>
+        <v>2.229070396310487</v>
       </c>
       <c r="F2001" t="n">
         <v>1.285904214452789</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.816972466148932</v>
+        <v>-1.821925111887213</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.251838097981136</v>
+        <v>2.249857039685824</v>
       </c>
       <c r="F2002" t="n">
         <v>1.300784560480509</v>
@@ -47620,10 +47620,10 @@
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.952925474205248</v>
+        <v>-1.957878119943529</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.381560026903569</v>
+        <v>2.379578968608257</v>
       </c>
       <c r="F2003" t="n">
         <v>1.300784560480509</v>
@@ -47643,10 +47643,10 @@
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.97533359201012</v>
+        <v>-1.980286237748401</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.364713474684614</v>
+        <v>2.362732416389302</v>
       </c>
       <c r="F2004" t="n">
         <v>1.300784560480509</v>
@@ -47666,10 +47666,10 @@
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.12333935948952</v>
+        <v>-2.1282920052278</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.307565167242491</v>
+        <v>2.305584108947179</v>
       </c>
       <c r="F2005" t="n">
         <v>1.214057551616967</v>
@@ -47689,10 +47689,10 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.13278028537805</v>
+        <v>-2.13773293111633</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.360042514608927</v>
+        <v>2.358061456313614</v>
       </c>
       <c r="F2006" t="n">
         <v>1.336484669160359</v>
@@ -47712,10 +47712,10 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.185053892713691</v>
+        <v>-2.190006538451972</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.342024166219971</v>
+        <v>2.340043107924659</v>
       </c>
       <c r="F2007" t="n">
         <v>1.284211061824717</v>
@@ -47735,10 +47735,10 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.261383870314597</v>
+        <v>-2.266336516052878</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.309603988073384</v>
+        <v>2.307622929778072</v>
       </c>
       <c r="F2008" t="n">
         <v>1.284211061824717</v>
@@ -47758,10 +47758,10 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.373140822929898</v>
+        <v>-2.378093468668179</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.259721436630126</v>
+        <v>2.257740378334813</v>
       </c>
       <c r="F2009" t="n">
         <v>1.172454109209416</v>
@@ -47781,10 +47781,10 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.371299803871647</v>
+        <v>-2.376252449609928</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.258891854463578</v>
+        <v>2.256910796168266</v>
       </c>
       <c r="F2010" t="n">
         <v>1.173722335880885</v>
@@ -47804,10 +47804,10 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.5036010959692</v>
+        <v>-2.508553741707481</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.219044744490476</v>
+        <v>2.217063686195163</v>
       </c>
       <c r="F2011" t="n">
         <v>1.173722335880885</v>
@@ -47827,10 +47827,10 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.50516273878406</v>
+        <v>-2.510115384522341</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.218420087364532</v>
+        <v>2.216439029069219</v>
       </c>
       <c r="F2012" t="n">
         <v>1.173722335880885</v>
@@ -47850,10 +47850,10 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.533063525893533</v>
+        <v>-2.538016171631814</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.205783813647745</v>
+        <v>2.203802755352432</v>
       </c>
       <c r="F2013" t="n">
         <v>1.13912541173795</v>
@@ -47873,10 +47873,10 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.655589628596427</v>
+        <v>-2.660542274334708</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.153537816543786</v>
+        <v>2.151556758248473</v>
       </c>
       <c r="F2014" t="n">
         <v>1.016599309035056</v>
@@ -47896,10 +47896,10 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.675650949872934</v>
+        <v>-2.680603595611215</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.212219247623687</v>
+        <v>2.210238189328375</v>
       </c>
       <c r="F2015" t="n">
         <v>0.996537987758549</v>
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199803</v>
+        <v>3.640764248199802</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.932371767867758</v>
+        <v>-3.043884217714658</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.249842639427604</v>
+        <v>2.205237659488844</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8881234136147341</v>
+        <v>0.8605332425646113</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.956021819057296</v>
+        <v>3.939467716427222</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622234</v>
+        <v>3.668303164622232</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.086358185643898</v>
+        <v>-3.197870635490798</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.257228341462788</v>
+        <v>2.212623361524028</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8881234136147341</v>
+        <v>0.8605332425646113</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.025002088202935</v>
+        <v>4.008447985572861</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808524</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.035836281816232</v>
+        <v>-3.147348731663132</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.263488305113975</v>
+        <v>2.218883325175215</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8881234136147341</v>
+        <v>0.8605332425646113</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.011053290323056</v>
+        <v>3.994499187692982</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994891</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.288311435823957</v>
+        <v>-3.399823885670857</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.174368732566299</v>
+        <v>2.129763752627539</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8881234136147341</v>
+        <v>0.8605332425646113</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.02292377937847</v>
+        <v>4.006369676748396</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674042696358295</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.557784237745665</v>
+        <v>-3.669296687592565</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.06779014631656</v>
+        <v>2.023185166377799</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8881234136147341</v>
+        <v>0.8605332425646113</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.024134313897414</v>
+        <v>4.00758021126734</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637084</v>
+        <v>3.663523617637083</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.715328309475106</v>
+        <v>-3.826840759322006</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.008894259852105</v>
+        <v>1.964289279913344</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.8212216084744597</v>
+        <v>0.7936314374243367</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.98811497304057</v>
+        <v>3.971560870410497</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.65216331330134</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.844178860177152</v>
+        <v>-3.955691310024053</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.952431892307476</v>
+        <v>1.907826912368715</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7802281996237381</v>
+        <v>0.7526380285736152</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.958596780466327</v>
+        <v>3.942042677836254</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215467</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.961146552816043</v>
+        <v>-4.072659002662944</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.067848871950964</v>
+        <v>2.023243892012203</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7802281996237381</v>
+        <v>0.7526380285736152</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.120800837165371</v>
+        <v>4.104246734535297</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69655362845669</v>
+        <v>3.696553628456689</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.045864495036997</v>
+        <v>-4.157376944883898</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.028808333026396</v>
+        <v>1.984203353087636</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6951121706956918</v>
+        <v>0.6675219996455688</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.064577857772357</v>
+        <v>4.048023755142284</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253286</v>
+        <v>3.750058176253285</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.12779931330588</v>
+        <v>-4.239311763152781</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.006263823287334</v>
+        <v>1.961658843348574</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.6851774251086116</v>
+        <v>0.6575872540584886</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.068846427988601</v>
+        <v>4.052292325358526</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78364702771783</v>
+        <v>3.783647027717829</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.074061139905618</v>
+        <v>-4.185573589752519</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.036684731103341</v>
+        <v>1.992079751164581</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.7389155985088737</v>
+        <v>0.7113254274587507</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.11001497048466</v>
+        <v>4.093460867854587</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616946</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.964054856428397</v>
+        <v>-4.075567306275297</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.072840131738405</v>
+        <v>2.028235151799645</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.7621201704261489</v>
+        <v>0.7345299993760259</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.1160906008792</v>
+        <v>4.099536498249127</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78557808520366</v>
+        <v>3.785578085203659</v>
       </c>
       <c r="C2028" t="n">
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.820995280687471</v>
+        <v>-3.932507730534371</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.13431397275675</v>
+        <v>2.089708992817989</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.7701335970161282</v>
+        <v>0.7425434259660052</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.125148667555163</v>
+        <v>4.108594564925089</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436926</v>
+        <v>3.777251572436925</v>
       </c>
       <c r="C2029" t="n">
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.519548555215634</v>
+        <v>-3.631061005062534</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.262153545828021</v>
+        <v>2.217548565889261</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.071580322487965</v>
+        <v>1.043990151437842</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.313277585720801</v>
+        <v>4.296723483090727</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064758</v>
+        <v>3.812650101064759</v>
       </c>
       <c r="C2030" t="n">
         <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.574503751658703</v>
+        <v>-3.686016201505603</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.241142645003503</v>
+        <v>2.196537665064743</v>
       </c>
       <c r="F2030" t="n">
-        <v>1.071580322487965</v>
+        <v>1.043990151437842</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.314248763473511</v>
+        <v>4.297694660843438</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.589336236616242</v>
+        <v>3.454914447480782</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.527558354233377</v>
+        <v>3.442936457994066</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.574503751658703</v>
+        <v>-3.686016201505603</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.241142645003503</v>
+        <v>2.196537665064743</v>
       </c>
       <c r="F2031" t="n">
-        <v>1.071580322487965</v>
+        <v>1.043990151437842</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.520622151219745</v>
+        <v>3.436000254980434</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240720.xlsx
+++ b/tame_output/ON/bt/strategyON_20240720.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>35.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-72.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.3%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>121.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-644.5%</t>
+          <t>-637.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.5%</t>
+          <t>-67.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.5%</t>
+          <t>458.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-530.2%</t>
+          <t>-511.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-258.2%</t>
+          <t>-255.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-35.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>183.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-156.6%</t>
+          <t>-148.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-263.7%</t>
+          <t>-256.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-136.8%</t>
+          <t>-124.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-119.6%</t>
+          <t>-109.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-158.6%</t>
+          <t>-154.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,22 +1471,22 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-102.4%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201484</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.127753658579592</v>
+        <v>-1.057194209571815</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.665622562205445</v>
+        <v>2.693846341808556</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9880615826826838</v>
+        <v>1.058621031690461</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.70991739956064</v>
+        <v>3.752253068965306</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537423</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.417885325185023</v>
+        <v>-1.347325876177246</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.549436112162195</v>
+        <v>2.577659891765305</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.012143377422864</v>
+        <v>1.082702826430641</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.72423269300367</v>
+        <v>3.766568362408336</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382188</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.625889383538101</v>
+        <v>-1.555329934530324</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.471126633374889</v>
+        <v>2.499350412978</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.012143377422864</v>
+        <v>1.082702826430641</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.729124837557595</v>
+        <v>3.771460506962261</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074618</v>
+        <v>3.251475576074619</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.688067794699071</v>
+        <v>-1.617508345691294</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.441336725248489</v>
+        <v>2.4695605048516</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9499649662618935</v>
+        <v>1.020524415269671</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.686899247199001</v>
+        <v>3.729234916603667</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911636</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.054136521843724</v>
+        <v>-1.983577072835946</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.287993533697077</v>
+        <v>2.316217313300188</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5838962391172409</v>
+        <v>0.654455688125018</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.460342310218659</v>
+        <v>3.502677979623325</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.262627303295408</v>
+        <v>-2.192067854287631</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.224935510855171</v>
+        <v>2.253159290458282</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3754054576655564</v>
+        <v>0.4459649066733335</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.355586131086416</v>
+        <v>3.397921800491083</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416042</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.50982848806063</v>
+        <v>-2.439269039052852</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.134153787357651</v>
+        <v>2.162377566960762</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3955588111643689</v>
+        <v>0.466118260172146</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.375776893594272</v>
+        <v>3.418112562998938</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382325</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.002213516084727</v>
+        <v>-2.931654067076949</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.938306168191745</v>
+        <v>1.966529947794855</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.02626676785195076</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.081452268823546</v>
+        <v>3.123787938228213</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495495</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.387393907014799</v>
+        <v>-3.316834458007022</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.782776550632579</v>
+        <v>1.81100033023569</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.02626676785195076</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.079994807636409</v>
+        <v>3.122330477041076</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347051</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.637264587029381</v>
+        <v>-3.566705138021603</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.684597402081363</v>
+        <v>1.712821181684473</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.06056349702926461</v>
+        <v>0.009995951978512496</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.103521562989304</v>
+        <v>3.14585723239397</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130013</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.843776363916402</v>
+        <v>-3.773216914908625</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.598098749982812</v>
+        <v>1.626322529585923</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.196515824908509</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.975720555513349</v>
+        <v>3.018056224918015</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.163120438996904</v>
+        <v>-4.092560989989126</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.472134046650871</v>
+        <v>1.500357826253981</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.196515824908509</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.977493482213608</v>
+        <v>3.019829151618274</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.594926232146691</v>
+        <v>-4.524366783138913</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.28574461685836</v>
+        <v>1.313968396461471</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4034927703575531</v>
+        <v>-0.332933321349776</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.881975871816252</v>
+        <v>2.924311541220919</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.829620226279244</v>
+        <v>-4.759060777271466</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.18015179420743</v>
+        <v>1.208375573810541</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3971565031282979</v>
+        <v>-0.3265970541205208</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.874062407155896</v>
+        <v>2.916398076560562</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.165282873509696</v>
+        <v>-5.094723424501918</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.044467326971214</v>
+        <v>1.072691106574325</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4650874886172027</v>
+        <v>-0.3945280396094256</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.831884407518518</v>
+        <v>2.874220076923184</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.241727203712568</v>
+        <v>-5.17116775470479</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.020377155124307</v>
+        <v>1.048600934727418</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3846419795235408</v>
+        <v>-0.3140825305157637</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.886639273208957</v>
+        <v>2.928974942613623</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.606854586351314</v>
+        <v>-5.536295137343537</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8735807170746397</v>
+        <v>0.9018044966777503</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6809527638225534</v>
+        <v>-0.6103933148147762</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.708107317635381</v>
+        <v>2.750442987040047</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.015443363531993</v>
+        <v>-5.944883914524214</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7089067502171269</v>
+        <v>0.7371305298202384</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.018982091995455</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.461715595341733</v>
+        <v>2.504051264746399</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.129203775554858</v>
+        <v>-6.058644326547079</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6585880178794419</v>
+        <v>0.6868117974825529</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.018982091995455</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.456901027813193</v>
+        <v>2.49923669721786</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.545595649841855</v>
+        <v>-6.475036200834077</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4900253187735202</v>
+        <v>0.5182490983766312</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.018982091995455</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.454895078422071</v>
+        <v>2.497230747826737</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.789867050568925</v>
+        <v>-6.719307601561146</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4025754491513713</v>
+        <v>0.4307992287544824</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.018982091995455</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.46515376909075</v>
+        <v>2.507489438495416</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.995118069805685</v>
+        <v>-6.924558620797907</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3165746066023623</v>
+        <v>0.3447983862054733</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.018982091995455</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.461253334236445</v>
+        <v>2.503589003641111</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.043320887048029</v>
+        <v>-6.972761438040251</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2956983997604259</v>
+        <v>0.323922179363537</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.018982091995455</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.459658254291446</v>
+        <v>2.501993923696112</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.339982228858227</v>
+        <v>-7.269422779850448</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1808128389655548</v>
+        <v>0.2090366185686663</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.087725227729333</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.464527018184993</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.526701937167529</v>
+        <v>-7.456142488159751</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1020986511074309</v>
+        <v>0.1303224307105419</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.087725227729333</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.46050071365059</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.909703325910161</v>
+        <v>-7.839143876902382</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.05120400571120598</v>
+        <v>-0.02298022610809447</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.087725227729333</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.460398612329006</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.914189771111549</v>
+        <v>-7.84363032210377</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05042706782033113</v>
+        <v>-0.02220328821722006</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.092211672930722</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.417942591774937</v>
+        <v>2.460278261179603</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.273720093615552</v>
+        <v>-8.203160644607774</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1888888935238819</v>
+        <v>-0.1606651139207709</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.092211672930722</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.423292895072987</v>
+        <v>2.465628564477653</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.324069157069774</v>
+        <v>-8.253509708061996</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2011124989483934</v>
+        <v>-0.1728887193452819</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.213120185392721</v>
+        <v>-1.142560736384944</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.400999476957631</v>
+        <v>2.443335146362298</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.42168843449117</v>
+        <v>-8.351128985483392</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2371184592951829</v>
+        <v>-0.2088946796920719</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.310739462814118</v>
+        <v>-1.240180013806341</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.387805330531228</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.475759933999528</v>
+        <v>-8.405200484991751</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.255853502776954</v>
+        <v>-0.2276297231738429</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.364810962322477</v>
+        <v>-1.2942515133147</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.315920317743119</v>
+        <v>2.358255987147785</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.680018109329392</v>
+        <v>-8.609458660321614</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3320435757902573</v>
+        <v>-0.3038197961871463</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.492449906936466</v>
+        <v>-1.421890457928689</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.287185817498034</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.713670947837866</v>
+        <v>-8.643111498830088</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3410221567092107</v>
+        <v>-0.3127983771060996</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.592863274853503</v>
+        <v>-1.522303825845726</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.231420351232248</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.640201116170417</v>
+        <v>-8.569641667162639</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.29626252254881</v>
+        <v>-0.2680387429456985</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.448833994178278</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.290873951726138</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.81532553355696</v>
+        <v>-8.744766084549182</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3517570687559104</v>
+        <v>-0.3235332891527993</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.623958411564822</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.200354522041728</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.04977762757145</v>
+        <v>-8.979218178563672</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4527570712633024</v>
+        <v>-0.4245332916601909</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.623958411564822</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.193135357140132</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.154152358597896</v>
+        <v>-9.083592909590118</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5011791544478572</v>
+        <v>-0.4729553748447457</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.728333142591268</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.123838327750288</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.206938514198223</v>
+        <v>-9.136379065190445</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5211778268494314</v>
+        <v>-0.4929540472463203</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-1.824008629173665</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>2.067548825639407</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.332975307566512</v>
+        <v>-9.262415858558734</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5688988155676324</v>
+        <v>-0.5406750359645214</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.798757006363922</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>2.085393527954366</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.275903535670581</v>
+        <v>-9.205344086662803</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5420797711228591</v>
+        <v>-0.513855991519748</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.798757006363922</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>2.089383863640768</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.417575377394702</v>
+        <v>-9.347015928386924</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6002237347112489</v>
+        <v>-0.5719999551081378</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.798757006363922</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>2.087908636742026</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.367984532969867</v>
+        <v>-9.297425083962089</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5653339867764431</v>
+        <v>-0.537110207173332</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-1.749166161939089</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.132716553561798</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.219066198498011</v>
+        <v>-9.148506749490233</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5188177866343833</v>
+        <v>-0.4905940070312722</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.717916571203915</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.138415174356219</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.993221045778601</v>
+        <v>-8.922661596770823</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4189006525104109</v>
+        <v>-0.3906768729072998</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.675989895616752</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.173150252744726</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.868642389441009</v>
+        <v>-8.798082940433231</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3679300454193153</v>
+        <v>-0.3397062658162038</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.675989895616752</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.174289397300785</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.921537677485295</v>
+        <v>-8.850978228477517</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3864543864749219</v>
+        <v>-0.3582306068718109</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.671034549528306</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.17989637911596</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.849404502197414</v>
+        <v>-8.778845053189636</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3518674121211331</v>
+        <v>-0.3236436325180221</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.671034549528306</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.185630083354597</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.778038109587767</v>
+        <v>-8.707478660579989</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3330581174711393</v>
+        <v>-0.3048343378680283</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.599668156918658</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.21871265652652</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.684579075602542</v>
+        <v>-8.614019626594764</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.305557985189957</v>
+        <v>-0.277334205586846</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.599668156918658</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.208829175213613</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.417337274734145</v>
+        <v>-8.346777825726367</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2004958253419717</v>
+        <v>-0.1722720457388607</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.599668156918658</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.206994614714239</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.319430236057654</v>
+        <v>-8.248870787049876</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1616333248448365</v>
+        <v>-0.1334095452417254</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.531682407058101</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.247485749657112</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.295476695081696</v>
+        <v>-8.224917246073918</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1513834023089595</v>
+        <v>-0.1231596227058485</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.507728866082144</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.26252638038818</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.031416756758899</v>
+        <v>-7.960857307751122</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05901974314159286</v>
+        <v>-0.03079596353848224</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.243668927759348</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.407702027220106</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.324337133254061</v>
+        <v>-7.253777684246284</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2210250726000416</v>
+        <v>0.2492488522031522</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.243668927759348</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.404914993559805</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.284152834887871</v>
+        <v>-7.213593385880094</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2374424158343591</v>
+        <v>0.2656661954374697</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.203484629393157</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.429369196467361</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.120752963948508</v>
+        <v>-7.050193514940731</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.302169185430861</v>
+        <v>0.3303929650339716</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.040084758453794</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.526775940251735</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.88727174171891</v>
+        <v>-6.816712292711133</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4034861031605526</v>
+        <v>0.4317098827636636</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.8066035362241957</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.674789102427347</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.737605350711394</v>
+        <v>-6.667045901703617</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4604604492505997</v>
+        <v>0.4886842288537103</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.7137000449816597</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.727638986859909</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.605329877080508</v>
+        <v>-6.534770428072731</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5087381254499812</v>
+        <v>0.5369619050530918</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.5814245713507731</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.802371757785468</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.449591544520766</v>
+        <v>-6.379032095512989</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5738485191615146</v>
+        <v>0.6020722987646252</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.4256862387910315</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.89862981800895</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.200591745837185</v>
+        <v>-6.130032296829408</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6863547798586058</v>
+        <v>0.7145785594617164</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.4256862387910315</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.911536159232608</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.30618173561029</v>
+        <v>-6.235622286602513</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5161428543501452</v>
+        <v>0.5443666339532562</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.5312762285641359</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.720206235769527</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.324916637728887</v>
+        <v>-6.25435718872111</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5571932353797928</v>
+        <v>0.5854170149829034</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.5368722382242672</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.765392971850535</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.176976596321287</v>
+        <v>-6.10641714731351</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.496490329254665</v>
+        <v>0.5247141088577756</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.5165513223157097</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.657706598707501</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.124007074067299</v>
+        <v>-6.053447625059522</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5089641519027821</v>
+        <v>0.5371879315058932</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.4635818000617208</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.680774325806417</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.729969716098113</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.080458667296608</v>
+        <v>-6.009899218288831</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5194229025159651</v>
+        <v>0.5476466821190762</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.4635818000617208</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.673813713711324</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493424</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.04709546081784</v>
+        <v>-5.976536011810063</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5472305394886159</v>
+        <v>0.5754543190917265</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.4635818000617208</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.688276068092467</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.82855148672282</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.938836323695318</v>
+        <v>-5.868276874687541</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5850663147968196</v>
+        <v>0.6132900943999302</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.4635818000617208</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.682808188551662</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.815545188878187</v>
+        <v>-5.74498573987041</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6318808627342487</v>
+        <v>0.6601046423373598</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.3402906652445903</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.754280963452517</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.794395989974744</v>
+        <v>-5.723836540966967</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6480415205329515</v>
+        <v>0.6762653001360621</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.3191414663411469</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.774671461031908</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.550630547991299</v>
+        <v>-5.480071098983522</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7413284056733795</v>
+        <v>0.7695521852764906</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.3191414663411469</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.770452169378959</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.448867727714005</v>
+        <v>-5.378308278706228</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7841578477043138</v>
+        <v>0.8123816273074245</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.3059223979487182</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.780507924334432</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.19901733376493</v>
+        <v>-5.128457884757153</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8768400802676455</v>
+        <v>0.9050638598707565</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.3059223979487182</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.773249999318134</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.023125241297498</v>
+        <v>-4.95256579228972</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9507960407752671</v>
+        <v>0.9790198203783784</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.3059223979487182</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.776849122838783</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.851678778275034</v>
+        <v>-4.781119329267256</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.032702132038806</v>
+        <v>1.060925911641917</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.1344759349262551</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.893044506706814</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.777389212536695</v>
+        <v>-4.706829763528917</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.061438435950439</v>
+        <v>1.08966221555355</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.06018636918791581</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.936638723766115</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.713753470302761</v>
+        <v>-4.643194021294983</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.09158753389833</v>
+        <v>1.119811313501441</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>0.003449373046018722</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.979514970160793</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.602326710976841</v>
+        <v>-4.531767261969063</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.117352496412494</v>
+        <v>1.145576276015605</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>0.003449373046018722</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.960709228944589</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.36189621417198</v>
+        <v>-4.291336765164202</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.215267771759315</v>
+        <v>1.243491551362426</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>0.243879869850879</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>3.106710603652382</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.289653646000786</v>
+        <v>-4.219094196993008</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.248094112862613</v>
+        <v>1.276317892465724</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>0.243879869850879</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>3.110639917487203</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.236655323719398</v>
+        <v>-4.16609587471162</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.269972025692508</v>
+        <v>1.29819580529562</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.2992161288528178</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.10218458740104</v>
+        <v>3.144520256805706</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.127850438239671</v>
+        <v>-4.057290989231893</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.310492051104393</v>
+        <v>1.338715830707504</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.2992161288528178</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.099182658621033</v>
+        <v>3.141518328025699</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.90782964020266</v>
+        <v>-3.837270191194882</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.400079407329811</v>
+        <v>1.428303186932922</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.4404359739207981</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.185493602672435</v>
+        <v>3.227829272077102</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.774961951139382</v>
+        <v>-3.704402502131604</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.469120665756946</v>
+        <v>1.497344445360057</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.4404359739207981</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.201387785474259</v>
+        <v>3.243723454878925</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.654788867774883</v>
+        <v>-3.584229418767105</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.518335743543047</v>
+        <v>1.546559523146158</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4900496082775201</v>
+        <v>0.5606090572852971</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.27463747993326</v>
+        <v>3.316973149337926</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.510116722675146</v>
+        <v>-3.439557273667368</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.586292704144382</v>
+        <v>1.614516483747493</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6347217533772576</v>
+        <v>0.7052812023850346</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.371528869554542</v>
+        <v>3.413864538959209</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.569991550032838</v>
+        <v>-3.49943210102506</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.548380264602731</v>
+        <v>1.576604044205842</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.6454063750273424</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.321641464541353</v>
+        <v>3.363977133946019</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.450171319122</v>
+        <v>-3.379611870114223</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.611597526201274</v>
+        <v>1.639821305804386</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.6454063750273424</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.336930633775562</v>
+        <v>3.379266303180227</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.452641025583806</v>
+        <v>-3.382081576576029</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.518253842938994</v>
+        <v>1.546477622542105</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5723772195577592</v>
+        <v>0.6429366685655362</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.243093009220919</v>
+        <v>3.285428678625586</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.521011211907816</v>
+        <v>-3.450451762900038</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.410167629894691</v>
+        <v>1.438391409497802</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.6522123676017512</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.16792029012795</v>
+        <v>3.210255959532616</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.534799264754863</v>
+        <v>-3.464239815747085</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.395089117387764</v>
+        <v>1.423312896990875</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.6522123676017512</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.158356998759841</v>
+        <v>3.200692668164507</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.565792424083568</v>
+        <v>-3.49523297507579</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.207401418696668</v>
+        <v>1.235625198299779</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.6522123676017512</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.983066563800228</v>
+        <v>3.025402233204894</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.390318164291099</v>
+        <v>-3.319758715283321</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.282158354605444</v>
+        <v>1.310382134208555</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.6522123676017512</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.987633795792016</v>
+        <v>3.029969465196682</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.501254416932348</v>
+        <v>-3.43069496792457</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.213525882310151</v>
+        <v>1.241749661913263</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.6522123676017512</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.963375824553223</v>
+        <v>3.005711493957889</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.467590871460066</v>
+        <v>-3.397031422452288</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.155529613900514</v>
+        <v>1.183753393503625</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.6858759130740331</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.912112265238041</v>
+        <v>2.954447934642708</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.407738252256343</v>
+        <v>-3.337178803248565</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.189643048014136</v>
+        <v>1.217866827617247</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.6858759130740331</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.922284651670174</v>
+        <v>2.96462032107484</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.321494789229965</v>
+        <v>-3.250935340222187</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.219086703798547</v>
+        <v>1.247310483401658</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.6858759130740331</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.917230922244034</v>
+        <v>2.9595665916487</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.366801608628945</v>
+        <v>-3.296242159621167</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.19273975148348</v>
+        <v>1.220963531086592</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.6450657500648023</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.884520599883021</v>
+        <v>2.926856269287687</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.395834713331247</v>
+        <v>-3.325275264323469</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.181678382635661</v>
+        <v>1.209902162238772</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.6450657500648023</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.885072472916123</v>
+        <v>2.927408142320789</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.303024231880388</v>
+        <v>-3.23246478287261</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.148075267107371</v>
+        <v>1.176299046710482</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6673167825078846</v>
+        <v>0.7378762315156616</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.870031453678004</v>
+        <v>2.91236712308267</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.347413701209815</v>
+        <v>-3.276854252202037</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.132192955300201</v>
+        <v>1.160416734903312</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.622927313178457</v>
+        <v>0.693486762186234</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.845271248004948</v>
+        <v>2.887606917409614</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.234742482973565</v>
+        <v>-3.164183033965787</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.172337151106424</v>
+        <v>1.200560930709535</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.8061579804224841</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.907949687458421</v>
+        <v>2.950285356863088</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.327594300339412</v>
+        <v>-3.242503187301583</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.140687719990752</v>
+        <v>1.174724165205884</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.8061579804224841</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.913440983289088</v>
+        <v>2.955776652693755</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.355374698240765</v>
+        <v>-3.270283585202936</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.14107276259875</v>
+        <v>1.175109207813881</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.707818133513354</v>
+        <v>0.778377582521131</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.908269946316816</v>
+        <v>2.950605615721482</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.438375979266044</v>
+        <v>-3.353284866228215</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9462279701892917</v>
+        <v>0.9802644154044229</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6892472489861803</v>
+        <v>0.7598066979939573</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.735483135601165</v>
+        <v>2.777818805005831</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.546990057709375</v>
+        <v>-3.461898944671546</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.022931999531165</v>
+        <v>1.056968444746296</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6892472489861803</v>
+        <v>0.7598066979939573</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.85563279632037</v>
+        <v>2.897968465725037</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.511581019461232</v>
+        <v>-3.426489906423404</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.051608640932745</v>
+        <v>1.085645086147876</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6892472489861803</v>
+        <v>0.7598066979939573</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.870145822422693</v>
+        <v>2.91248149182736</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.473197356903081</v>
+        <v>-3.388106243865252</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.064381547298374</v>
+        <v>1.098417992513505</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7276309115443315</v>
+        <v>0.7981903605521085</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.890595461299953</v>
+        <v>2.932931130704619</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.296081026867915</v>
+        <v>-3.210989913830086</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.131957108157742</v>
+        <v>1.165993553372874</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7276309115443315</v>
+        <v>0.7981903605521085</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.887324490145255</v>
+        <v>2.929660159549921</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.34117327170146</v>
+        <v>-3.256082158663632</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.114603601986238</v>
+        <v>1.148640047201369</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6657348683749417</v>
+        <v>0.7362943173827187</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.850870256005534</v>
+        <v>2.8932059254102</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.161797850462692</v>
+        <v>-3.076706737424864</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.180140745788159</v>
+        <v>1.21417719100329</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8225116265456603</v>
+        <v>0.8930710755534373</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.93872328621438</v>
+        <v>2.981058955619046</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.206812063983298</v>
+        <v>-3.12172095094547</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.142942515711506</v>
+        <v>1.176978960926637</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7921627312310557</v>
+        <v>0.8627221802388327</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.901321404357207</v>
+        <v>2.943657073761873</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.473816574255734</v>
+        <v>-3.388725461217906</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.041832273941478</v>
+        <v>1.075868719156609</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5977996931881071</v>
+        <v>0.6683591421958841</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.790395143870383</v>
+        <v>2.832730813275049</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.575014355692907</v>
+        <v>-3.489923242655078</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.00055708326311</v>
+        <v>1.034593528478241</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.529390879642788</v>
+        <v>0.599950328650565</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.748553777639693</v>
+        <v>2.790889447044359</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.568503389078594</v>
+        <v>-3.483412276040766</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.000761431463152</v>
+        <v>1.034797876678283</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.529390879642788</v>
+        <v>0.599950328650565</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.74615373919401</v>
+        <v>2.788489408598676</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.549465261371297</v>
+        <v>-3.464374148333468</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.004901401754316</v>
+        <v>1.038937846969447</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4712072683115934</v>
+        <v>0.5417667173193704</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.707768291603538</v>
+        <v>2.750103961008204</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.580591892521915</v>
+        <v>-3.495500779484086</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.170032618232749</v>
+        <v>1.20406906344788</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4712072683115934</v>
+        <v>0.5417667173193704</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.885350160542218</v>
+        <v>2.927685829946885</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.594458653855832</v>
+        <v>-3.509367540818004</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.165319242685316</v>
+        <v>1.199355687900447</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4333493515777705</v>
+        <v>0.5039088005855474</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.863468739488058</v>
+        <v>2.905804408892724</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789119</v>
       </c>
       <c r="C1965" t="n">
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.549654482315902</v>
+        <v>-3.464563369278074</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.189249441698214</v>
+        <v>1.223285886913345</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4333493515777705</v>
+        <v>0.5039088005855474</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.869477269884984</v>
+        <v>2.91181293928965</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.4019115120809</v>
+        <v>-3.316820399043072</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.146296851069414</v>
+        <v>1.180333296284545</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6011567088126537</v>
+        <v>0.6717161578204306</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.868111905503114</v>
+        <v>2.91044757490778</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.503926194612121</v>
+        <v>-3.418835081574293</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.108284599588407</v>
+        <v>1.142321044803538</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6011567088126537</v>
+        <v>0.6717161578204306</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.870905527034595</v>
+        <v>2.913241196439261</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.497773488559337</v>
+        <v>-3.412682375521508</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.111408030401179</v>
+        <v>1.14544447561631</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.607309414865438</v>
+        <v>0.6778688638732149</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.875259499057924</v>
+        <v>2.91759516846259</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.514582786709838</v>
+        <v>-3.42949167367201</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.103764787881088</v>
+        <v>1.137801233096219</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5905001167149364</v>
+        <v>0.6610595657227132</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.864254396907733</v>
+        <v>2.906590066312399</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.452284787933716</v>
+        <v>-3.367193674895888</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.195019541188358</v>
+        <v>1.229055986403489</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5905001167149364</v>
+        <v>0.6610595657227132</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.930589950704554</v>
+        <v>2.97292562010922</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.250494590268558</v>
+        <v>-3.16540347723073</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.078027621968548</v>
+        <v>1.112064067183679</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7885183088840908</v>
+        <v>0.8590777578918676</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.851692867720173</v>
+        <v>2.894028537124839</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.085681587189711</v>
+        <v>-3.000590474151883</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.214243055522262</v>
+        <v>1.248279500737393</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9533313119629377</v>
+        <v>1.023890760970715</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.020870901889657</v>
+        <v>3.063206571294323</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.183422131814686</v>
+        <v>-3.098331018776857</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.189774573788316</v>
+        <v>1.223811019003447</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9374420338299576</v>
+        <v>1.008001482837734</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.025965071125913</v>
+        <v>3.068300740530578</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.359759891937615</v>
+        <v>-3.274668778899787</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.117775450563816</v>
+        <v>1.151811895778947</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7611042737070282</v>
+        <v>0.8316637227148049</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.918698395876826</v>
+        <v>2.961034065281492</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.283337845505688</v>
+        <v>-3.19824673246786</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.146835887176515</v>
+        <v>1.180872332391647</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7611042737070282</v>
+        <v>0.8316637227148049</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.917190013916755</v>
+        <v>2.959525683321421</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.238964713867119</v>
+        <v>-3.153873600829291</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.164448007267379</v>
+        <v>1.19848445248251</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8054774053455968</v>
+        <v>0.8760368543533735</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.943676760335332</v>
+        <v>2.986012429739998</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.116130492979952</v>
+        <v>-3.031039379942124</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.207975489760836</v>
+        <v>1.242011934975968</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8054774053455968</v>
+        <v>0.8760368543533735</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.938070554473923</v>
+        <v>2.980406223878589</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.068474762418896</v>
+        <v>-2.983383649381068</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.233419539013063</v>
+        <v>1.267455984228195</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8531331359066524</v>
+        <v>0.9236925849144292</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.973045749838361</v>
+        <v>3.015381419243027</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.967956603920141</v>
+        <v>-2.882865490882313</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.27851917578729</v>
+        <v>1.312555621002421</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.953651294405407</v>
+        <v>1.024210743413184</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.038249018312338</v>
+        <v>3.080584687717004</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.028623194322531</v>
+        <v>-2.943532081284702</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.241007212102207</v>
+        <v>1.275043657317338</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8719529776868733</v>
+        <v>0.9425124266946501</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.975984700757091</v>
+        <v>3.018320370161756</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932765</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.983784792714133</v>
+        <v>-2.898693679676304</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.263040275356194</v>
+        <v>1.297076720571326</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8764964106317428</v>
+        <v>0.9470558596395195</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.982808463134641</v>
+        <v>3.025144132539307</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917047</v>
       </c>
       <c r="C1982" t="n">
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.003283248956141</v>
+        <v>-2.918192135918313</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.259401832490469</v>
+        <v>1.293438277705601</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8284117693518385</v>
+        <v>0.8989712183596152</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.958118617997776</v>
+        <v>3.000454287402442</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405954</v>
       </c>
       <c r="C1983" t="n">
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.95908041187024</v>
+        <v>-2.873989298832412</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.282962569852667</v>
+        <v>1.316999015067798</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8726146064377389</v>
+        <v>0.9431740554455157</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.990519922777153</v>
+        <v>3.03285559218182</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265639</v>
       </c>
       <c r="C1984" t="n">
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.996059439533683</v>
+        <v>-2.910968326495855</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.266580959256537</v>
+        <v>1.300617404471668</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9095885082290694</v>
+        <v>0.9801479572368462</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.011114264321199</v>
+        <v>3.053449933725865</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.837768021994411</v>
+        <v>-2.752676908956583</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.381145291455285</v>
+        <v>1.415181736670417</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9095885082290694</v>
+        <v>0.9801479572368462</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.062362029504239</v>
+        <v>3.104697698908905</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.630126018359935</v>
+        <v>-2.545034905322107</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.462642797503329</v>
+        <v>1.49667924271846</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.117230511863545</v>
+        <v>1.187789960871322</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.185387936279178</v>
+        <v>3.227723605683844</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475134</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.579093925637407</v>
+        <v>-2.494002812599579</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.47800386283061</v>
+        <v>1.512040308045742</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.168262604586074</v>
+        <v>1.238822053593851</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.210955420150964</v>
+        <v>3.253291089555631</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404848</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.513869744510202</v>
+        <v>-2.428778631472373</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.521280939374197</v>
+        <v>1.555317384589328</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.233486785713279</v>
+        <v>1.304046234721056</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.267277332919993</v>
+        <v>3.309613002324659</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.476442724439068</v>
+        <v>-2.39135161140124</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.532212719701931</v>
+        <v>1.566249164917062</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.238738323742461</v>
+        <v>1.309297772750238</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.266389228036783</v>
+        <v>3.308724897441448</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992655</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.496554380473776</v>
+        <v>-2.411463267435948</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.525424849619288</v>
+        <v>1.559461294834419</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.24976566873988</v>
+        <v>1.320325117747657</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.274262427366474</v>
+        <v>3.31659809677114</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636282</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.442809566046571</v>
+        <v>-2.357718453008743</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.707480546411381</v>
+        <v>1.741516991626512</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.259828978180342</v>
+        <v>1.330388427188119</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.440858184051962</v>
+        <v>3.483193853456628</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.81322282095762</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.368027305021559</v>
+        <v>-2.282936191983731</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.857506360039203</v>
+        <v>1.891542805254334</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.334611239205355</v>
+        <v>1.405170688213132</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.605840449884787</v>
+        <v>3.648176119289453</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.341943220757751</v>
+        <v>-2.256852107719923</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.859647969758585</v>
+        <v>1.893684414973717</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.334611239205355</v>
+        <v>1.405170688213132</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.597548425898646</v>
+        <v>3.639884095303312</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896923</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.263812039908804</v>
+        <v>-2.178720926870976</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.889093637681944</v>
+        <v>1.923130082897075</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.40878805008904</v>
+        <v>1.479347499096817</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.640247708012636</v>
+        <v>3.682583377417302</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959853</v>
+        <v>3.796264143959851</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.254919578515521</v>
+        <v>-2.169828465477693</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.910205027966048</v>
+        <v>1.944241473181179</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.40878805008904</v>
+        <v>1.479347499096817</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.657802113739427</v>
+        <v>3.700137783144094</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945361</v>
+        <v>3.794424941945359</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.423395695485399</v>
+        <v>-2.338304582447571</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.834669628582681</v>
+        <v>1.868706073797812</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.380840214372459</v>
+        <v>1.451399663380236</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.632888459714063</v>
+        <v>3.675224129118729</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782704</v>
+        <v>3.795574066782702</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.725596166623816</v>
+        <v>-1.640505053585987</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.095059137315176</v>
+        <v>2.129095582530307</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.310492155002048</v>
+        <v>1.381051604009825</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.571949321279678</v>
+        <v>3.614284990684345</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632632</v>
+        <v>3.78467134563263</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.702875062940663</v>
+        <v>-1.617783949902835</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.094811601285341</v>
+        <v>2.128848046500473</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.310492155002048</v>
+        <v>1.381051604009825</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.562613343776583</v>
+        <v>3.604949013181249</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.701150019650619</v>
+        <v>-1.616058906612791</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.254407744452528</v>
+        <v>2.28844418966766</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.312217198292092</v>
+        <v>1.382776647299869</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.722554495601778</v>
+        <v>3.764890165006444</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.855931026428875</v>
+        <v>-1.770839913391046</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.229573164234873</v>
+        <v>2.263609609450004</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.278849524237616</v>
+        <v>1.349408973245393</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.739611713662739</v>
+        <v>3.781947383067406</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.848876336213701</v>
+        <v>-1.763785223175873</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.229070396310487</v>
+        <v>2.263106841525619</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.285904214452789</v>
+        <v>1.356463663460566</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.740519883781388</v>
+        <v>3.782855553186055</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.76667349633111</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.821925111887213</v>
+        <v>-1.736833998849385</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.249857039685824</v>
+        <v>2.283893484900955</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.300784560480509</v>
+        <v>1.371344009488286</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.759454245042762</v>
+        <v>3.801789914447428</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.957878119943529</v>
+        <v>-1.872787006905701</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.379578968608257</v>
+        <v>2.413615413823389</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.300784560480509</v>
+        <v>1.371344009488286</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.943557377187721</v>
+        <v>3.985893046592388</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.980286237748401</v>
+        <v>-1.895195124710573</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.362732416389302</v>
+        <v>2.396768861604433</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.300784560480509</v>
+        <v>1.371344009488286</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.935674072090714</v>
+        <v>3.978009741495381</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.1282920052278</v>
+        <v>-2.043200892189972</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.305584108947179</v>
+        <v>2.33962055416231</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.214057551616967</v>
+        <v>1.284617000624744</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.885691866322227</v>
+        <v>3.928027535726893</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.13773293111633</v>
+        <v>-2.052641818078502</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.358061456313614</v>
+        <v>2.392097901528746</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.336484669160359</v>
+        <v>1.407044118168136</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.01540185457011</v>
+        <v>4.057737523974775</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.190006538451972</v>
+        <v>-2.104915425414144</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.340043107924659</v>
+        <v>2.37407955313979</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.284211061824717</v>
+        <v>1.354770510832494</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.986928784714025</v>
+        <v>4.029264454118691</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.266336516052878</v>
+        <v>-2.181245403015049</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.307622929778072</v>
+        <v>2.341659374993203</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.284211061824717</v>
+        <v>1.354770510832494</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.9850405976078</v>
+        <v>4.027376267012467</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887744</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.378093468668179</v>
+        <v>-2.29300235563035</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.257740378334813</v>
+        <v>2.291776823549945</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.172454109209416</v>
+        <v>1.243013558217193</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.912806655641482</v>
+        <v>3.955142325046149</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.376252449609928</v>
+        <v>-2.291161336572099</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.256910796168266</v>
+        <v>2.290947241383397</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.173722335880885</v>
+        <v>1.244281784888662</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.912001601854516</v>
+        <v>3.954337271259182</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647101</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.508553741707481</v>
+        <v>-2.423462628669653</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.217063686195163</v>
+        <v>2.251100131410295</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.173722335880885</v>
+        <v>1.244281784888662</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.925075008720434</v>
+        <v>3.9674106781251</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763528</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.510115384522341</v>
+        <v>-2.425024271484513</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.216439029069219</v>
+        <v>2.250475474284351</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.173722335880885</v>
+        <v>1.244281784888662</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.925075008720434</v>
+        <v>3.9674106781251</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392111</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.538016171631814</v>
+        <v>-2.452925058593986</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.203802755352432</v>
+        <v>2.237839200567564</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.13912541173795</v>
+        <v>1.209684860745727</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.902840895361675</v>
+        <v>3.945176564766341</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172522</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.660542274334708</v>
+        <v>-2.57545116129688</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.151556758248473</v>
+        <v>2.185593203463605</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.016599309035056</v>
+        <v>1.087158758042833</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.826089677717138</v>
+        <v>3.868425347121804</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971075</v>
+        <v>3.619362241971074</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.680603595611215</v>
+        <v>-2.595512482573386</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.210238189328375</v>
+        <v>2.244274634543506</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.996537987758549</v>
+        <v>1.067097436766326</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.880758844541737</v>
+        <v>3.923094513946404</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199802</v>
+        <v>3.6407642481998</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.043884217714658</v>
+        <v>-2.85223330056821</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.205237659488844</v>
+        <v>2.281898026347423</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8605332425646113</v>
+        <v>0.9586828626225111</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.939467716427222</v>
+        <v>3.998357488461961</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622232</v>
+        <v>3.66830316462223</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.197870635490798</v>
+        <v>-3.006219718344351</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.212623361524028</v>
+        <v>2.289283728382607</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8605332425646113</v>
+        <v>0.9586828626225111</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.008447985572861</v>
+        <v>4.067337757607602</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808524</v>
+        <v>3.619937176808523</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.147348731663132</v>
+        <v>-2.955697814516685</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.218883325175215</v>
+        <v>2.295543692033794</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8605332425646113</v>
+        <v>0.9586828626225111</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.994499187692982</v>
+        <v>4.053388959727722</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994891</v>
+        <v>3.656346893994889</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.399823885670857</v>
+        <v>-3.208172968524409</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.129763752627539</v>
+        <v>2.206424119486118</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8605332425646113</v>
+        <v>0.9586828626225111</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.006369676748396</v>
+        <v>4.065259448783136</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358295</v>
+        <v>3.674042696358293</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.669296687592565</v>
+        <v>-3.477645770446117</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.023185166377799</v>
+        <v>2.099845533236379</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8605332425646113</v>
+        <v>0.9586828626225111</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.00758021126734</v>
+        <v>4.066469983302079</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637083</v>
+        <v>3.663523617637082</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.826840759322006</v>
+        <v>-3.635189842175559</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.964289279913344</v>
+        <v>2.040949646771923</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7936314374243367</v>
+        <v>0.8917810574822367</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.971560870410497</v>
+        <v>4.030450642445237</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.65216331330134</v>
+        <v>3.652163313301338</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.955691310024053</v>
+        <v>-3.764040392877605</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.907826912368715</v>
+        <v>1.984487279227294</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7526380285736152</v>
+        <v>0.8507876486315151</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.942042677836254</v>
+        <v>4.000932449870994</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215467</v>
+        <v>3.667976467215465</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.072659002662944</v>
+        <v>-3.881008085516496</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.023243892012203</v>
+        <v>2.099904258870782</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7526380285736152</v>
+        <v>0.8507876486315151</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.104246734535297</v>
+        <v>4.163136506570037</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456689</v>
+        <v>3.696553628456687</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.157376944883898</v>
+        <v>-3.96572602773745</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.984203353087636</v>
+        <v>2.060863719946215</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6675219996455688</v>
+        <v>0.7656716197034688</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.048023755142284</v>
+        <v>4.106913527177023</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253285</v>
+        <v>3.750058176253283</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.239311763152781</v>
+        <v>-4.047660846006333</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.961658843348574</v>
+        <v>2.038319210207153</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.6575872540584886</v>
+        <v>0.7557368741163886</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.052292325358526</v>
+        <v>4.111182097393266</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717829</v>
+        <v>3.783647027717827</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.185573589752519</v>
+        <v>-3.993922672606071</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.992079751164581</v>
+        <v>2.06874011802316</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.7113254274587507</v>
+        <v>0.8094750475166507</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.093460867854587</v>
+        <v>4.152350639889327</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.798310944616944</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.075567306275297</v>
+        <v>-3.883916389128849</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.028235151799645</v>
+        <v>2.104895518658224</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.7345299993760259</v>
+        <v>0.8326796194339259</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.099536498249127</v>
+        <v>4.158426270283867</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203659</v>
+        <v>3.785578085203658</v>
       </c>
       <c r="C2028" t="n">
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.932507730534371</v>
+        <v>-3.740856813387924</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.089708992817989</v>
+        <v>2.166369359676569</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.7425434259660052</v>
+        <v>0.8406930460239052</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.108594564925089</v>
+        <v>4.167484336959829</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436925</v>
+        <v>3.777251572436923</v>
       </c>
       <c r="C2029" t="n">
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.631061005062534</v>
+        <v>-3.439410087916086</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.217548565889261</v>
+        <v>2.294208932747839</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.043990151437842</v>
+        <v>1.142139771495742</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.296723483090727</v>
+        <v>4.355613255125467</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064759</v>
+        <v>3.812650101064758</v>
       </c>
       <c r="C2030" t="n">
         <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.686016201505603</v>
+        <v>-3.494365284359155</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.196537665064743</v>
+        <v>2.273198031923322</v>
       </c>
       <c r="F2030" t="n">
-        <v>1.043990151437842</v>
+        <v>1.142139771495742</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.297694660843438</v>
+        <v>4.356584432878178</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.454914447480782</v>
+        <v>3.87538995872669</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.442936457994066</v>
+        <v>3.473310207915459</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.686016201505603</v>
+        <v>-3.494365284359155</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.196537665064743</v>
+        <v>2.273198031923322</v>
       </c>
       <c r="F2031" t="n">
-        <v>1.043990151437842</v>
+        <v>1.142139771495742</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.436000254980434</v>
+        <v>3.466374004901827</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240720.xlsx
+++ b/tame_output/ON/bt/strategyON_20240720.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>52.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>47.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.4%</t>
+          <t>122.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-637.5%</t>
+          <t>-644.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-48.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.0%</t>
+          <t>-66.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.7%</t>
+          <t>457.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-511.0%</t>
+          <t>-499.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-255.4%</t>
+          <t>-258.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>183.7%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-148.9%</t>
+          <t>-144.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-256.7%</t>
+          <t>-263.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-124.3%</t>
+          <t>-132.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-109.8%</t>
+          <t>-117.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,15 +1443,15 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-154.4%</t>
+          <t>-158.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,32 +1471,32 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-87.2%</t>
         </is>
       </c>
     </row>
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153003</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.057194209571815</v>
+        <v>-1.127753658579592</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.693846341808556</v>
+        <v>2.665622562205445</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.058621031690461</v>
+        <v>0.9880615826826838</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.752253068965306</v>
+        <v>3.70991739956064</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.347325876177246</v>
+        <v>-1.417885325185023</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.577659891765305</v>
+        <v>2.549436112162195</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.082702826430641</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.766568362408336</v>
+        <v>3.72423269300367</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.555329934530324</v>
+        <v>-1.625889383538101</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.499350412978</v>
+        <v>2.471126633374889</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.082702826430641</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.771460506962261</v>
+        <v>3.729124837557595</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074619</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.617508345691294</v>
+        <v>-1.688067794699071</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.4695605048516</v>
+        <v>2.441336725248489</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.020524415269671</v>
+        <v>0.9499649662618935</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.729234916603667</v>
+        <v>3.686899247199001</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.983577072835946</v>
+        <v>-2.054136521843724</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.316217313300188</v>
+        <v>2.287993533697077</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.654455688125018</v>
+        <v>0.5838962391172409</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.502677979623325</v>
+        <v>3.460342310218659</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.192067854287631</v>
+        <v>-2.262627303295408</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.253159290458282</v>
+        <v>2.224935510855171</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4459649066733335</v>
+        <v>0.3754054576655564</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.397921800491083</v>
+        <v>3.355586131086416</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.439269039052852</v>
+        <v>-2.50982848806063</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.162377566960762</v>
+        <v>2.134153787357651</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.466118260172146</v>
+        <v>0.3955588111643689</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.418112562998938</v>
+        <v>3.375776893594272</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.931654067076949</v>
+        <v>-3.002213516084727</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.966529947794855</v>
+        <v>1.938306168191745</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.02626676785195076</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.123787938228213</v>
+        <v>3.081452268823546</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.316834458007022</v>
+        <v>-3.387393907014799</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.81100033023569</v>
+        <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.02626676785195076</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.122330477041076</v>
+        <v>3.079994807636409</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.566705138021603</v>
+        <v>-3.637264587029381</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.712821181684473</v>
+        <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.009995951978512496</v>
+        <v>-0.06056349702926461</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.14585723239397</v>
+        <v>3.103521562989304</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.773216914908625</v>
+        <v>-3.843776363916402</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.626322529585923</v>
+        <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.196515824908509</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.018056224918015</v>
+        <v>2.975720555513349</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.092560989989126</v>
+        <v>-4.163120438996904</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.500357826253981</v>
+        <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.196515824908509</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.019829151618274</v>
+        <v>2.977493482213608</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.524366783138913</v>
+        <v>-4.594926232146691</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.313968396461471</v>
+        <v>1.28574461685836</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.332933321349776</v>
+        <v>-0.4034927703575531</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.924311541220919</v>
+        <v>2.881975871816252</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.759060777271466</v>
+        <v>-4.829620226279244</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.208375573810541</v>
+        <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3265970541205208</v>
+        <v>-0.3971565031282979</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.916398076560562</v>
+        <v>2.874062407155896</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.094723424501918</v>
+        <v>-5.165282873509696</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.072691106574325</v>
+        <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.3945280396094256</v>
+        <v>-0.4650874886172027</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.874220076923184</v>
+        <v>2.831884407518518</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.17116775470479</v>
+        <v>-5.241727203712568</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.048600934727418</v>
+        <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3140825305157637</v>
+        <v>-0.3846419795235408</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.928974942613623</v>
+        <v>2.886639273208957</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.536295137343537</v>
+        <v>-5.606854586351314</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.9018044966777503</v>
+        <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6103933148147762</v>
+        <v>-0.6809527638225534</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.750442987040047</v>
+        <v>2.708107317635381</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.944883914524214</v>
+        <v>-6.015443363531993</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7371305298202384</v>
+        <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.018982091995455</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.504051264746399</v>
+        <v>2.461715595341733</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.058644326547079</v>
+        <v>-6.129203775554858</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6868117974825529</v>
+        <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.018982091995455</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.49923669721786</v>
+        <v>2.456901027813193</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.475036200834077</v>
+        <v>-6.545595649841855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.5182490983766312</v>
+        <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.018982091995455</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.497230747826737</v>
+        <v>2.454895078422071</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.719307601561146</v>
+        <v>-6.789867050568925</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4307992287544824</v>
+        <v>0.4025754491513713</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.018982091995455</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.507489438495416</v>
+        <v>2.46515376909075</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.924558620797907</v>
+        <v>-6.995118069805685</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3447983862054733</v>
+        <v>0.3165746066023623</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.018982091995455</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.503589003641111</v>
+        <v>2.461253334236445</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.972761438040251</v>
+        <v>-7.043320887048029</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.323922179363537</v>
+        <v>0.2956983997604259</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.018982091995455</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.501993923696112</v>
+        <v>2.459658254291446</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.269422779850448</v>
+        <v>-7.339982228858227</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2090366185686663</v>
+        <v>0.1808128389655548</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.087725227729333</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.464527018184993</v>
+        <v>2.422191348780327</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.456142488159751</v>
+        <v>-7.526701937167529</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1303224307105419</v>
+        <v>0.1020986511074309</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.087725227729333</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.46050071365059</v>
+        <v>2.418165044245924</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.839143876902382</v>
+        <v>-7.909703325910161</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.02298022610809447</v>
+        <v>-0.05120400571120598</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.087725227729333</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.460398612329006</v>
+        <v>2.41806294292434</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.84363032210377</v>
+        <v>-7.914189771111549</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.02220328821722006</v>
+        <v>-0.05042706782033113</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.092211672930722</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.460278261179603</v>
+        <v>2.417942591774937</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.203160644607774</v>
+        <v>-8.273720093615552</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1606651139207709</v>
+        <v>-0.1888888935238819</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.092211672930722</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.465628564477653</v>
+        <v>2.423292895072987</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.253509708061996</v>
+        <v>-8.324069157069774</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1728887193452819</v>
+        <v>-0.2011124989483934</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.142560736384944</v>
+        <v>-1.213120185392721</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.443335146362298</v>
+        <v>2.400999476957631</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.351128985483392</v>
+        <v>-8.42168843449117</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2088946796920719</v>
+        <v>-0.2371184592951829</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.240180013806341</v>
+        <v>-1.310739462814118</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.387805330531228</v>
+        <v>2.345469661126562</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.405200484991751</v>
+        <v>-8.475759933999528</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2276297231738429</v>
+        <v>-0.255853502776954</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.2942515133147</v>
+        <v>-1.364810962322477</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.358255987147785</v>
+        <v>2.315920317743119</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.609458660321614</v>
+        <v>-8.680018109329392</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3038197961871463</v>
+        <v>-0.3320435757902573</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.421890457928689</v>
+        <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.287185817498034</v>
+        <v>2.244850148093368</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.643111498830088</v>
+        <v>-8.713670947837866</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3127983771060996</v>
+        <v>-0.3410221567092107</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.522303825845726</v>
+        <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.231420351232248</v>
+        <v>2.189084681827581</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.569641667162639</v>
+        <v>-8.640201116170417</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2680387429456985</v>
+        <v>-0.29626252254881</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.448833994178278</v>
+        <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.290873951726138</v>
+        <v>2.248538282321471</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.744766084549182</v>
+        <v>-8.81532553355696</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3235332891527993</v>
+        <v>-0.3517570687559104</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.623958411564822</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.200354522041728</v>
+        <v>2.158018852637062</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.979218178563672</v>
+        <v>-9.04977762757145</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4245332916601909</v>
+        <v>-0.4527570712633024</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.623958411564822</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.193135357140132</v>
+        <v>2.150799687735466</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.083592909590118</v>
+        <v>-9.154152358597896</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4729553748447457</v>
+        <v>-0.5011791544478572</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.728333142591268</v>
+        <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.123838327750288</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.136379065190445</v>
+        <v>-9.206938514198223</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4929540472463203</v>
+        <v>-0.5211778268494314</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.824008629173665</v>
+        <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.067548825639407</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.262415858558734</v>
+        <v>-9.332975307566512</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5406750359645214</v>
+        <v>-0.5688988155676324</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.798757006363922</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.085393527954366</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.205344086662803</v>
+        <v>-9.275903535670581</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.513855991519748</v>
+        <v>-0.5420797711228591</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.798757006363922</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.089383863640768</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.347015928386924</v>
+        <v>-9.417575377394702</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5719999551081378</v>
+        <v>-0.6002237347112489</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.798757006363922</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.087908636742026</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.297425083962089</v>
+        <v>-9.367984532969867</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.537110207173332</v>
+        <v>-0.5653339867764431</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.749166161939089</v>
+        <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.132716553561798</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.148506749490233</v>
+        <v>-9.219066198498011</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4905940070312722</v>
+        <v>-0.5188177866343833</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.717916571203915</v>
+        <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.138415174356219</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.922661596770823</v>
+        <v>-8.993221045778601</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3906768729072998</v>
+        <v>-0.4189006525104109</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.675989895616752</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.173150252744726</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.798082940433231</v>
+        <v>-8.868642389441009</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3397062658162038</v>
+        <v>-0.3679300454193153</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.675989895616752</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.174289397300785</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.850978228477517</v>
+        <v>-8.921537677485295</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3582306068718109</v>
+        <v>-0.3864543864749219</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.671034549528306</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.17989637911596</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.778845053189636</v>
+        <v>-8.849404502197414</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3236436325180221</v>
+        <v>-0.3518674121211331</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.671034549528306</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.185630083354597</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.707478660579989</v>
+        <v>-8.778038109587767</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3048343378680283</v>
+        <v>-0.3330581174711393</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.599668156918658</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.21871265652652</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.614019626594764</v>
+        <v>-8.684579075602542</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.277334205586846</v>
+        <v>-0.305557985189957</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.599668156918658</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.208829175213613</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.346777825726367</v>
+        <v>-8.417337274734145</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1722720457388607</v>
+        <v>-0.2004958253419717</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.599668156918658</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.206994614714239</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.248870787049876</v>
+        <v>-8.319430236057654</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1334095452417254</v>
+        <v>-0.1616333248448365</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.531682407058101</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.247485749657112</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097243</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.224917246073918</v>
+        <v>-8.295476695081696</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1231596227058485</v>
+        <v>-0.1513834023089595</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.507728866082144</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.26252638038818</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.960857307751122</v>
+        <v>-8.031416756758899</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.03079596353848224</v>
+        <v>-0.05901974314159286</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.243668927759348</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.407702027220106</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.253777684246284</v>
+        <v>-7.324337133254061</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2492488522031522</v>
+        <v>0.2210250726000416</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.243668927759348</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.404914993559805</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.213593385880094</v>
+        <v>-7.284152834887871</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2656661954374697</v>
+        <v>0.2374424158343591</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.203484629393157</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.429369196467361</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626474</v>
+        <v>3.856161751626473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.050193514940731</v>
+        <v>-7.120752963948508</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3303929650339716</v>
+        <v>0.302169185430861</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.040084758453794</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.526775940251735</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.816712292711133</v>
+        <v>-6.88727174171891</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4317098827636636</v>
+        <v>0.4034861031605526</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8066035362241957</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.674789102427347</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.667045901703617</v>
+        <v>-6.737605350711394</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4886842288537103</v>
+        <v>0.4604604492505997</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7137000449816597</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.727638986859909</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.534770428072731</v>
+        <v>-6.605329877080508</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5369619050530918</v>
+        <v>0.5087381254499812</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5814245713507731</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.802371757785468</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.379032095512989</v>
+        <v>-6.449591544520766</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.6020722987646252</v>
+        <v>0.5738485191615146</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4256862387910315</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.89862981800895</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.130032296829408</v>
+        <v>-6.200591745837185</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.7145785594617164</v>
+        <v>0.6863547798586058</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4256862387910315</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.911536159232608</v>
+        <v>2.869200489827942</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.235622286602513</v>
+        <v>-6.30618173561029</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5443666339532562</v>
+        <v>0.5161428543501452</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.5312762285641359</v>
+        <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.720206235769527</v>
+        <v>2.677870566364861</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.25435718872111</v>
+        <v>-6.324916637728887</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5854170149829034</v>
+        <v>0.5571932353797928</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.5368722382242672</v>
+        <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.765392971850535</v>
+        <v>2.723057302445869</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.10641714731351</v>
+        <v>-6.176976596321287</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.5247141088577756</v>
+        <v>0.496490329254665</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5165513223157097</v>
+        <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.657706598707501</v>
+        <v>2.615370929302836</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.053447625059522</v>
+        <v>-6.124007074067299</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5371879315058932</v>
+        <v>0.5089641519027821</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.4635818000617208</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.680774325806417</v>
+        <v>2.638438656401751</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098113</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.009899218288831</v>
+        <v>-6.080458667296608</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5476466821190762</v>
+        <v>0.5194229025159651</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.4635818000617208</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.673813713711324</v>
+        <v>2.631478044306657</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493424</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.976536011810063</v>
+        <v>-6.04709546081784</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5754543190917265</v>
+        <v>0.5472305394886159</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.4635818000617208</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.688276068092467</v>
+        <v>2.645940398687801</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.82855148672282</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.868276874687541</v>
+        <v>-5.938836323695318</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6132900943999302</v>
+        <v>0.5850663147968196</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.4635818000617208</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.682808188551662</v>
+        <v>2.640472519146996</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.74498573987041</v>
+        <v>-5.815545188878187</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6601046423373598</v>
+        <v>0.6318808627342487</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.3402906652445903</v>
+        <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.754280963452517</v>
+        <v>2.711945294047851</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919909</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.723836540966967</v>
+        <v>-5.794395989974744</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6762653001360621</v>
+        <v>0.6480415205329515</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3191414663411469</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.774671461031908</v>
+        <v>2.732335791627242</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318095</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.480071098983522</v>
+        <v>-5.550630547991299</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7695521852764906</v>
+        <v>0.7413284056733795</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3191414663411469</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.770452169378959</v>
+        <v>2.728116499974293</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.378308278706228</v>
+        <v>-5.448867727714005</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.8123816273074245</v>
+        <v>0.7841578477043138</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3059223979487182</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.780507924334432</v>
+        <v>2.738172254929766</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.128457884757153</v>
+        <v>-5.19901733376493</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.9050638598707565</v>
+        <v>0.8768400802676455</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3059223979487182</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.773249999318134</v>
+        <v>2.730914329913468</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.95256579228972</v>
+        <v>-5.023125241297498</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9790198203783784</v>
+        <v>0.9507960407752671</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3059223979487182</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.776849122838783</v>
+        <v>2.734513453434117</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.781119329267256</v>
+        <v>-4.851678778275034</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.060925911641917</v>
+        <v>1.032702132038806</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.1344759349262551</v>
+        <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.893044506706814</v>
+        <v>2.850708837302149</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.706829763528917</v>
+        <v>-4.777389212536695</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.08966221555355</v>
+        <v>1.061438435950439</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.06018636918791581</v>
+        <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.936638723766115</v>
+        <v>2.894303054361449</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.643194021294983</v>
+        <v>-4.713753470302761</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.119811313501441</v>
+        <v>1.09158753389833</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.003449373046018722</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.979514970160793</v>
+        <v>2.937179300756127</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.531767261969063</v>
+        <v>-4.602326710976841</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.145576276015605</v>
+        <v>1.117352496412494</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.003449373046018722</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.960709228944589</v>
+        <v>2.918373559539923</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.291336765164202</v>
+        <v>-4.36189621417198</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.243491551362426</v>
+        <v>1.215267771759315</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.243879869850879</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.106710603652382</v>
+        <v>3.064374934247716</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.219094196993008</v>
+        <v>-4.289653646000786</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.276317892465724</v>
+        <v>1.248094112862613</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.243879869850879</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.110639917487203</v>
+        <v>3.068304248082536</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.16609587471162</v>
+        <v>-4.236655323719398</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.29819580529562</v>
+        <v>1.269972025692508</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2992161288528178</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.144520256805706</v>
+        <v>3.10218458740104</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.057290989231893</v>
+        <v>-4.127850438239671</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.338715830707504</v>
+        <v>1.310492051104393</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2992161288528178</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.141518328025699</v>
+        <v>3.099182658621033</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.837270191194882</v>
+        <v>-3.90782964020266</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.428303186932922</v>
+        <v>1.400079407329811</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4404359739207981</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.227829272077102</v>
+        <v>3.185493602672435</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.704402502131604</v>
+        <v>-3.774961951139382</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.497344445360057</v>
+        <v>1.469120665756946</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4404359739207981</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.243723454878925</v>
+        <v>3.201387785474259</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.584229418767105</v>
+        <v>-3.654788867774883</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.546559523146158</v>
+        <v>1.518335743543047</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5606090572852971</v>
+        <v>0.4900496082775201</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.316973149337926</v>
+        <v>3.27463747993326</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.439557273667368</v>
+        <v>-3.510116722675146</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.614516483747493</v>
+        <v>1.586292704144382</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7052812023850346</v>
+        <v>0.6347217533772576</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.413864538959209</v>
+        <v>3.371528869554542</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.49943210102506</v>
+        <v>-3.569991550032838</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.576604044205842</v>
+        <v>1.548380264602731</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6454063750273424</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.363977133946019</v>
+        <v>3.321641464541353</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.379611870114223</v>
+        <v>-3.450171319122</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.639821305804386</v>
+        <v>1.611597526201274</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6454063750273424</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.379266303180227</v>
+        <v>3.336930633775562</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.382081576576029</v>
+        <v>-3.452641025583806</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.546477622542105</v>
+        <v>1.518253842938994</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6429366685655362</v>
+        <v>0.5723772195577592</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.285428678625586</v>
+        <v>3.243093009220919</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.450451762900038</v>
+        <v>-3.521011211907816</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.438391409497802</v>
+        <v>1.410167629894691</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6522123676017512</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.210255959532616</v>
+        <v>3.16792029012795</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.464239815747085</v>
+        <v>-3.534799264754863</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.423312896990875</v>
+        <v>1.395089117387764</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6522123676017512</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.200692668164507</v>
+        <v>3.158356998759841</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.49523297507579</v>
+        <v>-3.565792424083568</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.235625198299779</v>
+        <v>1.207401418696668</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6522123676017512</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.025402233204894</v>
+        <v>2.983066563800228</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.319758715283321</v>
+        <v>-3.390318164291099</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.310382134208555</v>
+        <v>1.282158354605444</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6522123676017512</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.029969465196682</v>
+        <v>2.987633795792016</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.43069496792457</v>
+        <v>-3.501254416932348</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.241749661913263</v>
+        <v>1.213525882310151</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6522123676017512</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.005711493957889</v>
+        <v>2.963375824553223</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.397031422452288</v>
+        <v>-3.467590871460066</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.183753393503625</v>
+        <v>1.155529613900514</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6858759130740331</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.954447934642708</v>
+        <v>2.912112265238041</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.337178803248565</v>
+        <v>-3.407738252256343</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.217866827617247</v>
+        <v>1.189643048014136</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6858759130740331</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.96462032107484</v>
+        <v>2.922284651670174</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.250935340222187</v>
+        <v>-3.321494789229965</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.247310483401658</v>
+        <v>1.219086703798547</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6858759130740331</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.9595665916487</v>
+        <v>2.917230922244034</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.296242159621167</v>
+        <v>-3.366801608628945</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.220963531086592</v>
+        <v>1.19273975148348</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6450657500648023</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.926856269287687</v>
+        <v>2.884520599883021</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.325275264323469</v>
+        <v>-3.395834713331247</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.209902162238772</v>
+        <v>1.181678382635661</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6450657500648023</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.927408142320789</v>
+        <v>2.885072472916123</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.23246478287261</v>
+        <v>-3.303024231880388</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.176299046710482</v>
+        <v>1.148075267107371</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7378762315156616</v>
+        <v>0.6673167825078846</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.91236712308267</v>
+        <v>2.870031453678004</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.276854252202037</v>
+        <v>-3.347413701209815</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.160416734903312</v>
+        <v>1.132192955300201</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.693486762186234</v>
+        <v>0.622927313178457</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.887606917409614</v>
+        <v>2.845271248004948</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.164183033965787</v>
+        <v>-3.234742482973565</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.200560930709535</v>
+        <v>1.172337151106424</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.8061579804224841</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.950285356863088</v>
+        <v>2.907949687458421</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798538</v>
       </c>
       <c r="C1949" t="n">
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.242503187301583</v>
+        <v>-3.122365481790892</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.174724165205884</v>
+        <v>1.22277924741016</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.8061579804224841</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.955776652693755</v>
+        <v>2.913440983289088</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498866</v>
       </c>
       <c r="C1950" t="n">
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.270283585202936</v>
+        <v>-3.150145879692245</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.175109207813881</v>
+        <v>1.223164290018158</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.778377582521131</v>
+        <v>0.707818133513354</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.950605615721482</v>
+        <v>2.908269946316816</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.353284866228215</v>
+        <v>-3.233147160717524</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9802644154044229</v>
+        <v>1.028319497608699</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7598066979939573</v>
+        <v>0.6892472489861803</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.777818805005831</v>
+        <v>2.735483135601165</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.461898944671546</v>
+        <v>-3.341761239160856</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.056968444746296</v>
+        <v>1.105023526950573</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7598066979939573</v>
+        <v>0.6892472489861803</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.897968465725037</v>
+        <v>2.85563279632037</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.426489906423404</v>
+        <v>-3.306352200912713</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.085645086147876</v>
+        <v>1.133700168352153</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7598066979939573</v>
+        <v>0.6892472489861803</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.91248149182736</v>
+        <v>2.870145822422693</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.388106243865252</v>
+        <v>-3.267968538354562</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.098417992513505</v>
+        <v>1.146473074717782</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7981903605521085</v>
+        <v>0.7276309115443315</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.932931130704619</v>
+        <v>2.890595461299953</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.210989913830086</v>
+        <v>-3.090852208319395</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.165993553372874</v>
+        <v>1.21404863557715</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7981903605521085</v>
+        <v>0.7276309115443315</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.929660159549921</v>
+        <v>2.887324490145255</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.256082158663632</v>
+        <v>-3.135944453152941</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.148640047201369</v>
+        <v>1.196695129405645</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.7362943173827187</v>
+        <v>0.6657348683749417</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.8932059254102</v>
+        <v>2.850870256005534</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.076706737424864</v>
+        <v>-2.956569031914174</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.21417719100329</v>
+        <v>1.262232273207566</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8930710755534373</v>
+        <v>0.8225116265456603</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.981058955619046</v>
+        <v>2.93872328621438</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.12172095094547</v>
+        <v>-3.00158324543478</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.176978960926637</v>
+        <v>1.225034043130914</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.8627221802388327</v>
+        <v>0.7921627312310557</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.943657073761873</v>
+        <v>2.901321404357207</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.388725461217906</v>
+        <v>-3.268587755707215</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.075868719156609</v>
+        <v>1.123923801360885</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6683591421958841</v>
+        <v>0.5977996931881071</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.832730813275049</v>
+        <v>2.790395143870383</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.489923242655078</v>
+        <v>-3.369785537144388</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.034593528478241</v>
+        <v>1.082648610682517</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.599950328650565</v>
+        <v>0.529390879642788</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.790889447044359</v>
+        <v>2.748553777639693</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.483412276040766</v>
+        <v>-3.363274570530075</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.034797876678283</v>
+        <v>1.082852958882559</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.599950328650565</v>
+        <v>0.529390879642788</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.788489408598676</v>
+        <v>2.74615373919401</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.464374148333468</v>
+        <v>-3.344236442822778</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.038937846969447</v>
+        <v>1.086992929173723</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.5417667173193704</v>
+        <v>0.4712072683115934</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.750103961008204</v>
+        <v>2.707768291603538</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.495500779484086</v>
+        <v>-3.375363073973396</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.20406906344788</v>
+        <v>1.252124145652157</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.5417667173193704</v>
+        <v>0.4712072683115934</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.927685829946885</v>
+        <v>2.885350160542218</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.509367540818004</v>
+        <v>-3.497943782118395</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.199355687900447</v>
+        <v>1.20392519138029</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5039088005855474</v>
+        <v>0.4303109421951324</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.905804408892724</v>
+        <v>2.861645693858475</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789119</v>
+        <v>3.787425580789126</v>
       </c>
       <c r="C1965" t="n">
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.464563369278074</v>
+        <v>-3.453139610578465</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.223285886913345</v>
+        <v>1.227855390393188</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5039088005855474</v>
+        <v>0.4303109421951324</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.91181293928965</v>
+        <v>2.867654224255401</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.316820399043072</v>
+        <v>-3.305396640343463</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.180333296284545</v>
+        <v>1.184902799764389</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6717161578204306</v>
+        <v>0.5981182994300156</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.91044757490778</v>
+        <v>2.866288859873531</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.418835081574293</v>
+        <v>-3.407411322874684</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.142321044803538</v>
+        <v>1.146890548283381</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6717161578204306</v>
+        <v>0.5981182994300156</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.913241196439261</v>
+        <v>2.869082481405012</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.412682375521508</v>
+        <v>-3.4012586168219</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.14544447561631</v>
+        <v>1.150013979096153</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6778688638732149</v>
+        <v>0.6042710054827999</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.91759516846259</v>
+        <v>2.873436453428341</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.42949167367201</v>
+        <v>-3.418067914972401</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.137801233096219</v>
+        <v>1.142370736576063</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.6610595657227132</v>
+        <v>0.5874617073322983</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.906590066312399</v>
+        <v>2.86243135127815</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.367193674895888</v>
+        <v>-3.355769916196279</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.229055986403489</v>
+        <v>1.233625489883333</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.6610595657227132</v>
+        <v>0.5874617073322983</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.97292562010922</v>
+        <v>2.928766905074971</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.16540347723073</v>
+        <v>-3.153979718531121</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.112064067183679</v>
+        <v>1.116633570663523</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.8590777578918676</v>
+        <v>0.7854798995014527</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.894028537124839</v>
+        <v>2.849869822090591</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.000590474151883</v>
+        <v>-2.989166715452274</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.248279500737393</v>
+        <v>1.252849004217237</v>
       </c>
       <c r="F1972" t="n">
-        <v>1.023890760970715</v>
+        <v>0.9502929025802996</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.063206571294323</v>
+        <v>3.019047856260074</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.098331018776857</v>
+        <v>-3.086907260077249</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.223811019003447</v>
+        <v>1.228380522483291</v>
       </c>
       <c r="F1973" t="n">
-        <v>1.008001482837734</v>
+        <v>0.9344036244473195</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.068300740530578</v>
+        <v>3.024142025496329</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.274668778899787</v>
+        <v>-3.263245020200178</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.151811895778947</v>
+        <v>1.156381399258791</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8316637227148049</v>
+        <v>0.75806586432439</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.961034065281492</v>
+        <v>2.916875350247243</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.19824673246786</v>
+        <v>-3.186822973768251</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.180872332391647</v>
+        <v>1.18544183587149</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8316637227148049</v>
+        <v>0.75806586432439</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.959525683321421</v>
+        <v>2.915366968287172</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316251</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.153873600829291</v>
+        <v>-3.142449842129682</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.19848445248251</v>
+        <v>1.203053955962354</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8760368543533735</v>
+        <v>0.8024389959629586</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.986012429739998</v>
+        <v>2.941853714705749</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.031039379942124</v>
+        <v>-3.019615621242515</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.242011934975968</v>
+        <v>1.246581438455811</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8760368543533735</v>
+        <v>0.8024389959629586</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.980406223878589</v>
+        <v>2.93624750884434</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.983383649381068</v>
+        <v>-2.971959890681459</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.267455984228195</v>
+        <v>1.272025487708038</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.9236925849144292</v>
+        <v>0.8500947265240143</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.015381419243027</v>
+        <v>2.971222704208778</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.882865490882313</v>
+        <v>-2.871441732182705</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.312555621002421</v>
+        <v>1.317125124482265</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.024210743413184</v>
+        <v>0.9506128850227689</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.080584687717004</v>
+        <v>3.036425972682756</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.943532081284702</v>
+        <v>-2.932108322585094</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.275043657317338</v>
+        <v>1.279613160797181</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9425124266946501</v>
+        <v>0.8689145683042352</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.018320370161756</v>
+        <v>2.974161655127507</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932765</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.898693679676304</v>
+        <v>-2.887269920976696</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.297076720571326</v>
+        <v>1.301646224051169</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.9470558596395195</v>
+        <v>0.8734580012491047</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.025144132539307</v>
+        <v>2.980985417505058</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917047</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.918192135918313</v>
+        <v>-2.906768377218704</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.293438277705601</v>
+        <v>1.298007781185444</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8989712183596152</v>
+        <v>0.8253733599692004</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.000454287402442</v>
+        <v>2.956295572368193</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405954</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.873989298832412</v>
+        <v>-2.862565540132803</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.316999015067798</v>
+        <v>1.321568518547641</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9431740554455157</v>
+        <v>0.8695761970551008</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.03285559218182</v>
+        <v>2.988696877147571</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265639</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.910968326495855</v>
+        <v>-2.899544567796247</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.300617404471668</v>
+        <v>1.305186907951511</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9801479572368462</v>
+        <v>0.9065500988464313</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.053449933725865</v>
+        <v>3.009291218691617</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284873</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.752676908956583</v>
+        <v>-2.741253150256974</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.415181736670417</v>
+        <v>1.41975124015026</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9801479572368462</v>
+        <v>0.9065500988464313</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.104697698908905</v>
+        <v>3.060538983874656</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321017</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.545034905322107</v>
+        <v>-2.533611146622498</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.49667924271846</v>
+        <v>1.501248746198304</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.187789960871322</v>
+        <v>1.114192102480907</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.227723605683844</v>
+        <v>3.183564890649595</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475134</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.494002812599579</v>
+        <v>-2.48257905389997</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.512040308045742</v>
+        <v>1.516609811525585</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.238822053593851</v>
+        <v>1.165224195203435</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.253291089555631</v>
+        <v>3.209132374521382</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404848</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.428778631472373</v>
+        <v>-2.417354872772765</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.555317384589328</v>
+        <v>1.559886888069172</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.304046234721056</v>
+        <v>1.230448376330641</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.309613002324659</v>
+        <v>3.26545428729041</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.39135161140124</v>
+        <v>-2.379927852701631</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.566249164917062</v>
+        <v>1.570818668396906</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.309297772750238</v>
+        <v>1.235699914359823</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.308724897441448</v>
+        <v>3.264566182407199</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992655</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.411463267435948</v>
+        <v>-2.400039508736339</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.559461294834419</v>
+        <v>1.564030798314263</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.320325117747657</v>
+        <v>1.246727259357242</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.31659809677114</v>
+        <v>3.272439381736891</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636282</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.357718453008743</v>
+        <v>-2.346294694309135</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.741516991626512</v>
+        <v>1.746086495106355</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.330388427188119</v>
+        <v>1.256790568797704</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.483193853456628</v>
+        <v>3.439035138422379</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095762</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.282936191983731</v>
+        <v>-2.271512433284122</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.891542805254334</v>
+        <v>1.896112308734178</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.405170688213132</v>
+        <v>1.331572829822717</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.648176119289453</v>
+        <v>3.604017404255204</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.256852107719923</v>
+        <v>-2.245428349020314</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.893684414973717</v>
+        <v>1.89825391845356</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.405170688213132</v>
+        <v>1.331572829822717</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.639884095303312</v>
+        <v>3.595725380269063</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896923</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.178720926870976</v>
+        <v>-2.167297168171367</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.923130082897075</v>
+        <v>1.927699586376918</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.479347499096817</v>
+        <v>1.405749640706401</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.682583377417302</v>
+        <v>3.638424662383053</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959851</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.169828465477693</v>
+        <v>-2.158404706778084</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.944241473181179</v>
+        <v>1.948810976661023</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.479347499096817</v>
+        <v>1.405749640706401</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.700137783144094</v>
+        <v>3.655979068109845</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945359</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.338304582447571</v>
+        <v>-2.326880823747962</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.868706073797812</v>
+        <v>1.873275577277655</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.451399663380236</v>
+        <v>1.377801804989821</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.675224129118729</v>
+        <v>3.63106541408448</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782702</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.640505053585987</v>
+        <v>-1.629081294886379</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.129095582530307</v>
+        <v>2.133665086010151</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.381051604009825</v>
+        <v>1.30745374561941</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.614284990684345</v>
+        <v>3.570126275650096</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.78467134563263</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.617783949902835</v>
+        <v>-1.606360191203226</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.128848046500473</v>
+        <v>2.133417549980316</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.381051604009825</v>
+        <v>1.30745374561941</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.604949013181249</v>
+        <v>3.560790298147</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.616058906612791</v>
+        <v>-1.604635147913182</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.28844418966766</v>
+        <v>2.293013693147503</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.382776647299869</v>
+        <v>1.309178788909454</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.764890165006444</v>
+        <v>3.720731449972195</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.770839913391046</v>
+        <v>-1.759416154691438</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.263609609450004</v>
+        <v>2.268179112929847</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.349408973245393</v>
+        <v>1.275811114854978</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.781947383067406</v>
+        <v>3.737788668033156</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799959</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.763785223175873</v>
+        <v>-1.752361464476264</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.263106841525619</v>
+        <v>2.267676345005462</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.356463663460566</v>
+        <v>1.282865805070151</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.782855553186055</v>
+        <v>3.738696838151806</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76667349633111</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.736833998849385</v>
+        <v>-1.725410240149776</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.283893484900955</v>
+        <v>2.288462988380799</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.371344009488286</v>
+        <v>1.297746151097871</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.801789914447428</v>
+        <v>3.757631199413179</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.872787006905701</v>
+        <v>-1.861363248206092</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.413615413823389</v>
+        <v>2.418184917303232</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.371344009488286</v>
+        <v>1.297746151097871</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.985893046592388</v>
+        <v>3.941734331558139</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.895195124710573</v>
+        <v>-1.883771366010964</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.396768861604433</v>
+        <v>2.401338365084277</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.371344009488286</v>
+        <v>1.297746151097871</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.978009741495381</v>
+        <v>3.933851026461132</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.043200892189972</v>
+        <v>-2.031777133490364</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.33962055416231</v>
+        <v>2.344190057642154</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.284617000624744</v>
+        <v>1.211019142234329</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.928027535726893</v>
+        <v>3.883868820692644</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.052641818078502</v>
+        <v>-2.041218059378894</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.392097901528746</v>
+        <v>2.396667405008589</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.407044118168136</v>
+        <v>1.333446259777721</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.057737523974775</v>
+        <v>4.013578808940526</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.104915425414144</v>
+        <v>-2.093491666714535</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.37407955313979</v>
+        <v>2.378649056619634</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.354770510832494</v>
+        <v>1.281172652442079</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.029264454118691</v>
+        <v>3.985105739084442</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.181245403015049</v>
+        <v>-2.169821644315441</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.341659374993203</v>
+        <v>2.346228878473046</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.354770510832494</v>
+        <v>1.281172652442079</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.027376267012467</v>
+        <v>3.983217551978218</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887744</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.29300235563035</v>
+        <v>-2.281578596930742</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.291776823549945</v>
+        <v>2.296346327029788</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.243013558217193</v>
+        <v>1.169415699826778</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.955142325046149</v>
+        <v>3.9109836100119</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.291161336572099</v>
+        <v>-2.279737577872491</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.290947241383397</v>
+        <v>2.295516744863241</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.244281784888662</v>
+        <v>1.170683926498246</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.954337271259182</v>
+        <v>3.910178556224932</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647101</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.423462628669653</v>
+        <v>-2.412038869970044</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.251100131410295</v>
+        <v>2.255669634890138</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.244281784888662</v>
+        <v>1.170683926498246</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.9674106781251</v>
+        <v>3.923251963090851</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763528</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.425024271484513</v>
+        <v>-2.413600512784904</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.250475474284351</v>
+        <v>2.255044977764194</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.244281784888662</v>
+        <v>1.170683926498246</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.9674106781251</v>
+        <v>3.923251963090851</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392111</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.452925058593986</v>
+        <v>-2.441501299894377</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.237839200567564</v>
+        <v>2.242408704047407</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.209684860745727</v>
+        <v>1.136087002355312</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.945176564766341</v>
+        <v>3.901017849732092</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172522</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.57545116129688</v>
+        <v>-2.564027402597271</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.185593203463605</v>
+        <v>2.190162706943448</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.087158758042833</v>
+        <v>1.013560899652418</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.868425347121804</v>
+        <v>3.824266632087555</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971074</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.595512482573386</v>
+        <v>-2.584088723873778</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.244274634543506</v>
+        <v>2.248844138023349</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.067097436766326</v>
+        <v>0.9934995783759109</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.923094513946404</v>
+        <v>3.878935798912154</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.6407642481998</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.85223330056821</v>
+        <v>-2.840809541868602</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.281898026347423</v>
+        <v>2.286467529827267</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.9586828626225111</v>
+        <v>0.885085004232096</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.998357488461961</v>
+        <v>3.954198773427713</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.66830316462223</v>
+        <v>3.668303164622236</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.006219718344351</v>
+        <v>-2.994795959644742</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.289283728382607</v>
+        <v>2.29385323186245</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.9586828626225111</v>
+        <v>0.885085004232096</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.067337757607602</v>
+        <v>4.023179042573352</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808523</v>
+        <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.955697814516685</v>
+        <v>-2.944274055817076</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.295543692033794</v>
+        <v>2.300113195513638</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.9586828626225111</v>
+        <v>0.885085004232096</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.053388959727722</v>
+        <v>4.009230244693473</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994889</v>
+        <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.208172968524409</v>
+        <v>-3.196749209824801</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.206424119486118</v>
+        <v>2.210993622965962</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.9586828626225111</v>
+        <v>0.885085004232096</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.065259448783136</v>
+        <v>4.021100733748887</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358293</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.477645770446117</v>
+        <v>-3.466222011746509</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.099845533236379</v>
+        <v>2.104415036716222</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.9586828626225111</v>
+        <v>0.885085004232096</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.066469983302079</v>
+        <v>4.022311268267831</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637082</v>
+        <v>3.663523617637086</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.635189842175559</v>
+        <v>-3.62376608347595</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.040949646771923</v>
+        <v>2.045519150251767</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.8917810574822367</v>
+        <v>0.8181831990918216</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.030450642445237</v>
+        <v>3.986291927410988</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301338</v>
+        <v>3.652163313301343</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.764040392877605</v>
+        <v>-3.752616634177997</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.984487279227294</v>
+        <v>1.989056782707138</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.8507876486315151</v>
+        <v>0.7771897902411</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.000932449870994</v>
+        <v>3.956773734836744</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215465</v>
+        <v>3.667976467215469</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.881008085516496</v>
+        <v>-3.869584326816887</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.099904258870782</v>
+        <v>2.104473762350626</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.8507876486315151</v>
+        <v>0.7771897902411</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.163136506570037</v>
+        <v>4.118977791535788</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456687</v>
+        <v>3.696553628456692</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.96572602773745</v>
+        <v>-3.954302269037841</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.060863719946215</v>
+        <v>2.065433223426059</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.7656716197034688</v>
+        <v>0.6920737613130536</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.106913527177023</v>
+        <v>4.062754812142774</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253283</v>
+        <v>3.750058176253288</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.047660846006333</v>
+        <v>-4.036237087306724</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.038319210207153</v>
+        <v>2.042888713686996</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.7557368741163886</v>
+        <v>0.6821390157259735</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.111182097393266</v>
+        <v>4.067023382359017</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717827</v>
+        <v>3.783647027717832</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.993922672606071</v>
+        <v>-3.982498913906462</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.06874011802316</v>
+        <v>2.073309621503004</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.8094750475166507</v>
+        <v>0.7358771891262356</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.152350639889327</v>
+        <v>4.108191924855078</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616944</v>
+        <v>3.798310944616948</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.883916389128849</v>
+        <v>-3.872492630429241</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.104895518658224</v>
+        <v>2.109465022138068</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.8326796194339259</v>
+        <v>0.7590817610435108</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.158426270283867</v>
+        <v>4.114267555249618</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203658</v>
+        <v>3.785578085203662</v>
       </c>
       <c r="C2028" t="n">
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.740856813387924</v>
+        <v>-3.729433054688315</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.166369359676569</v>
+        <v>2.170938863156412</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.8406930460239052</v>
+        <v>0.76709518763349</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.167484336959829</v>
+        <v>4.12332562192558</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436923</v>
+        <v>3.777251572436928</v>
       </c>
       <c r="C2029" t="n">
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.439410087916086</v>
+        <v>-3.427986329216478</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.294208932747839</v>
+        <v>2.298778436227683</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.142139771495742</v>
+        <v>1.068541913105327</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.355613255125467</v>
+        <v>4.311454540091218</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064758</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
         <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.494365284359155</v>
+        <v>-3.382248057783906</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.273198031923322</v>
+        <v>2.318044922553422</v>
       </c>
       <c r="F2030" t="n">
-        <v>1.142139771495742</v>
+        <v>1.068541913105327</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.356584432878178</v>
+        <v>4.312425717843928</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.87538995872669</v>
+        <v>3.804271824136142</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.473310207915459</v>
+        <v>3.595038642435096</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.494365284359155</v>
+        <v>-3.382248057783906</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.273198031923322</v>
+        <v>2.318044922553422</v>
       </c>
       <c r="F2031" t="n">
-        <v>1.142139771495742</v>
+        <v>1.068541913105327</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.466374004901827</v>
+        <v>3.588102439421464</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240720.xlsx
+++ b/tame_output/ON/bt/strategyON_20240720.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>15.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-71.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.4%</t>
+          <t>122.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.0%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.9%</t>
+          <t>-66.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.3%</t>
+          <t>455.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-499.8%</t>
+          <t>-490.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,22 +1175,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-144.4%</t>
+          <t>-140.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-132.3%</t>
+          <t>-136.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-117.1%</t>
+          <t>-123.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-87.2%</t>
+          <t>-18.2%</t>
         </is>
       </c>
     </row>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074619</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611569</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626473</v>
+        <v>3.856161751626474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785789</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.19901733376493</v>
+        <v>-5.407598646802909</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8768400802676455</v>
+        <v>0.793407555052454</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.3764818469564952</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.023125241297498</v>
+        <v>-5.231706554335476</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9507960407752671</v>
+        <v>0.8673635155600761</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.3764818469564952</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.851678778275034</v>
+        <v>-5.060260091313013</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.032702132038806</v>
+        <v>0.9492696068236151</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.2050353839340321</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.777389212536695</v>
+        <v>-4.985970525574674</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.061438435950439</v>
+        <v>0.9780059107352477</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.1307458181956928</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.713753470302761</v>
+        <v>-4.922334783340739</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.09158753389833</v>
+        <v>1.008155008683139</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.06711007596175828</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.602326710976841</v>
+        <v>-4.810908024014819</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.117352496412494</v>
+        <v>1.033919971197302</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.06711007596175828</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.36189621417198</v>
+        <v>-4.570477527209959</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.215267771759315</v>
+        <v>1.131835246544124</v>
       </c>
       <c r="F1925" t="n">
         <v>0.173320420843102</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367683</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.289653646000786</v>
+        <v>-4.498234959038764</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.248094112862613</v>
+        <v>1.164661587647422</v>
       </c>
       <c r="F1926" t="n">
         <v>0.173320420843102</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.236655323719398</v>
+        <v>-4.445236636757376</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.269972025692508</v>
+        <v>1.186539500477317</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2286566798450408</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.127850438239671</v>
+        <v>-4.336431751277649</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.310492051104393</v>
+        <v>1.227059525889201</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2286566798450408</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.90782964020266</v>
+        <v>-4.116410953240639</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.400079407329811</v>
+        <v>1.31664688211462</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3698765249130211</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.774961951139382</v>
+        <v>-3.98354326417736</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.469120665756946</v>
+        <v>1.385688140541754</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3698765249130211</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.654788867774883</v>
+        <v>-3.863370180812861</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.518335743543047</v>
+        <v>1.434903218327856</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4900496082775201</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.510116722675146</v>
+        <v>-3.718698035713124</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.586292704144382</v>
+        <v>1.502860178929191</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6347217533772576</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.569991550032838</v>
+        <v>-3.778572863070816</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.548380264602731</v>
+        <v>1.46494773938754</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5748469260195654</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.450171319122</v>
+        <v>-3.658752632159979</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.611597526201274</v>
+        <v>1.528165000986083</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5748469260195654</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.452641025583806</v>
+        <v>-3.661222338621785</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.518253842938994</v>
+        <v>1.434821317723802</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5723772195577592</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.521011211907816</v>
+        <v>-3.729592524945795</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.410167629894691</v>
+        <v>1.3267351046795</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5816529185939742</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.534799264754863</v>
+        <v>-3.743380577792841</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.395089117387764</v>
+        <v>1.311656592172572</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5816529185939742</v>
@@ -46125,10 +46125,10 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.565792424083568</v>
+        <v>-3.774373737121547</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.207401418696668</v>
+        <v>1.123968893481477</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5816529185939742</v>
@@ -46148,10 +46148,10 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.390318164291099</v>
+        <v>-3.598899477329077</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.282158354605444</v>
+        <v>1.198725829390253</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5816529185939742</v>
@@ -46171,10 +46171,10 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.501254416932348</v>
+        <v>-3.709835729970326</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.213525882310151</v>
+        <v>1.13009335709496</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5816529185939742</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111297</v>
       </c>
       <c r="C1941" t="n">
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.467590871460066</v>
+        <v>-3.676172184498044</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.155529613900514</v>
+        <v>1.072097088685322</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6153164640662561</v>
@@ -46217,10 +46217,10 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.407738252256343</v>
+        <v>-3.616319565294321</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.189643048014136</v>
+        <v>1.106210522798944</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6153164640662561</v>
@@ -46240,10 +46240,10 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.321494789229965</v>
+        <v>-3.530076102267944</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.219086703798547</v>
+        <v>1.135654178583355</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6153164640662561</v>
@@ -46263,10 +46263,10 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.366801608628945</v>
+        <v>-3.575382921666924</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.19273975148348</v>
+        <v>1.109307226268289</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5745063010570253</v>
@@ -46286,10 +46286,10 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.395834713331247</v>
+        <v>-3.604416026369225</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.181678382635661</v>
+        <v>1.09824585742047</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5745063010570253</v>
@@ -46309,10 +46309,10 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.303024231880388</v>
+        <v>-3.511605544918366</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.148075267107371</v>
+        <v>1.064642741892179</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6673167825078846</v>
@@ -46332,10 +46332,10 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.347413701209815</v>
+        <v>-3.555995014247793</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.132192955300201</v>
+        <v>1.048760430085009</v>
       </c>
       <c r="F1947" t="n">
         <v>0.622927313178457</v>
@@ -46355,10 +46355,10 @@
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.234742482973565</v>
+        <v>-3.443323796011543</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.172337151106424</v>
+        <v>1.088904625891232</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7355985314147071</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798538</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.122365481790892</v>
+        <v>-3.330946794828871</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.22277924741016</v>
+        <v>1.139346722194968</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7355985314147071</v>
@@ -46401,16 +46401,16 @@
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.150145879692245</v>
+        <v>-3.445620762092875</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.223164290018158</v>
+        <v>1.104974337057906</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.707818133513354</v>
+        <v>0.6209245641507025</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.908269946316816</v>
+        <v>2.856133804699225</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.233147160717524</v>
+        <v>-3.528622043118154</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.028319497608699</v>
+        <v>0.9101295446484474</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6892472489861803</v>
+        <v>0.6023536796235287</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.735483135601165</v>
+        <v>2.683346993983574</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.341761239160856</v>
+        <v>-3.637236121561485</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.105023526950573</v>
+        <v>0.9868335739903205</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6892472489861803</v>
+        <v>0.6023536796235287</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.85563279632037</v>
+        <v>2.80349665470278</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.306352200912713</v>
+        <v>-3.601827083313343</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.133700168352153</v>
+        <v>1.015510215391901</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6892472489861803</v>
+        <v>0.6023536796235287</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.870145822422693</v>
+        <v>2.818009680805103</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913428</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.267968538354562</v>
+        <v>-3.563443420755191</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.146473074717782</v>
+        <v>1.02828312175753</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7276309115443315</v>
+        <v>0.6407373421816799</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.890595461299953</v>
+        <v>2.838459319682362</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.090852208319395</v>
+        <v>-3.386327090720025</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.21404863557715</v>
+        <v>1.095858682616898</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7276309115443315</v>
+        <v>0.6407373421816799</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.887324490145255</v>
+        <v>2.835188348527664</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.135944453152941</v>
+        <v>-3.431419335553571</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.196695129405645</v>
+        <v>1.078505176445393</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6657348683749417</v>
+        <v>0.5788412990122901</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.850870256005534</v>
+        <v>2.798734114387943</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.956569031914174</v>
+        <v>-3.252043914314803</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.262232273207566</v>
+        <v>1.144042320247315</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8225116265456603</v>
+        <v>0.7356180571830088</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.93872328621438</v>
+        <v>2.886587144596788</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.00158324543478</v>
+        <v>-3.297058127835409</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.225034043130914</v>
+        <v>1.106844090170662</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7921627312310557</v>
+        <v>0.7052691618684042</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.901321404357207</v>
+        <v>2.849185262739616</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.268587755707215</v>
+        <v>-3.564062638107845</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.123923801360885</v>
+        <v>1.005733848400634</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5977996931881071</v>
+        <v>0.5109061238254555</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.790395143870383</v>
+        <v>2.738259002252792</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.369785537144388</v>
+        <v>-3.665260419545017</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.082648610682517</v>
+        <v>0.9644586577222658</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.529390879642788</v>
+        <v>0.4424973102801363</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.748553777639693</v>
+        <v>2.696417636022102</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.363274570530075</v>
+        <v>-3.658749452930705</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.082852958882559</v>
+        <v>0.9646630059223076</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.529390879642788</v>
+        <v>0.4424973102801363</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.74615373919401</v>
+        <v>2.694017597576419</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.344236442822778</v>
+        <v>-3.639711325223407</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.086992929173723</v>
+        <v>0.9688029762134713</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4712072683115934</v>
+        <v>0.3843136989489418</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.707768291603538</v>
+        <v>2.655632149985947</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.375363073973396</v>
+        <v>-3.670837956374025</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.252124145652157</v>
+        <v>1.133934192691905</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4712072683115934</v>
+        <v>0.3843136989489418</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.885350160542218</v>
+        <v>2.833214018924628</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.497943782118395</v>
+        <v>-3.684704717707943</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.20392519138029</v>
+        <v>1.129220817144471</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4303109421951324</v>
+        <v>0.3464557822151189</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.861645693858475</v>
+        <v>2.811332597870467</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789126</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.453139610578465</v>
+        <v>-3.639900546168013</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.227855390393188</v>
+        <v>1.153151016157369</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4303109421951324</v>
+        <v>0.3464557822151189</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.867654224255401</v>
+        <v>2.817341128267393</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.305396640343463</v>
+        <v>-3.492157575933011</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.184902799764389</v>
+        <v>1.11019842552857</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5981182994300156</v>
+        <v>0.514263139450002</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.866288859873531</v>
+        <v>2.815975763885523</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.407411322874684</v>
+        <v>-3.594172258464232</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.146890548283381</v>
+        <v>1.072186174047562</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5981182994300156</v>
+        <v>0.514263139450002</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.869082481405012</v>
+        <v>2.818769385417004</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.4012586168219</v>
+        <v>-3.588019552411447</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.150013979096153</v>
+        <v>1.075309604860334</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6042710054827999</v>
+        <v>0.5204158455027863</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.873436453428341</v>
+        <v>2.823123357440333</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.418067914972401</v>
+        <v>-3.604828850561949</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.142370736576063</v>
+        <v>1.067666362340244</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5874617073322983</v>
+        <v>0.5036065473522846</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.86243135127815</v>
+        <v>2.812118255290142</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.355769916196279</v>
+        <v>-3.542530851785827</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.233625489883333</v>
+        <v>1.158921115647514</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5874617073322983</v>
+        <v>0.5036065473522846</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.928766905074971</v>
+        <v>2.878453809086963</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.153979718531121</v>
+        <v>-3.340740654120669</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.116633570663523</v>
+        <v>1.041929196427704</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7854798995014527</v>
+        <v>0.701624739521439</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.849869822090591</v>
+        <v>2.799556726102582</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.989166715452274</v>
+        <v>-3.175927651041822</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.252849004217237</v>
+        <v>1.178144629981418</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9502929025802996</v>
+        <v>0.8664377426002859</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.019047856260074</v>
+        <v>2.968734760272066</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.086907260077249</v>
+        <v>-3.273668195666796</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.228380522483291</v>
+        <v>1.153676148247472</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9344036244473195</v>
+        <v>0.8505484644673058</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.024142025496329</v>
+        <v>2.973828929508321</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.263245020200178</v>
+        <v>-3.450005955789726</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.156381399258791</v>
+        <v>1.081677025022972</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.75806586432439</v>
+        <v>0.6742107043443764</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.916875350247243</v>
+        <v>2.866562254259235</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.186822973768251</v>
+        <v>-3.373583909357799</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.18544183587149</v>
+        <v>1.110737461635671</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.75806586432439</v>
+        <v>0.6742107043443764</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.915366968287172</v>
+        <v>2.865053872299164</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316251</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.142449842129682</v>
+        <v>-3.32921077771923</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.203053955962354</v>
+        <v>1.128349581726535</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8024389959629586</v>
+        <v>0.718583835982945</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.941853714705749</v>
+        <v>2.891540618717741</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.019615621242515</v>
+        <v>-3.206376556832063</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.246581438455811</v>
+        <v>1.171877064219992</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8024389959629586</v>
+        <v>0.718583835982945</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.93624750884434</v>
+        <v>2.885934412856332</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.971959890681459</v>
+        <v>-3.158720826271007</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.272025487708038</v>
+        <v>1.197321113472219</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8500947265240143</v>
+        <v>0.7662395665440006</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.971222704208778</v>
+        <v>2.92090960822077</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.871441732182705</v>
+        <v>-3.058202667772252</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.317125124482265</v>
+        <v>1.242420750246446</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9506128850227689</v>
+        <v>0.8667577250427552</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.036425972682756</v>
+        <v>2.986112876694747</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.932108322585094</v>
+        <v>-3.118869258174641</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.279613160797181</v>
+        <v>1.204908786561362</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8689145683042352</v>
+        <v>0.7850594083242215</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.974161655127507</v>
+        <v>2.923848559139499</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.887269920976696</v>
+        <v>-3.074030856566243</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.301646224051169</v>
+        <v>1.22694184981535</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8734580012491047</v>
+        <v>0.789602841269091</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.980985417505058</v>
+        <v>2.93067232151705</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.906768377218704</v>
+        <v>-3.093529312808251</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.298007781185444</v>
+        <v>1.223303406949625</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8253733599692004</v>
+        <v>0.7415181999891867</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.956295572368193</v>
+        <v>2.905982476380185</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.862565540132803</v>
+        <v>-3.049326475722351</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.321568518547641</v>
+        <v>1.246864144311822</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8695761970551008</v>
+        <v>0.7857210370750871</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.988696877147571</v>
+        <v>2.938383781159562</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.899544567796247</v>
+        <v>-3.086305503385794</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.305186907951511</v>
+        <v>1.230482533715692</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9065500988464313</v>
+        <v>0.8226949388664176</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.009291218691617</v>
+        <v>2.958978122703608</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.741253150256974</v>
+        <v>-2.928014085846522</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.41975124015026</v>
+        <v>1.345046865914441</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9065500988464313</v>
+        <v>0.8226949388664176</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.060538983874656</v>
+        <v>3.010225887886648</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.533611146622498</v>
+        <v>-2.720372082212046</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.501248746198304</v>
+        <v>1.426544371962485</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.114192102480907</v>
+        <v>1.030336942500894</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.183564890649595</v>
+        <v>3.133251794661587</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.48257905389997</v>
+        <v>-2.669339989489518</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.516609811525585</v>
+        <v>1.441905437289766</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.165224195203435</v>
+        <v>1.081369035223422</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.209132374521382</v>
+        <v>3.158819278533374</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.417354872772765</v>
+        <v>-2.604115808362312</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.559886888069172</v>
+        <v>1.485182513833353</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.230448376330641</v>
+        <v>1.146593216350628</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.26545428729041</v>
+        <v>3.215141191302402</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.379927852701631</v>
+        <v>-2.566688788291179</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.570818668396906</v>
+        <v>1.496114294161087</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.235699914359823</v>
+        <v>1.151844754379809</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.264566182407199</v>
+        <v>3.214253086419191</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.400039508736339</v>
+        <v>-2.586800444325887</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.564030798314263</v>
+        <v>1.489326424078444</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.246727259357242</v>
+        <v>1.162872099377229</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.272439381736891</v>
+        <v>3.222126285748883</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.346294694309135</v>
+        <v>-2.533055629898682</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.746086495106355</v>
+        <v>1.671382120870536</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.256790568797704</v>
+        <v>1.172935408817691</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.439035138422379</v>
+        <v>3.388722042434371</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.271512433284122</v>
+        <v>-2.45827336887367</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.896112308734178</v>
+        <v>1.821407934498359</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.331572829822717</v>
+        <v>1.247717669842703</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.604017404255204</v>
+        <v>3.553704308267196</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.245428349020314</v>
+        <v>-2.432189284609862</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.89825391845356</v>
+        <v>1.823549544217741</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.331572829822717</v>
+        <v>1.247717669842703</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.595725380269063</v>
+        <v>3.545412284281055</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.167297168171367</v>
+        <v>-2.354058103760915</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.927699586376918</v>
+        <v>1.852995212141099</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.405749640706401</v>
+        <v>1.321894480726388</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.638424662383053</v>
+        <v>3.588111566395045</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.158404706778084</v>
+        <v>-2.345165642367632</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.948810976661023</v>
+        <v>1.874106602425204</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.405749640706401</v>
+        <v>1.321894480726388</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.655979068109845</v>
+        <v>3.605665972121836</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.326880823747962</v>
+        <v>-2.429644502642787</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.873275577277655</v>
+        <v>1.832170105719725</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.377801804989821</v>
+        <v>1.319623730262866</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.63106541408448</v>
+        <v>3.596158569248307</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.629081294886379</v>
+        <v>-1.731844973781204</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.133665086010151</v>
+        <v>2.092559614452221</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.30745374561941</v>
+        <v>1.249275670892455</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.570126275650096</v>
+        <v>3.535219430813923</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.606360191203226</v>
+        <v>-1.709123870098051</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.133417549980316</v>
+        <v>2.092312078422386</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.30745374561941</v>
+        <v>1.249275670892455</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.560790298147</v>
+        <v>3.525883453310827</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.604635147913182</v>
+        <v>-1.707398826808008</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.293013693147503</v>
+        <v>2.251908221589573</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.309178788909454</v>
+        <v>1.251000714182499</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.720731449972195</v>
+        <v>3.685824605136022</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.759416154691438</v>
+        <v>-1.862179833586263</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.268179112929847</v>
+        <v>2.227073641371917</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.275811114854978</v>
+        <v>1.217633040128023</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.737788668033156</v>
+        <v>3.702881823196984</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.752361464476264</v>
+        <v>-1.855125143371089</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.267676345005462</v>
+        <v>2.226570873447532</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.282865805070151</v>
+        <v>1.224687730343196</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.738696838151806</v>
+        <v>3.703789993315633</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.725410240149776</v>
+        <v>-1.828173919044601</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.288462988380799</v>
+        <v>2.247357516822869</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.297746151097871</v>
+        <v>1.239568076370916</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.757631199413179</v>
+        <v>3.722724354577006</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.861363248206092</v>
+        <v>-1.964126927100917</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.418184917303232</v>
+        <v>2.377079445745302</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.297746151097871</v>
+        <v>1.239568076370916</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.941734331558139</v>
+        <v>3.906827486721966</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.883771366010964</v>
+        <v>-1.986535044905789</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.401338365084277</v>
+        <v>2.360232893526346</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.297746151097871</v>
+        <v>1.239568076370916</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.933851026461132</v>
+        <v>3.898944181624959</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.031777133490364</v>
+        <v>-2.134540812385189</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.344190057642154</v>
+        <v>2.303084586084224</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.211019142234329</v>
+        <v>1.152841067507374</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.883868820692644</v>
+        <v>3.848961975856471</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.041218059378894</v>
+        <v>-2.143981738273719</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.396667405008589</v>
+        <v>2.355561933450659</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.333446259777721</v>
+        <v>1.275268185050765</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.013578808940526</v>
+        <v>3.978671964104353</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.093491666714535</v>
+        <v>-2.19625534560936</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.378649056619634</v>
+        <v>2.337543585061703</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.281172652442079</v>
+        <v>1.222994577715124</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.985105739084442</v>
+        <v>3.95019889424827</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.169821644315441</v>
+        <v>-2.272585323210266</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.346228878473046</v>
+        <v>2.305123406915116</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.281172652442079</v>
+        <v>1.222994577715124</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.983217551978218</v>
+        <v>3.948310707142045</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.281578596930742</v>
+        <v>-2.384342275825567</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.296346327029788</v>
+        <v>2.255240855471858</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.169415699826778</v>
+        <v>1.111237625099823</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.9109836100119</v>
+        <v>3.876076765175726</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.279737577872491</v>
+        <v>-2.382501256767316</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.295516744863241</v>
+        <v>2.254411273305311</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.170683926498246</v>
+        <v>1.112505851771291</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.910178556224932</v>
+        <v>3.87527171138876</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.412038869970044</v>
+        <v>-2.514802548864869</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.255669634890138</v>
+        <v>2.214564163332208</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.170683926498246</v>
+        <v>1.112505851771291</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.923251963090851</v>
+        <v>3.888345118254678</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.413600512784904</v>
+        <v>-2.516364191679729</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.255044977764194</v>
+        <v>2.213939506206264</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.170683926498246</v>
+        <v>1.112505851771291</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.923251963090851</v>
+        <v>3.888345118254678</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.441501299894377</v>
+        <v>-2.544264978789202</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.242408704047407</v>
+        <v>2.201303232489477</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.136087002355312</v>
+        <v>1.077908927628357</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.901017849732092</v>
+        <v>3.866111004895919</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.564027402597271</v>
+        <v>-2.666791081492096</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.190162706943448</v>
+        <v>2.149057235385518</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.013560899652418</v>
+        <v>0.9553828249254628</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.824266632087555</v>
+        <v>3.789359787251382</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.584088723873778</v>
+        <v>-2.686852402768603</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.248844138023349</v>
+        <v>2.207738666465419</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.9934995783759109</v>
+        <v>0.9353215036489557</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.878935798912154</v>
+        <v>3.844028954075981</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199802</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.840809541868602</v>
+        <v>-2.943573220763427</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.286467529827267</v>
+        <v>2.245362058269337</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.885085004232096</v>
+        <v>0.8269069295051409</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.954198773427713</v>
+        <v>3.919291928591539</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622236</v>
+        <v>3.668303164622232</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.994795959644742</v>
+        <v>-3.097559638539567</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.29385323186245</v>
+        <v>2.25274776030452</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.885085004232096</v>
+        <v>0.8269069295051409</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.023179042573352</v>
+        <v>3.988272197737179</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808524</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.944274055817076</v>
+        <v>-3.047037734711902</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.300113195513638</v>
+        <v>2.259007723955707</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.885085004232096</v>
+        <v>0.8269069295051409</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.009230244693473</v>
+        <v>3.9743233998573</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994894</v>
+        <v>3.65634689399489</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.196749209824801</v>
+        <v>-3.299512888719626</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.210993622965962</v>
+        <v>2.169888151408032</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.885085004232096</v>
+        <v>0.8269069295051409</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.021100733748887</v>
+        <v>3.986193888912714</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358295</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.466222011746509</v>
+        <v>-3.568985690641334</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.104415036716222</v>
+        <v>2.063309565158292</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.885085004232096</v>
+        <v>0.8269069295051409</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.022311268267831</v>
+        <v>3.987404423431657</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637086</v>
+        <v>3.663523617637083</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.62376608347595</v>
+        <v>-3.726529762370775</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.045519150251767</v>
+        <v>2.004413678693837</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.8181831990918216</v>
+        <v>0.7600051243648664</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.986291927410988</v>
+        <v>3.951385082574815</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301343</v>
+        <v>3.65216331330134</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.752616634177997</v>
+        <v>-3.855380313072822</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.989056782707138</v>
+        <v>1.947951311149208</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7771897902411</v>
+        <v>0.7190117155141449</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.956773734836744</v>
+        <v>3.921866890000571</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215469</v>
+        <v>3.667976467215467</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.869584326816887</v>
+        <v>-3.972348005711713</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.104473762350626</v>
+        <v>2.063368290792695</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7771897902411</v>
+        <v>0.7190117155141449</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.118977791535788</v>
+        <v>4.084070946699615</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456692</v>
+        <v>3.696553628456689</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.954302269037841</v>
+        <v>-4.057065947932666</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.065433223426059</v>
+        <v>2.024327751868128</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6920737613130536</v>
+        <v>0.6338956865860985</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.062754812142774</v>
+        <v>4.027847967306601</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253288</v>
+        <v>3.750058176253285</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.036237087306724</v>
+        <v>-4.13900076620155</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.042888713686996</v>
+        <v>2.001783242129066</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.6821390157259735</v>
+        <v>0.6239609409990183</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.067023382359017</v>
+        <v>4.032116537522844</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717832</v>
+        <v>3.783647027717829</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.982498913906462</v>
+        <v>-4.085262592801287</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.073309621503004</v>
+        <v>2.032204149945073</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.7358771891262356</v>
+        <v>0.6776991143992804</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.108191924855078</v>
+        <v>4.073285080018904</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616948</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.872492630429241</v>
+        <v>-3.975256309324066</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.109465022138068</v>
+        <v>2.068359550580138</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.7590817610435108</v>
+        <v>0.7009036863165556</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.114267555249618</v>
+        <v>4.079360710413445</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203662</v>
+        <v>3.785578085203659</v>
       </c>
       <c r="C2028" t="n">
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.729433054688315</v>
+        <v>-3.83219673358314</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.170938863156412</v>
+        <v>2.129833391598482</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.76709518763349</v>
+        <v>0.7089171129065349</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.12332562192558</v>
+        <v>4.088418777089407</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436928</v>
+        <v>3.777251572436925</v>
       </c>
       <c r="C2029" t="n">
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.427986329216478</v>
+        <v>-3.530750008111303</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.298778436227683</v>
+        <v>2.257672964669753</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.068541913105327</v>
+        <v>1.010363838378372</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.311454540091218</v>
+        <v>4.276547695255045</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064763</v>
+        <v>3.812650101064761</v>
       </c>
       <c r="C2030" t="n">
         <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.382248057783906</v>
+        <v>-3.517474385647206</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.318044922553422</v>
+        <v>2.263954391408102</v>
       </c>
       <c r="F2030" t="n">
-        <v>1.068541913105327</v>
+        <v>1.010363838378372</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.312425717843928</v>
+        <v>4.277518873007756</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.804271824136142</v>
+        <v>3.43869811764084</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.595038642435096</v>
+        <v>3.672143474360487</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.382248057783906</v>
+        <v>-3.292444692477535</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.318044922553422</v>
+        <v>2.354809173055727</v>
       </c>
       <c r="F2031" t="n">
-        <v>1.068541913105327</v>
+        <v>1.010363838378372</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.588102439421464</v>
+        <v>4.278361777387511</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240720.xlsx
+++ b/tame_output/ON/bt/strategyON_20240720.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>53.9%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.5%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.1%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-644.5%</t>
+          <t>-670.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-49.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,32 +1007,32 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.3%</t>
+          <t>-69.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.6%</t>
+          <t>452.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-490.8%</t>
+          <t>-530.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-258.2%</t>
+          <t>-268.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>2887.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-140.7%</t>
+          <t>-158.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-263.7%</t>
+          <t>-289.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>745.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-136.5%</t>
+          <t>-140.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-123.0%</t>
+          <t>-140.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-158.6%</t>
+          <t>-174.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-30.2%</t>
         </is>
       </c>
     </row>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.688067794699071</v>
+        <v>-1.946215697465108</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.441336725248489</v>
+        <v>2.338077564142074</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9499649662618935</v>
+        <v>0.6918170634958563</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.686899247199001</v>
+        <v>3.532010505539378</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.054136521843724</v>
+        <v>-2.312284424609761</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.287993533697077</v>
+        <v>2.184734372590662</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5838962391172409</v>
+        <v>0.3257483363512036</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.460342310218659</v>
+        <v>3.305453568559036</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.262627303295408</v>
+        <v>-2.520775206061445</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.224935510855171</v>
+        <v>2.121676349748757</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3754054576655564</v>
+        <v>0.1172575548995192</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.355586131086416</v>
+        <v>3.200697389426794</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.50982848806063</v>
+        <v>-2.767976390826667</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.134153787357651</v>
+        <v>2.030894626251237</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3955588111643689</v>
+        <v>0.1374109083983316</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.375776893594272</v>
+        <v>3.22088815193465</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.002213516084727</v>
+        <v>-3.260361418850764</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.938306168191745</v>
+        <v>1.83504700708533</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.3549741196257651</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.081452268823546</v>
+        <v>2.926563527163924</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.387393907014799</v>
+        <v>-3.645541809780836</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.782776550632579</v>
+        <v>1.679517389526164</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.3549741196257651</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.079994807636409</v>
+        <v>2.925106065976787</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.637264587029381</v>
+        <v>-3.895412489795418</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.684597402081363</v>
+        <v>1.581338240974948</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.06056349702926461</v>
+        <v>-0.3187113997953019</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.103521562989304</v>
+        <v>2.948632821329681</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.843776363916402</v>
+        <v>-4.101924266682439</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.598098749982812</v>
+        <v>1.494839588876397</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.5252231766823234</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.975720555513349</v>
+        <v>2.820831813853726</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.163120438996904</v>
+        <v>-4.421268341762941</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.472134046650871</v>
+        <v>1.368874885544456</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.5252231766823234</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.977493482213608</v>
+        <v>2.822604740553986</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.594926232146691</v>
+        <v>-4.853074134912728</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.28574461685836</v>
+        <v>1.182485455751945</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4034927703575531</v>
+        <v>-0.6616406731235904</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.881975871816252</v>
+        <v>2.72708713015663</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.829620226279244</v>
+        <v>-5.087768129045281</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.18015179420743</v>
+        <v>1.076892633101015</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3971565031282979</v>
+        <v>-0.6553044058943353</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.874062407155896</v>
+        <v>2.719173665496274</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.165282873509696</v>
+        <v>-5.423430776275733</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.044467326971214</v>
+        <v>0.9412081658647993</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4650874886172027</v>
+        <v>-0.7232353913832401</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.831884407518518</v>
+        <v>2.676995665858896</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.241727203712568</v>
+        <v>-5.499875106478605</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.020377155124307</v>
+        <v>0.9171179940178922</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3846419795235408</v>
+        <v>-0.6427898822895782</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.886639273208957</v>
+        <v>2.731750531549335</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.606854586351314</v>
+        <v>-5.865002489117352</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8735807170746397</v>
+        <v>0.7703215559682248</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6809527638225534</v>
+        <v>-0.9391006665885908</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.708107317635381</v>
+        <v>2.553218575975758</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.015443363531993</v>
+        <v>-6.27359126629803</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7089067502171269</v>
+        <v>0.605647589110712</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.347689443769269</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.461715595341733</v>
+        <v>2.30682685368211</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.129203775554858</v>
+        <v>-6.387351678320895</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6585880178794419</v>
+        <v>0.555328856773027</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.347689443769269</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.456901027813193</v>
+        <v>2.302012286153571</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.545595649841855</v>
+        <v>-6.803743552607893</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4900253187735202</v>
+        <v>0.3867661576671053</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.347689443769269</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.454895078422071</v>
+        <v>2.300006336762448</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.789867050568925</v>
+        <v>-7.048014953334962</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4025754491513713</v>
+        <v>0.2993162880449565</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.347689443769269</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.46515376909075</v>
+        <v>2.310265027431127</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.995118069805685</v>
+        <v>-7.253265972571723</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3165746066023623</v>
+        <v>0.2133154454959474</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.347689443769269</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.461253334236445</v>
+        <v>2.306364592576823</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.043320887048029</v>
+        <v>-7.301468789814066</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2956983997604259</v>
+        <v>0.192439238654011</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.347689443769269</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.459658254291446</v>
+        <v>2.304769512631824</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.339982228858227</v>
+        <v>-7.598130131624264</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1808128389655548</v>
+        <v>0.07755367785913991</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.416432579503148</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.267302607120705</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.526701937167529</v>
+        <v>-7.784849839933567</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1020986511074309</v>
+        <v>-0.001160509998983983</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.416432579503148</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.263276302586301</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.909703325910161</v>
+        <v>-8.167851228676197</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.05120400571120598</v>
+        <v>-0.1544631668176204</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.416432579503148</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.263174201264717</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.914189771111549</v>
+        <v>-8.172337673877585</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05042706782033113</v>
+        <v>-0.1536862289267455</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.420919024704536</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.417942591774937</v>
+        <v>2.263053850115314</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.273720093615552</v>
+        <v>-8.531867996381587</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1888888935238819</v>
+        <v>-0.2921480546302959</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.420919024704536</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.423292895072987</v>
+        <v>2.268404153413365</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.324069157069774</v>
+        <v>-8.582217059835809</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2011124989483934</v>
+        <v>-0.3043716600548074</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.213120185392721</v>
+        <v>-1.471268088158759</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.400999476957631</v>
+        <v>2.246110735298009</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.42168843449117</v>
+        <v>-8.679836337257205</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2371184592951829</v>
+        <v>-0.3403776204015969</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.310739462814118</v>
+        <v>-1.568887365580155</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.19058091946694</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.475759933999528</v>
+        <v>-8.733907836765564</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.255853502776954</v>
+        <v>-0.3591126638833684</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.364810962322477</v>
+        <v>-1.622958865088515</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.315920317743119</v>
+        <v>2.161031576083496</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.680018109329392</v>
+        <v>-8.938166012095428</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3320435757902573</v>
+        <v>-0.4353027368966713</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.492449906936466</v>
+        <v>-1.750597809702504</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.089961406433745</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.713670947837866</v>
+        <v>-8.971818850603901</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3410221567092107</v>
+        <v>-0.4442813178156246</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.592863274853503</v>
+        <v>-1.851011177619541</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.034195940167959</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.640201116170417</v>
+        <v>-8.898349018936452</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.29626252254881</v>
+        <v>-0.399521683655224</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.777541345952093</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.093649540661849</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.81532553355696</v>
+        <v>-9.073473436322995</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3517570687559104</v>
+        <v>-0.4550162298623244</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.952665763338636</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.003130110977439</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.04977762757145</v>
+        <v>-9.307925530337485</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4527570712633024</v>
+        <v>-0.5560162323697164</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.952665763338636</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>1.995910946075844</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.154152358597896</v>
+        <v>-9.412300261363931</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5011791544478572</v>
+        <v>-0.6044383155542712</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-2.057040494365082</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>1.926613916686</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.206938514198223</v>
+        <v>-9.465086416964258</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5211778268494314</v>
+        <v>-0.6244369879558453</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-2.152715980947479</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>1.870324414575118</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.332975307566512</v>
+        <v>-9.591123210332547</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5688988155676324</v>
+        <v>-0.6721579766740464</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-2.127464358137737</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>1.888169116890078</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.275903535670581</v>
+        <v>-9.534051438436617</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5420797711228591</v>
+        <v>-0.6453389322292735</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-2.127464358137737</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>1.892159452576479</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.417575377394702</v>
+        <v>-9.675723280160737</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6002237347112489</v>
+        <v>-0.7034828958176633</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-2.127464358137737</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>1.890684225677737</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.367984532969867</v>
+        <v>-9.626132435735903</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5653339867764431</v>
+        <v>-0.6685931478828571</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-2.077873513712903</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>1.93549214249751</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.219066198498011</v>
+        <v>-9.477214101264046</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5188177866343833</v>
+        <v>-0.6220769477407977</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-2.04662392297773</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>1.941190763291931</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.993221045778601</v>
+        <v>-9.251368948544634</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4189006525104109</v>
+        <v>-0.5221598136168244</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-2.004697247390566</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>1.975925841680438</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.868642389441009</v>
+        <v>-9.126790292207042</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3679300454193153</v>
+        <v>-0.4711892065257284</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-2.004697247390566</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>1.977064986236496</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.921537677485295</v>
+        <v>-9.179685580251329</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3864543864749219</v>
+        <v>-0.4897135475813355</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.99974190130212</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>1.982671968051672</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.849404502197414</v>
+        <v>-9.107552404963448</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3518674121211331</v>
+        <v>-0.4551265732275467</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.99974190130212</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>1.988405672290308</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.778038109587767</v>
+        <v>-9.0361860123538</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3330581174711393</v>
+        <v>-0.4363172785775529</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.928375508692472</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.021488245462232</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.684579075602542</v>
+        <v>-8.942726978368576</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.305557985189957</v>
+        <v>-0.4088171462963706</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.928375508692472</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.011604764149324</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.417337274734145</v>
+        <v>-8.675485177500178</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2004958253419717</v>
+        <v>-0.3037549864483853</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.928375508692472</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.00977020364995</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.319430236057654</v>
+        <v>-8.577578138823688</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1616333248448365</v>
+        <v>-0.26489248595125</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.860389758831916</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.050261338592823</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097243</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.295476695081696</v>
+        <v>-8.55362459784773</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1513834023089595</v>
+        <v>-0.2546425634153731</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.836436217855958</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.065301969323891</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.031416756758899</v>
+        <v>-8.289564659524933</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05901974314159286</v>
+        <v>-0.1622789042480064</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.572376279533162</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.210477616155817</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.324337133254061</v>
+        <v>-7.582485036020095</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2210250726000416</v>
+        <v>0.117765911493628</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.572376279533162</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.207690582495516</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.284152834887871</v>
+        <v>-7.542300737653904</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2374424158343591</v>
+        <v>0.1341832547279456</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.532191981166971</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.232144785403072</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626474</v>
+        <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.120752963948508</v>
+        <v>-7.378900866714542</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.302169185430861</v>
+        <v>0.1989100243244475</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.368792110227609</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.329551529187446</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291816</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.88727174171891</v>
+        <v>-7.145419644484943</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4034861031605526</v>
+        <v>0.300226942054139</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-1.13531088799801</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.477564691363058</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785792</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.737605350711394</v>
+        <v>-6.995753253477428</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4604604492505997</v>
+        <v>0.3572012881441862</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-1.042407396755474</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.53041457579562</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390432</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.605329877080508</v>
+        <v>-6.863477779846542</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5087381254499812</v>
+        <v>0.4054789643435677</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.9101319231245877</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.605147346721179</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105956</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.449591544520766</v>
+        <v>-6.7077394472868</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5738485191615146</v>
+        <v>0.470589358055101</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.7543935905648461</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.701405406944661</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.200591745837185</v>
+        <v>-6.458739648603219</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6863547798586058</v>
+        <v>0.5830956187521923</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.7543935905648461</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.71431174816832</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.30618173561029</v>
+        <v>-6.564329638376323</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5161428543501452</v>
+        <v>0.4128836932437316</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.8599835803379505</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.522981824705238</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.324916637728887</v>
+        <v>-6.541439213048624</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5571932353797928</v>
+        <v>0.4705842052518978</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.841322407644261</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.582722870198539</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710816</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.176976596321287</v>
+        <v>-6.393499171641024</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.496490329254665</v>
+        <v>0.40988129912677</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.8210014917357035</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.475036497055505</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409209</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.124007074067299</v>
+        <v>-6.340529649387036</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5089641519027821</v>
+        <v>0.4223551217748875</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.7680319694817146</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.49810422415442</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.729969716098114</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.080458667296608</v>
+        <v>-6.296981242616345</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5194229025159651</v>
+        <v>0.4328138723880706</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.7680319694817146</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.491143612059327</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493425</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.04709546081784</v>
+        <v>-6.263618036137577</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5472305394886159</v>
+        <v>0.4606215093607209</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.7680319694817146</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.50560596644047</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722821</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.938836323695318</v>
+        <v>-6.155358899015055</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5850663147968196</v>
+        <v>0.4984572846689246</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.7680319694817146</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.500138086899665</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.82805292879205</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.815545188878187</v>
+        <v>-6.032067764197924</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6318808627342487</v>
+        <v>0.5452718326063537</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.6447408346645841</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.571610861800521</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.794395989974744</v>
+        <v>-6.010918565294481</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6480415205329515</v>
+        <v>0.5614324904050565</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.6235916357611407</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.592001359379912</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.550630547991299</v>
+        <v>-5.767153123311036</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7413284056733795</v>
+        <v>0.654719375545485</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.6235916357611407</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.587782067726963</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.448867727714005</v>
+        <v>-5.665390303033742</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7841578477043138</v>
+        <v>0.6975488175764188</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.610372567368712</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.597837822682436</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279187</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.407598646802909</v>
+        <v>-5.415539909084667</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.793407555052454</v>
+        <v>0.7902310501397509</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.610372567368712</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.590579897666138</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.231706554335476</v>
+        <v>-5.239647816617234</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8673635155600761</v>
+        <v>0.8641870106473726</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.610372567368712</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.594179021186787</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.060260091313013</v>
+        <v>-5.068201353594771</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9492696068236151</v>
+        <v>0.946093101910912</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.4389261043462489</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.710374405054818</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.985970525574674</v>
+        <v>-4.993911787856431</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9780059107352477</v>
+        <v>0.9748294058225444</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.3646365386079096</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.753968622114119</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.922334783340739</v>
+        <v>-4.930276045622497</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.008155008683139</v>
+        <v>1.004978503770436</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.3010007963739751</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.796844868508797</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.810908024014819</v>
+        <v>-4.818849286296577</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.033919971197302</v>
+        <v>1.030743466284599</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.3010007963739751</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.778039127292593</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.570477527209959</v>
+        <v>-4.578418789491717</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.131835246544124</v>
+        <v>1.128658741631421</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>-0.0605702995691148</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>2.924040502000386</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367683</v>
+        <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.498234959038764</v>
+        <v>-4.506176221320522</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.164661587647422</v>
+        <v>1.161485082734719</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>-0.0605702995691148</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>2.927969815835206</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.445236636757376</v>
+        <v>-4.453177899039134</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.186539500477317</v>
+        <v>1.183362995564614</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2286566798450408</v>
+        <v>-0.005234040567175968</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.10218458740104</v>
+        <v>2.96185015515371</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.336431751277649</v>
+        <v>-4.344373013559407</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.227059525889201</v>
+        <v>1.223883020976498</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2286566798450408</v>
+        <v>-0.005234040567175968</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.099182658621033</v>
+        <v>2.958848226373703</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.116410953240639</v>
+        <v>-4.124352215522396</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.31664688211462</v>
+        <v>1.313470377201917</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.1359858045008043</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.185493602672435</v>
+        <v>3.045159170425105</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.98354326417736</v>
+        <v>-3.991484526459118</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.385688140541754</v>
+        <v>1.382511635629051</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.1359858045008043</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.201387785474259</v>
+        <v>3.061053353226928</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.863370180812861</v>
+        <v>-3.871311443094619</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.434903218327856</v>
+        <v>1.431726713415153</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4900496082775201</v>
+        <v>0.2561588878653032</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.27463747993326</v>
+        <v>3.13430304768593</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551577001</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.718698035713124</v>
+        <v>-3.726639297994882</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.502860178929191</v>
+        <v>1.499683674016488</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6347217533772576</v>
+        <v>0.4008310329650406</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.371528869554542</v>
+        <v>3.231194437307212</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.778572863070816</v>
+        <v>-3.786514125352574</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.46494773938754</v>
+        <v>1.461771234474836</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.3409562056073485</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.321641464541353</v>
+        <v>3.181307032294023</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.658752632159979</v>
+        <v>-3.666693894441737</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.528165000986083</v>
+        <v>1.52498849607338</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.3409562056073485</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.336930633775562</v>
+        <v>3.196596201528231</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.661222338621785</v>
+        <v>-3.669163600903543</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.434821317723802</v>
+        <v>1.431644812811099</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5723772195577592</v>
+        <v>0.3384864991455424</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.243093009220919</v>
+        <v>3.102758576973589</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.729592524945795</v>
+        <v>-3.737533787227552</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.3267351046795</v>
+        <v>1.323558599766796</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.3477621981817573</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.16792029012795</v>
+        <v>3.02758585788062</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.743380577792841</v>
+        <v>-3.751321840074599</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.311656592172572</v>
+        <v>1.308480087259869</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.3477621981817573</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.158356998759841</v>
+        <v>3.018022566512511</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.774373737121547</v>
+        <v>-3.782314999403305</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.123968893481477</v>
+        <v>1.120792388568774</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.3477621981817573</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.983066563800228</v>
+        <v>2.842732131552898</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.598899477329077</v>
+        <v>-3.606840739610835</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.198725829390253</v>
+        <v>1.195549324477549</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.3477621981817573</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.987633795792016</v>
+        <v>2.847299363544685</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.709835729970326</v>
+        <v>-3.717776992252084</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.13009335709496</v>
+        <v>1.126916852182257</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.3477621981817573</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.963375824553223</v>
+        <v>2.823041392305893</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111297</v>
+        <v>3.773210297111298</v>
       </c>
       <c r="C1941" t="n">
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.676172184498044</v>
+        <v>-3.684113446779802</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.072097088685322</v>
+        <v>1.068920583772619</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.3814257436540391</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.912112265238041</v>
+        <v>2.771777832990711</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.616319565294321</v>
+        <v>-3.624260827576079</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.106210522798944</v>
+        <v>1.103034017886241</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.3814257436540391</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.922284651670174</v>
+        <v>2.781950219422844</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.530076102267944</v>
+        <v>-3.538017364549702</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.135654178583355</v>
+        <v>1.132477673670652</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.3814257436540391</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.917230922244034</v>
+        <v>2.776896489996704</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316051</v>
       </c>
       <c r="C1944" t="n">
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.575382921666924</v>
+        <v>-3.583324183948681</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.109307226268289</v>
+        <v>1.106130721355586</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.3406155806448083</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.884520599883021</v>
+        <v>2.744186167635691</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803196</v>
       </c>
       <c r="C1945" t="n">
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.604416026369225</v>
+        <v>-3.612357288650983</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.09824585742047</v>
+        <v>1.095069352507767</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.3406155806448083</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.885072472916123</v>
+        <v>2.744738040668793</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.511605544918366</v>
+        <v>-3.519546807200124</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.064642741892179</v>
+        <v>1.061466236979476</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6673167825078846</v>
+        <v>0.4334260620956677</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.870031453678004</v>
+        <v>2.729697021430674</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.74828581656043</v>
       </c>
       <c r="C1947" t="n">
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.555995014247793</v>
+        <v>-3.563936276529551</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.048760430085009</v>
+        <v>1.045583925172306</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.622927313178457</v>
+        <v>0.38903659276624</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.845271248004948</v>
+        <v>2.704936815757618</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.443323796011543</v>
+        <v>-3.451265058293301</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.088904625891232</v>
+        <v>1.085728120978529</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.5017078110024902</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.907949687458421</v>
+        <v>2.767615255211091</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798541</v>
       </c>
       <c r="C1949" t="n">
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.330946794828871</v>
+        <v>-3.338888057110629</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.139346722194968</v>
+        <v>1.136170217282265</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.5017078110024902</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.913440983289088</v>
+        <v>2.773106551041758</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498866</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.445620762092875</v>
+        <v>-3.366668455011982</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.104974337057906</v>
+        <v>1.136555259890263</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6209245641507025</v>
+        <v>0.4739274131011371</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.856133804699225</v>
+        <v>2.767935514069486</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.528622043118154</v>
+        <v>-3.449669736037261</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9101295446484474</v>
+        <v>0.9417104674808048</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6023536796235287</v>
+        <v>0.4553565285739634</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.683346993983574</v>
+        <v>2.595148703353835</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.637236121561485</v>
+        <v>-3.558283814480592</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9868335739903205</v>
+        <v>1.018414496822678</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6023536796235287</v>
+        <v>0.4553565285739634</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.80349665470278</v>
+        <v>2.71529836407304</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.601827083313343</v>
+        <v>-3.522874776232449</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.015510215391901</v>
+        <v>1.047091138224258</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6023536796235287</v>
+        <v>0.4553565285739634</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.818009680805103</v>
+        <v>2.729811390175363</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913429</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.563443420755191</v>
+        <v>-3.484491113674298</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.02828312175753</v>
+        <v>1.059864044589887</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6407373421816799</v>
+        <v>0.4937401911321145</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.838459319682362</v>
+        <v>2.750261029052623</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.386327090720025</v>
+        <v>-3.307374783639132</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.095858682616898</v>
+        <v>1.127439605449256</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6407373421816799</v>
+        <v>0.4937401911321145</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.835188348527664</v>
+        <v>2.746990057897924</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793906</v>
       </c>
       <c r="C1956" t="n">
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.431419335553571</v>
+        <v>-3.352467028472677</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.078505176445393</v>
+        <v>1.11008609927775</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5788412990122901</v>
+        <v>0.4318441479627247</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.798734114387943</v>
+        <v>2.710535823758204</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.252043914314803</v>
+        <v>-3.17309160723391</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.144042320247315</v>
+        <v>1.175623243079672</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7356180571830088</v>
+        <v>0.5886209061334434</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.886587144596788</v>
+        <v>2.798388853967049</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982232</v>
       </c>
       <c r="C1958" t="n">
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.297058127835409</v>
+        <v>-3.218105820754516</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.106844090170662</v>
+        <v>1.138425013003019</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7052691618684042</v>
+        <v>0.5582720108188388</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.849185262739616</v>
+        <v>2.760986972109877</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.564062638107845</v>
+        <v>-3.485110331026951</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.005733848400634</v>
+        <v>1.037314771232991</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5109061238254555</v>
+        <v>0.3639089727758902</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.738259002252792</v>
+        <v>2.650060711623053</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.665260419545017</v>
+        <v>-3.586308112464124</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9644586577222658</v>
+        <v>0.9960395805546232</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4424973102801363</v>
+        <v>0.295500159230571</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.696417636022102</v>
+        <v>2.608219345392363</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.70557166181546</v>
       </c>
       <c r="C1961" t="n">
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.658749452930705</v>
+        <v>-3.579797145849811</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9646630059223076</v>
+        <v>0.9962439287546649</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4424973102801363</v>
+        <v>0.295500159230571</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.694017597576419</v>
+        <v>2.60581930694668</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378105</v>
       </c>
       <c r="C1962" t="n">
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.639711325223407</v>
+        <v>-3.560759018142514</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9688029762134713</v>
+        <v>1.000383899045829</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3843136989489418</v>
+        <v>0.2373165478993765</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.655632149985947</v>
+        <v>2.567433859356208</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131254</v>
       </c>
       <c r="C1963" t="n">
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.670837956374025</v>
+        <v>-3.591885649293132</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.133934192691905</v>
+        <v>1.165515115524262</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3843136989489418</v>
+        <v>0.2373165478993765</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.833214018924628</v>
+        <v>2.745015728294888</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.684704717707943</v>
+        <v>-3.60575241062705</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.129220817144471</v>
+        <v>1.160801739976829</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3464557822151189</v>
+        <v>0.1994586311655536</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.811332597870467</v>
+        <v>2.723134307240728</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.639900546168013</v>
+        <v>-3.56094823908712</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.153151016157369</v>
+        <v>1.184731938989727</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3464557822151189</v>
+        <v>0.1994586311655536</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.817341128267393</v>
+        <v>2.729142837637654</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.492157575933011</v>
+        <v>-3.413205268852118</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.11019842552857</v>
+        <v>1.141779348360927</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.514263139450002</v>
+        <v>0.3672659884004367</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.815975763885523</v>
+        <v>2.727777473255784</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.594172258464232</v>
+        <v>-3.515219951383338</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.072186174047562</v>
+        <v>1.10376709687992</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.514263139450002</v>
+        <v>0.3672659884004367</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.818769385417004</v>
+        <v>2.730571094787265</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.588019552411447</v>
+        <v>-3.509067245330554</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.075309604860334</v>
+        <v>1.106890527692692</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5204158455027863</v>
+        <v>0.373418694453221</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.823123357440333</v>
+        <v>2.734925066810594</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.604828850561949</v>
+        <v>-3.525876543481056</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.067666362340244</v>
+        <v>1.099247285172601</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5036065473522846</v>
+        <v>0.3566093963027194</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.812118255290142</v>
+        <v>2.723919964660403</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.542530851785827</v>
+        <v>-3.463578544704934</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.158921115647514</v>
+        <v>1.190502038479871</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5036065473522846</v>
+        <v>0.3566093963027194</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.878453809086963</v>
+        <v>2.790255518457224</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.340740654120669</v>
+        <v>-3.261788347039776</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.041929196427704</v>
+        <v>1.073510119260061</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.701624739521439</v>
+        <v>0.5546275884718738</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.799556726102582</v>
+        <v>2.711358435472843</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.175927651041822</v>
+        <v>-3.096975343960929</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.178144629981418</v>
+        <v>1.209725552813775</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8664377426002859</v>
+        <v>0.7194405915507207</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.968734760272066</v>
+        <v>2.880536469642327</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.273668195666796</v>
+        <v>-3.194715888585903</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.153676148247472</v>
+        <v>1.185257071079829</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8505484644673058</v>
+        <v>0.7035513134177405</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.973828929508321</v>
+        <v>2.885630638878582</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.450005955789726</v>
+        <v>-3.371053648708832</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.081677025022972</v>
+        <v>1.113257947855329</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6742107043443764</v>
+        <v>0.527213553294811</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.866562254259235</v>
+        <v>2.778363963629496</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397797</v>
       </c>
       <c r="C1975" t="n">
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.373583909357799</v>
+        <v>-3.294631602276906</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.110737461635671</v>
+        <v>1.142318384468028</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6742107043443764</v>
+        <v>0.527213553294811</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.865053872299164</v>
+        <v>2.776855581669424</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316252</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.32921077771923</v>
+        <v>-3.250258470638337</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.128349581726535</v>
+        <v>1.159930504558892</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.718583835982945</v>
+        <v>0.5715866849333796</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.891540618717741</v>
+        <v>2.803342328088002</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.206376556832063</v>
+        <v>-3.12742424975117</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.171877064219992</v>
+        <v>1.203457987052349</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.718583835982945</v>
+        <v>0.5715866849333796</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.885934412856332</v>
+        <v>2.797736122226592</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190328</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.158720826271007</v>
+        <v>-3.079768519190114</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.197321113472219</v>
+        <v>1.228902036304576</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7662395665440006</v>
+        <v>0.6192424154944353</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.92090960822077</v>
+        <v>2.832711317591031</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.82267821056962</v>
       </c>
       <c r="C1979" t="n">
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.058202667772252</v>
+        <v>-2.979250360691359</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.242420750246446</v>
+        <v>1.274001673078803</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8667577250427552</v>
+        <v>0.7197605739931898</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.986112876694747</v>
+        <v>2.897914586065008</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557296</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.118869258174641</v>
+        <v>-3.039916951093748</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.204908786561362</v>
+        <v>1.23648970939372</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7850594083242215</v>
+        <v>0.6380622572746562</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.923848559139499</v>
+        <v>2.83565026850976</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932771</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.074030856566243</v>
+        <v>-2.99507854948535</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.22694184981535</v>
+        <v>1.258522772647708</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.789602841269091</v>
+        <v>0.6426056902195256</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.93067232151705</v>
+        <v>2.84247403088731</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.093529312808251</v>
+        <v>-3.014577005727358</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.223303406949625</v>
+        <v>1.254884329781982</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7415181999891867</v>
+        <v>0.5945210489396213</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.905982476380185</v>
+        <v>2.817784185750446</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.82668474540596</v>
       </c>
       <c r="C1983" t="n">
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.049326475722351</v>
+        <v>-2.970374168641458</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.246864144311822</v>
+        <v>1.27844506714418</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7857210370750871</v>
+        <v>0.6387238860255218</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.938383781159562</v>
+        <v>2.850185490529823</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.086305503385794</v>
+        <v>-3.007353196304901</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.230482533715692</v>
+        <v>1.26206345654805</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8226949388664176</v>
+        <v>0.6756977878168523</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.958978122703608</v>
+        <v>2.870779832073869</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.928014085846522</v>
+        <v>-2.849061778765629</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.345046865914441</v>
+        <v>1.376627788746798</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8226949388664176</v>
+        <v>0.6756977878168523</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.010225887886648</v>
+        <v>2.922027597256909</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.720372082212046</v>
+        <v>-2.641419775131153</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.426544371962485</v>
+        <v>1.458125294794842</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.030336942500894</v>
+        <v>0.8833397914513285</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.133251794661587</v>
+        <v>3.045053504031848</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.669339989489518</v>
+        <v>-2.590387682408624</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.441905437289766</v>
+        <v>1.473486360122123</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.081369035223422</v>
+        <v>0.9343718841738564</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.158819278533374</v>
+        <v>3.070620987903634</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.604115808362312</v>
+        <v>-2.525163501281419</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.485182513833353</v>
+        <v>1.51676343666571</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.146593216350628</v>
+        <v>0.999596065301062</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.215141191302402</v>
+        <v>3.126942900672663</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.566688788291179</v>
+        <v>-2.487736481210285</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.496114294161087</v>
+        <v>1.527695216993444</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.151844754379809</v>
+        <v>1.004847603330244</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.214253086419191</v>
+        <v>3.126054795789452</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.586800444325887</v>
+        <v>-2.507848137244994</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.489326424078444</v>
+        <v>1.520907346910801</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.162872099377229</v>
+        <v>1.015874948327663</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.222126285748883</v>
+        <v>3.133927995119144</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.533055629898682</v>
+        <v>-2.454103322817789</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.671382120870536</v>
+        <v>1.702963043702894</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.172935408817691</v>
+        <v>1.025938257768125</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.388722042434371</v>
+        <v>3.300523751804632</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.45827336887367</v>
+        <v>-2.379321061792776</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.821407934498359</v>
+        <v>1.852988857330716</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.247717669842703</v>
+        <v>1.100720518793138</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.553704308267196</v>
+        <v>3.465506017637457</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.432189284609862</v>
+        <v>-2.353236977528968</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.823549544217741</v>
+        <v>1.855130467050098</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.247717669842703</v>
+        <v>1.100720518793138</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.545412284281055</v>
+        <v>3.457213993651316</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.354058103760915</v>
+        <v>-2.275105796680021</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.852995212141099</v>
+        <v>1.884576134973456</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.321894480726388</v>
+        <v>1.174897329676822</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.588111566395045</v>
+        <v>3.499913275765306</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.345165642367632</v>
+        <v>-2.266213335286738</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.874106602425204</v>
+        <v>1.905687525257561</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.321894480726388</v>
+        <v>1.174897329676822</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.605665972121836</v>
+        <v>3.517467681492097</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.429644502642787</v>
+        <v>-2.434689452256616</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.832170105719725</v>
+        <v>1.830152125874194</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.319623730262866</v>
+        <v>1.146949493960242</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.596158569248307</v>
+        <v>3.492554027466733</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.731844973781204</v>
+        <v>-1.736889923395033</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.092559614452221</v>
+        <v>2.090541634606689</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.249275670892455</v>
+        <v>1.076601434589831</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.535219430813923</v>
+        <v>3.431614889032348</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.709123870098051</v>
+        <v>-1.714168819711881</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.092312078422386</v>
+        <v>2.090294098576854</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.249275670892455</v>
+        <v>1.076601434589831</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.525883453310827</v>
+        <v>3.422278911529253</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.707398826808008</v>
+        <v>-1.712443776421837</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.251908221589573</v>
+        <v>2.249890241744041</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.251000714182499</v>
+        <v>1.078326477879875</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.685824605136022</v>
+        <v>3.582220063354448</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.862179833586263</v>
+        <v>-1.867224783200092</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.227073641371917</v>
+        <v>2.225055661526385</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.217633040128023</v>
+        <v>1.044958803825399</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.702881823196984</v>
+        <v>3.599277281415409</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.855125143371089</v>
+        <v>-1.860170092984918</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.226570873447532</v>
+        <v>2.224552893602</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.224687730343196</v>
+        <v>1.052013494040572</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.703789993315633</v>
+        <v>3.600185451534058</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.828173919044601</v>
+        <v>-1.83321886865843</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.247357516822869</v>
+        <v>2.245339536977337</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.239568076370916</v>
+        <v>1.066893840068291</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.722724354577006</v>
+        <v>3.619119812795431</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.964126927100917</v>
+        <v>-1.969171876714746</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.377079445745302</v>
+        <v>2.37506146589977</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.239568076370916</v>
+        <v>1.066893840068291</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.906827486721966</v>
+        <v>3.803222944940391</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.986535044905789</v>
+        <v>-1.991579994519618</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.360232893526346</v>
+        <v>2.358214913680815</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.239568076370916</v>
+        <v>1.066893840068291</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.898944181624959</v>
+        <v>3.795339639843384</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.134540812385189</v>
+        <v>-2.139585761999018</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.303084586084224</v>
+        <v>2.301066606238692</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.152841067507374</v>
+        <v>0.98016683120475</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.848961975856471</v>
+        <v>3.745357434074897</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.143981738273719</v>
+        <v>-2.149026687887548</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.355561933450659</v>
+        <v>2.353543953605127</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.275268185050765</v>
+        <v>1.102593948748142</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.978671964104353</v>
+        <v>3.875067422322779</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.19625534560936</v>
+        <v>-2.201300295223189</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.337543585061703</v>
+        <v>2.335525605216172</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.222994577715124</v>
+        <v>1.0503203414125</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.95019889424827</v>
+        <v>3.846594352466695</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.272585323210266</v>
+        <v>-2.277630272824095</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.305123406915116</v>
+        <v>2.303105427069585</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.222994577715124</v>
+        <v>1.0503203414125</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.948310707142045</v>
+        <v>3.84470616536047</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.384342275825567</v>
+        <v>-2.389387225439396</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.255240855471858</v>
+        <v>2.253222875626326</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.111237625099823</v>
+        <v>0.9385633887971991</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.876076765175726</v>
+        <v>3.772472223394152</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.382501256767316</v>
+        <v>-2.387546206381145</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.254411273305311</v>
+        <v>2.252393293459779</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.112505851771291</v>
+        <v>0.9398316154686676</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.87527171138876</v>
+        <v>3.771667169607185</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.514802548864869</v>
+        <v>-2.519847498478698</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.214564163332208</v>
+        <v>2.212546183486676</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.112505851771291</v>
+        <v>0.9398316154686676</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.888345118254678</v>
+        <v>3.784740576473104</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.516364191679729</v>
+        <v>-2.521409141293558</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.213939506206264</v>
+        <v>2.211921526360732</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.112505851771291</v>
+        <v>0.9398316154686676</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.888345118254678</v>
+        <v>3.784740576473104</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.544264978789202</v>
+        <v>-2.549309928403031</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.201303232489477</v>
+        <v>2.199285252643945</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.077908927628357</v>
+        <v>0.9052346913257328</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.866111004895919</v>
+        <v>3.762506463114345</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.666791081492096</v>
+        <v>-2.671836031105925</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.149057235385518</v>
+        <v>2.147039255539986</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9553828249254628</v>
+        <v>0.7827085886228389</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.789359787251382</v>
+        <v>3.685755245469807</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971075</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.686852402768603</v>
+        <v>-2.691897352382432</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.207738666465419</v>
+        <v>2.205720686619888</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.9353215036489557</v>
+        <v>0.7626472673463318</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.844028954075981</v>
+        <v>3.740424412294407</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199802</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.943573220763427</v>
+        <v>-2.948618170377256</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.245362058269337</v>
+        <v>2.243344078423805</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8269069295051409</v>
+        <v>0.654232693202517</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.919291928591539</v>
+        <v>3.815687386809965</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622232</v>
+        <v>3.668303164622234</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.097559638539567</v>
+        <v>-3.162632538498015</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.25274776030452</v>
+        <v>2.226718600321141</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8269069295051409</v>
+        <v>0.654232693202517</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.988272197737179</v>
+        <v>3.884667655955605</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808524</v>
+        <v>3.619937176808526</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.047037734711902</v>
+        <v>-3.11211063467035</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.259007723955707</v>
+        <v>2.232978563972328</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8269069295051409</v>
+        <v>0.654232693202517</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.9743233998573</v>
+        <v>3.870718858075726</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.65634689399489</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.299512888719626</v>
+        <v>-3.364585788678074</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.169888151408032</v>
+        <v>2.143858991424652</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8269069295051409</v>
+        <v>0.654232693202517</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.986193888912714</v>
+        <v>3.88258934713114</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358295</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.568985690641334</v>
+        <v>-3.634058590599782</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.063309565158292</v>
+        <v>2.037280405174913</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8269069295051409</v>
+        <v>0.654232693202517</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.987404423431657</v>
+        <v>3.883799881650083</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637083</v>
+        <v>3.663523617637085</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.726529762370775</v>
+        <v>-3.791602662329223</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.004413678693837</v>
+        <v>1.978384518710458</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7600051243648664</v>
+        <v>0.5873308880622425</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.951385082574815</v>
+        <v>3.84778054079324</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.65216331330134</v>
+        <v>3.652163313301342</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.855380313072822</v>
+        <v>-3.92045321303127</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.947951311149208</v>
+        <v>1.921922151165829</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7190117155141449</v>
+        <v>0.546337479211521</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.921866890000571</v>
+        <v>3.818262348218997</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215467</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.972348005711713</v>
+        <v>-4.037420905670161</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.063368290792695</v>
+        <v>2.037339130809317</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7190117155141449</v>
+        <v>0.546337479211521</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.084070946699615</v>
+        <v>3.980466404918041</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456689</v>
+        <v>3.696553628456691</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.057065947932666</v>
+        <v>-4.122138847891114</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.024327751868128</v>
+        <v>1.998298591884749</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6338956865860985</v>
+        <v>0.4612214502834746</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.027847967306601</v>
+        <v>3.924243425525027</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253285</v>
+        <v>3.750058176253287</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.13900076620155</v>
+        <v>-4.204073666159998</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.001783242129066</v>
+        <v>1.975754082145687</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.6239609409990183</v>
+        <v>0.4512867046963944</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.032116537522844</v>
+        <v>3.92851199574127</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717829</v>
+        <v>3.783647027717831</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.085262592801287</v>
+        <v>-4.150335492759735</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.032204149945073</v>
+        <v>2.006174989961695</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6776991143992804</v>
+        <v>0.5050248780966565</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.073285080018904</v>
+        <v>3.96968053823733</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.798310944616947</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.975256309324066</v>
+        <v>-4.040329209282514</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.068359550580138</v>
+        <v>2.042330390596758</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.7009036863165556</v>
+        <v>0.5282294500139317</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.079360710413445</v>
+        <v>3.975756168631871</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203659</v>
+        <v>3.785578085203661</v>
       </c>
       <c r="C2028" t="n">
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.83219673358314</v>
+        <v>-3.897269633541588</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.129833391598482</v>
+        <v>2.103804231615103</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.7089171129065349</v>
+        <v>0.536242876603911</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.088418777089407</v>
+        <v>3.984814235307832</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436925</v>
+        <v>3.777251572436927</v>
       </c>
       <c r="C2029" t="n">
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.530750008111303</v>
+        <v>-3.595822908069751</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.257672964669753</v>
+        <v>2.231643804686374</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.010363838378372</v>
+        <v>0.8376896020757483</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.276547695255045</v>
+        <v>4.17294315347347</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064761</v>
+        <v>3.812650101064762</v>
       </c>
       <c r="C2030" t="n">
         <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.517474385647206</v>
+        <v>-3.65077810451282</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.263954391408102</v>
+        <v>2.210632903861857</v>
       </c>
       <c r="F2030" t="n">
-        <v>1.010363838378372</v>
+        <v>0.8376896020757483</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.277518873007756</v>
+        <v>4.173914331226181</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.43869811764084</v>
+        <v>3.857396054639731</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.672143474360487</v>
+        <v>3.655687834438142</v>
       </c>
       <c r="D2031" t="n">
-        <v>-3.292444692477535</v>
+        <v>-3.690259490329856</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.354809173055727</v>
+        <v>2.179227613992452</v>
       </c>
       <c r="F2031" t="n">
-        <v>1.010363838378372</v>
+        <v>0.8376896020757483</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.278361777387511</v>
+        <v>4.158301595683591</v>
       </c>
     </row>
   </sheetData>
